--- a/Results/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001385122794605202</v>
+        <v>0.0001385122794605194</v>
       </c>
       <c r="C2" t="n">
-        <v>3.625612813026398e-05</v>
+        <v>3.625612813026399e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.708970575188211e-05</v>
+        <v>2.708970575188187e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>3.670506773261671e-05</v>
+        <v>3.670506773261651e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>3.536482442033274e-05</v>
+        <v>3.536482442033259e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>4.940853905205322e-05</v>
+        <v>4.940853905205301e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.915285760095599e-05</v>
+        <v>8.915285760095603e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.472419768657017e-05</v>
+        <v>3.472419768657004e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>4.415516815248728e-05</v>
+        <v>4.415516815248734e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.849658550064598e-05</v>
+        <v>6.849658550064606e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>9.482868977935938e-05</v>
+        <v>9.482868977935949e-05</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001592734425647046</v>
+        <v>0.0001592734425647052</v>
       </c>
       <c r="C3" t="n">
-        <v>4.142342151776642e-05</v>
+        <v>4.142342151776641e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.11144016831629e-05</v>
+        <v>3.111440168316289e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.18779626906338e-05</v>
+        <v>4.187796269063379e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.053771937834973e-05</v>
+        <v>4.053771937834982e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.678568331074959e-05</v>
+        <v>5.678568331074939e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001025126958175936</v>
+        <v>0.0001025126958175935</v>
       </c>
       <c r="I3" t="n">
-        <v>3.989956026744255e-05</v>
+        <v>3.989956026744259e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.024915003751891e-05</v>
+        <v>5.024915003751872e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.829444414888619e-05</v>
+        <v>7.829444414888569e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001090268979146226</v>
+        <v>0.0001090268979146228</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001008078015644197</v>
+        <v>8.569403166249024e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.746927688433497e-05</v>
+        <v>2.371232111341035e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.457180286958584e-05</v>
+        <v>1.945803296765656e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.765551455223483e-05</v>
+        <v>2.374510111757816e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>3.765551455223485e-05</v>
+        <v>2.374510111757819e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.771915337219467e-05</v>
+        <v>3.270446960646527e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>7.145692064102959e-05</v>
+        <v>5.634315073910036e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.83416467149196e-05</v>
+        <v>2.386407400509712e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.276117881827852e-05</v>
+        <v>2.764740891634929e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.741958754451581e-05</v>
+        <v>4.230581764258649e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.483148756873552e-05</v>
+        <v>5.971771766680642e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007969228415793577</v>
+        <v>0.001470536052262903</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001744512547370936</v>
+        <v>0.0003241519350910872</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001301138436243807</v>
+        <v>0.0002423737592336268</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001744512550010247</v>
+        <v>0.0003241519377304019</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001744512550010247</v>
+        <v>0.0003241519377304019</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00274875351442335</v>
+        <v>0.000508086514575561</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005803950824716126</v>
+        <v>0.001065262072389386</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001744510382082507</v>
+        <v>0.0003241497698026628</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002274082863168</v>
+        <v>0.0004203600232339448</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003685945289178703</v>
+        <v>0.0006809263376697692</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006408552133469705</v>
+        <v>0.0001502197387609809</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001385532828323368</v>
+        <v>8.782143543200306e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.865678885750789e-05</v>
+        <v>2.568132321001956e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.427906702063764e-05</v>
+        <v>2.116653608825735e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.806956901954174e-05</v>
+        <v>2.557797469389256e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.017168764719247e-05</v>
+        <v>2.594794757035431e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>8.546463464011171e-05</v>
+        <v>3.934767427362179e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001106070509588789</v>
+        <v>6.323357363770529e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>7.608712798283671e-05</v>
+        <v>2.599147777460984e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5764408540692e-05</v>
+        <v>2.993597733509307e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>7.185705893672808e-05</v>
+        <v>4.484681259384713e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.810741652645313e-05</v>
+        <v>6.205428115070378e-05</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001290607005872635</v>
+        <v>9.06665418635669e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.659671102618839e-05</v>
+        <v>2.883874949459845e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.281527988187926e-05</v>
+        <v>2.442888489488512e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.655677558932744e-05</v>
+        <v>2.883172303254405e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.655677558932744e-05</v>
+        <v>2.883172303254405e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>7.597205239503865e-05</v>
+        <v>3.767697980754179e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.97098196638736e-05</v>
+        <v>6.131566094017683e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.659454573776351e-05</v>
+        <v>2.883658420617354e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>7.101407784112251e-05</v>
+        <v>3.261991911742577e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>8.567248656735965e-05</v>
+        <v>4.727832784366296e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001030843865915795</v>
+        <v>6.469022786788288e-05</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001806518474441711</v>
+        <v>9.974658366118132e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001729653165506818</v>
+        <v>4.755962396546824e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001805705733693076</v>
+        <v>4.515381643637234e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001579790466158064</v>
+        <v>4.492204264601733e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001199065107299387</v>
+        <v>3.822127636641335e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001823562316590052</v>
+        <v>5.640059525654405e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002060939989278422</v>
+        <v>8.003927638917946e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001729787250017302</v>
+        <v>4.756019965517577e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001774090255051428</v>
+        <v>5.13454298048272e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001362458247167392</v>
+        <v>5.617923530972313e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002667044699225399</v>
+        <v>9.348736237809161e-05</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0002655415016304578</v>
+        <v>0.000114687162717011</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002504030355699784</v>
+        <v>6.11886624390141e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002466310300308078</v>
+        <v>5.678045674579624e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003050156067420375</v>
+        <v>7.080047708800903e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000250402969910654</v>
+        <v>6.118865305776819e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002597783769388284</v>
+        <v>7.00268927519574e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002835161442076637</v>
+        <v>9.366557388459248e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002504008702815535</v>
+        <v>6.11864971505892e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002548204023849126</v>
+        <v>6.49698320618414e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0002098875285162398</v>
+        <v>7.480221650501158e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002868907111353695</v>
+        <v>9.704014081229855e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.601796685271364e-06</v>
+        <v>4.601796685271349e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>8.143175991594639e-06</v>
+        <v>8.143175991594609e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.16587778390873e-06</v>
+        <v>8.165877783908721e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>8.458822474807921e-06</v>
+        <v>8.45882247480791e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>7.521373656342816e-06</v>
+        <v>7.521373656342797e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.492035251783214e-06</v>
+        <v>8.492035251783212e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>8.11098278715002e-06</v>
+        <v>8.110982787150012e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.092655095024568e-06</v>
+        <v>7.092655095024555e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.926320054702671e-06</v>
+        <v>8.926320054702644e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.058914196204934e-06</v>
+        <v>6.058914196204912e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>8.229032605996401e-06</v>
+        <v>8.229032605996393e-06</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.156144607568403e-06</v>
+        <v>5.156144607568395e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>9.068309616752123e-06</v>
+        <v>9.068309616752099e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.255576168176758e-06</v>
+        <v>9.255576168176749e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>9.389067103875568e-06</v>
+        <v>9.389067103875526e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.451618285410452e-06</v>
+        <v>8.451618285410426e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.630724819548364e-06</v>
+        <v>9.630724819548325e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.202448733969395e-06</v>
+        <v>9.202448733969378e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.034960502208883e-06</v>
+        <v>8.034960502208852e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.779436640855719e-06</v>
+        <v>9.77943664085568e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.696741070330773e-06</v>
+        <v>6.696741070330762e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.328640837476449e-06</v>
+        <v>9.328640837476434e-06</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.140951471283294e-05</v>
+        <v>4.541596705601712e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.221379231240471e-05</v>
+        <v>5.908966911653498e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.35282099030458e-05</v>
+        <v>6.660291895814565e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.227143512987191e-05</v>
+        <v>5.919112804576492e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.227143512987193e-05</v>
+        <v>5.919112804576502e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.363267484196435e-05</v>
+        <v>6.838440443559681e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.349588910655878e-05</v>
+        <v>6.627971099327545e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.232070361790951e-05</v>
+        <v>5.927515155798204e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.259191722495095e-05</v>
+        <v>5.723999217719703e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.173988979660993e-05</v>
+        <v>4.8719717893787e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35663651395883e-05</v>
+        <v>6.698447132357081e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.025451067181466e-05</v>
+        <v>1.48983159382635e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002019151751589185</v>
+        <v>3.929641011172657e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002542543662990526</v>
+        <v>4.902809519193747e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002019151760777335</v>
+        <v>3.929641103054187e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002019151760777334</v>
+        <v>3.929641103054187e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002769779712833941</v>
+        <v>5.318721236610582e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002818656606608435</v>
+        <v>5.38610506369442e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002019148497395962</v>
+        <v>3.929608469240384e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001819905830721754</v>
+        <v>3.553816424527997e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001019716036550596</v>
+        <v>2.075275334241414e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001358417961238138</v>
+        <v>5.703478044387972e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.474360938998625e-05</v>
+        <v>6.888397356064295e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.503543804933144e-05</v>
+        <v>6.405576558661675e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.648255445188787e-05</v>
+        <v>9.037703690169963e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.486608325117527e-05</v>
+        <v>6.375770871451425e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.519496486854226e-05</v>
+        <v>6.433654035794381e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.69667695191177e-05</v>
+        <v>7.338044303161744e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.750234756687971e-05</v>
+        <v>9.093107774986429e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.515936192648466e-05</v>
+        <v>6.427119015400268e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.603575672399527e-05</v>
+        <v>8.090114956730423e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.435871785718483e-05</v>
+        <v>5.332885525541871e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.647110576037967e-05</v>
+        <v>7.209681478846175e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.616648009164212e-05</v>
+        <v>7.138822598198759e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.707799441604124e-05</v>
+        <v>8.525066467717898e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.827706266816583e-05</v>
+        <v>9.256089968410073e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.709787957223741e-05</v>
+        <v>8.528567012293206e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.709787957223743e-05</v>
+        <v>8.528567012293206e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.838964022077353e-05</v>
+        <v>9.435666336156718e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.825285448536793e-05</v>
+        <v>9.225196991924608e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.707766899671868e-05</v>
+        <v>8.524741048395257e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.734888260376008e-05</v>
+        <v>8.321225110316745e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>2.64968551754191e-05</v>
+        <v>7.469197681975739e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.832333051839745e-05</v>
+        <v>9.29567302495412e-06</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.257446139824585e-05</v>
+        <v>1.354662727343965e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.783527479279879e-05</v>
+        <v>2.097834774654783e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001061215461397983</v>
+        <v>2.295671898517908e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.844486735067675e-05</v>
+        <v>1.93256368027935e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.459035683437959e-05</v>
+        <v>1.51272429746746e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.911092423241765e-05</v>
+        <v>2.188261225476102e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.897413849700718e-05</v>
+        <v>2.167214291052797e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.779895300836293e-05</v>
+        <v>2.097168696699953e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.807691016302856e-05</v>
+        <v>2.076935789329649e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.22674492678486e-05</v>
+        <v>1.376482220812983e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001348877284374201</v>
+        <v>2.805100695707434e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.513317097846915e-05</v>
+        <v>1.575696014758203e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.445284184191452e-05</v>
+        <v>2.03830395504179e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.566002812435125e-05</v>
+        <v>2.111549182443729e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001156954642129647</v>
+        <v>2.412174182456793e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>9.445283814115755e-05</v>
+        <v>2.038303965618843e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.57644876466468e-05</v>
+        <v>2.129363941885674e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>9.562770191124125e-05</v>
+        <v>2.108317007462461e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>9.445251642259198e-05</v>
+        <v>2.038271413109529e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.472373002963338e-05</v>
+        <v>2.01791981930168e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>8.320594668640357e-05</v>
+        <v>1.744999773382702e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.569817794427077e-05</v>
+        <v>2.115364610765418e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.154091671158334e-05</v>
+        <v>3.154091671158337e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>5.618271697718505e-05</v>
+        <v>5.618271697718503e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.960536594488943e-05</v>
+        <v>1.960536594488944e-05</v>
       </c>
       <c r="E2" t="n">
         <v>2.192338845442425e-05</v>
@@ -1322,22 +1322,22 @@
         <v>2.192338845442425e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>3.020782572633896e-05</v>
+        <v>3.020782572633892e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>4.567445539929084e-05</v>
+        <v>4.567445539929082e-05</v>
       </c>
       <c r="I2" t="n">
         <v>2.194246184944976e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.990111518087521e-05</v>
+        <v>3.990111518087525e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.389488268498794e-05</v>
+        <v>3.389488268498797e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.413197463399527e-05</v>
+        <v>2.413197463399529e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.609811388385378e-05</v>
+        <v>3.609811388385375e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.436920444343048e-05</v>
+        <v>6.43692044434306e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.236975806026297e-05</v>
+        <v>2.236975806026298e-05</v>
       </c>
       <c r="E3" t="n">
         <v>2.504044412229731e-05</v>
@@ -1365,19 +1365,19 @@
         <v>3.456478310185705e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.236725921670896e-05</v>
+        <v>5.236725921670894e-05</v>
       </c>
       <c r="I3" t="n">
         <v>2.506579405624984e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>4.559262940209753e-05</v>
+        <v>4.559262940209755e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.867448889997999e-05</v>
+        <v>3.867448889998001e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.757732598219435e-05</v>
+        <v>2.757732598219433e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.531497370202655e-05</v>
+        <v>2.135691294441773e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>5.082037992296777e-05</v>
+        <v>3.593013772499266e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.821979452341452e-05</v>
+        <v>1.426173376580597e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.852414161786436e-05</v>
+        <v>1.546535247348163e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.852414161786455e-05</v>
+        <v>1.546535247348162e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.441827820335262e-05</v>
+        <v>2.054610246798489e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.371350632173602e-05</v>
+        <v>2.975544556412702e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.894445634950137e-05</v>
+        <v>1.553828064644813e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.980413033213919e-05</v>
+        <v>2.584606957453024e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.619517648982137e-05</v>
+        <v>2.223711573221282e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>3.091346277729923e-05</v>
+        <v>1.695540201969e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001511892983674674</v>
+        <v>0.0002812346412914289</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002957087927136172</v>
+        <v>0.0005474332232628834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007957717772724709</v>
+        <v>0.0001493508819976453</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00093963963292213</v>
+        <v>0.0001758216780741254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00093963963292213</v>
+        <v>0.0001758216780741254</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001447864146734212</v>
+        <v>0.0002693125739814497</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002599079422655377</v>
+        <v>0.0004794998444018604</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009396383620248008</v>
+        <v>0.0001758204071767958</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00201890476784956</v>
+        <v>0.0003741677798901796</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001575546318558714</v>
+        <v>0.0002931629152682991</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001216851448121639</v>
+        <v>0.0002256804863092949</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.261672186085006e-05</v>
+        <v>2.31169290679448e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>6.252375677414038e-05</v>
+        <v>3.798993203963785e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.715008181081181e-05</v>
+        <v>1.583347414943119e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.730238354695016e-05</v>
+        <v>1.701032304462922e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.868698920609594e-05</v>
+        <v>1.725401363931838e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>6.17200263621753e-05</v>
+        <v>2.535121011790069e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>7.314175766648745e-05</v>
+        <v>3.493481777273823e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>5.624620450832403e-05</v>
+        <v>2.034338829636394e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>6.79468732572477e-05</v>
+        <v>3.079919230251035e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.667922530270992e-05</v>
+        <v>2.408230831328277e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>4.078321121463543e-05</v>
+        <v>1.869247773524867e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.716406139803179e-05</v>
+        <v>2.52023523580778e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>7.152963662258997e-05</v>
+        <v>3.957496688437644e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>5.006019090360489e-05</v>
+        <v>1.810564350789082e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>5.077954796283922e-05</v>
+        <v>1.938230396897281e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>5.077954796283922e-05</v>
+        <v>1.938230396897281e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>5.626736589935802e-05</v>
+        <v>2.439154188164495e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.556259401774071e-05</v>
+        <v>3.360088497778704e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.079354404550599e-05</v>
+        <v>1.938372006010817e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.16532180281438e-05</v>
+        <v>2.969150898819027e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>5.804426418582653e-05</v>
+        <v>2.608255514587288e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.276255047330391e-05</v>
+        <v>2.080084143335004e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001011074433380054</v>
+        <v>3.293638753760538e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001603668231156073</v>
+        <v>5.521031162245087e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001482087289575484</v>
+        <v>3.537978611178324e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001273523975009027</v>
+        <v>3.285912541464621e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>9.615717141769445e-05</v>
+        <v>2.736876565375178e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000145099282544658</v>
+        <v>4.002595912650079e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001543945106630851</v>
+        <v>4.923530222265092e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001396254606908055</v>
+        <v>3.501813730496405e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001504939565564732</v>
+        <v>4.532747888445096e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001011538185478772</v>
+        <v>3.366983667248117e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001884842951363977</v>
+        <v>4.468786836462024e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001435030218591013</v>
+        <v>4.03980093168867e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001891312078652286</v>
+        <v>6.027284331092722e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000167670449562337</v>
+        <v>3.880504891966596e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002044727182011169</v>
+        <v>4.643230178433638e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001683963426441112</v>
+        <v>4.008285972070852e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.000173868937141997</v>
+        <v>4.508941830819565e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001831641652603788</v>
+        <v>5.429876140433775e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001683951152881448</v>
+        <v>4.008159648665886e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001792547892707824</v>
+        <v>5.038938541474101e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001362806291089488</v>
+        <v>4.359242371526063e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001703641217159423</v>
+        <v>4.149871785990071e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.512730186874157e-05</v>
+        <v>1.512730186874158e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>3.839626396517913e-05</v>
+        <v>3.839626396517912e-05</v>
       </c>
       <c r="D2" t="n">
         <v>1.477583314065554e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.319355303732831e-05</v>
+        <v>1.31935530373283e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.319355303732831e-05</v>
+        <v>1.31935530373283e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.930764861246445e-05</v>
+        <v>1.930764861246443e-05</v>
       </c>
       <c r="H2" t="n">
         <v>2.65046987750821e-05</v>
@@ -1727,13 +1727,13 @@
         <v>1.307783014272801e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.579455882524257e-05</v>
+        <v>2.579455882524256e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.420541361440488e-05</v>
+        <v>1.420541361440489e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.101492059182575e-05</v>
+        <v>1.101492059182573e-05</v>
       </c>
     </row>
     <row r="3">
@@ -1743,19 +1743,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.725718540220238e-05</v>
+        <v>1.72571854022024e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>4.396204446852393e-05</v>
+        <v>4.396204446852381e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.685292355837579e-05</v>
+        <v>1.685292355837582e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.501724733715509e-05</v>
+        <v>1.501724733715508e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.501724733715509e-05</v>
+        <v>1.501724733715507e-05</v>
       </c>
       <c r="G3" t="n">
         <v>2.206545011370285e-05</v>
@@ -1767,10 +1767,10 @@
         <v>1.491004409372543e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.938225754013014e-05</v>
+        <v>2.938225754013013e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.612909861945689e-05</v>
+        <v>1.612909861945695e-05</v>
       </c>
       <c r="L3" t="n">
         <v>1.252810804743871e-05</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.24573876834681e-05</v>
+        <v>1.121808055312186e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.679016368226396e-05</v>
+        <v>2.495688669621401e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.224845441761427e-05</v>
+        <v>1.10091472872681e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.048572540416468e-05</v>
+        <v>9.87256947068063e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>2.048572540416469e-05</v>
+        <v>9.872569470680614e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.484292134245999e-05</v>
+        <v>1.368560661552766e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.921938224456646e-05</v>
+        <v>1.798007511422025e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.060467917371561e-05</v>
+        <v>9.892692699958203e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>2.822681581048714e-05</v>
+        <v>1.698750868014106e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.164133939099019e-05</v>
+        <v>1.040203226064384e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.001563318384944e-05</v>
+        <v>8.776326053503319e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000561483740744114</v>
+        <v>0.0001060867181777401</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00186257732034463</v>
+        <v>0.0003462954245275838</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0005425860111520372</v>
+        <v>0.0001025885567762941</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004541350034141399</v>
+        <v>8.619484198687575e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0004541350034141399</v>
+        <v>8.619484198687575e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000812739776724603</v>
+        <v>0.0001523554524113872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001336804072299132</v>
+        <v>0.000248114979316814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004541340172077699</v>
+        <v>8.619385578050571e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001148342962080448</v>
+        <v>0.0002141279493554282</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004887295349234641</v>
+        <v>9.260955422890922e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003861845155997514</v>
+        <v>7.322204900949607e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.238184350503738e-05</v>
+        <v>1.472478475871675e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.455183776004191e-05</v>
+        <v>2.63229413265008e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.840460469399832e-05</v>
+        <v>1.466685238338608e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.600248255525352e-05</v>
+        <v>1.084351872401105e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.693571979469075e-05</v>
+        <v>1.100776847726206e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.124727134940576e-05</v>
+        <v>1.481277221064254e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.140950139760383e-05</v>
+        <v>2.188553606399276e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.700902918066166e-05</v>
+        <v>1.101985829507306e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.534674294533161e-05</v>
+        <v>1.824061584908351e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.77168981317119e-05</v>
+        <v>1.14713305932168e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.634830671262493e-05</v>
+        <v>9.890876588528505e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.106032940201065e-05</v>
+        <v>1.449219827784422e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>5.465816309397052e-05</v>
+        <v>2.810165457563413e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>4.084320154419086e-05</v>
+        <v>1.428182276381225e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.926197095427795e-05</v>
+        <v>1.317718866959418e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>3.926197095427795e-05</v>
+        <v>1.317718866959418e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>4.34458630610025e-05</v>
+        <v>1.695972434024999e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.782232396310916e-05</v>
+        <v>2.125419283894265e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.920762089225824e-05</v>
+        <v>1.316681042468055e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.68297575290298e-05</v>
+        <v>2.026162640486332e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.02442811095328e-05</v>
+        <v>1.36761499853662e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.861857490239211e-05</v>
+        <v>1.205044377822571e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.107117522777509e-05</v>
+        <v>2.15341071050215e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001345967107093308</v>
+        <v>4.217083887973409e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001289855918467287</v>
+        <v>2.979488337299975e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001082366005394881</v>
+        <v>2.531672341081182e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>8.051962660042584e-05</v>
+        <v>2.04385360239698e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001233151511208033</v>
+        <v>3.101671896260571e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001276916120230395</v>
+        <v>3.531118746132092e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001190769089520592</v>
+        <v>2.722380504703625e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000126706878913383</v>
+        <v>3.431999969233284e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.951473590754913e-05</v>
+        <v>2.058774999236577e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001601233387832097</v>
+        <v>3.343528210537361e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001033314214372631</v>
+        <v>2.545191041666231e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001404339688411675</v>
+        <v>4.319819630533855e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001266272010393648</v>
+        <v>2.937980659315284e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001521083207666534</v>
+        <v>3.303814612895355e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001249843867982493</v>
+        <v>2.826433377638184e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001292216688081995</v>
+        <v>3.205626606995447e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001335981297103059</v>
+        <v>3.635073456864715e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001249834266394553</v>
+        <v>2.826335215438505e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001326055632762268</v>
+        <v>3.535816813456777e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001124013630669507</v>
+        <v>2.637579634105737e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000124394380649589</v>
+        <v>2.714698550793015e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.089271343763653e-06</v>
+        <v>6.089271343763648e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3457766781316e-05</v>
+        <v>2.345776678131599e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.105747320194791e-05</v>
+        <v>1.105747320194788e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.019365635738703e-06</v>
+        <v>6.019365635738689e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.019365635738703e-06</v>
+        <v>6.019365635738689e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.191433032894797e-05</v>
+        <v>1.191433032894795e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.585959839839791e-05</v>
+        <v>1.585959839839792e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>5.890496285473144e-06</v>
+        <v>5.890496285473104e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.225463762284658e-05</v>
+        <v>1.225463762284655e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.073916836317218e-06</v>
+        <v>6.07391683631717e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>6.526174337404388e-06</v>
+        <v>6.52617433740438e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.883778930580916e-06</v>
+        <v>6.883778930580886e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.682625788869672e-05</v>
+        <v>2.682625788869674e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.259824022740728e-05</v>
+        <v>1.259824022740721e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.785659888182871e-06</v>
+        <v>6.785659888182849e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.78565988818287e-06</v>
+        <v>6.785659888182848e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.358380342087648e-05</v>
+        <v>1.358380342087641e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.813316504816495e-05</v>
+        <v>1.813316504816494e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.66559080946505e-06</v>
+        <v>6.665590809464912e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.382946772090136e-05</v>
+        <v>1.382946772090135e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.817318968875005e-06</v>
+        <v>6.817318968875038e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.387089230877397e-06</v>
+        <v>7.387089230877387e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.467175342064551e-05</v>
+        <v>5.52575458471137e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>2.521763095343028e-05</v>
+        <v>1.578962170627047e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.762513890476535e-05</v>
+        <v>8.479140068831208e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.384768036045036e-05</v>
+        <v>5.288712621528354e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.384768036045036e-05</v>
+        <v>5.288712621528354e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.803545657382868e-05</v>
+        <v>8.971072947882143e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.047913405051959e-05</v>
+        <v>1.133313521458535e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.392194512205421e-05</v>
+        <v>5.300997209136089e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.775994642469564e-05</v>
+        <v>8.613947588761432e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.446949921928642e-05</v>
+        <v>5.323500383352273e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49333977099868e-05</v>
+        <v>5.787398874052602e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.937894333547031e-05</v>
+        <v>1.867421993847419e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001070361152522375</v>
+        <v>0.0001997348805056785</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0003755883491842423</v>
+        <v>7.148066473663862e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>9.402999020328161e-05</v>
+        <v>1.940079907739869e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>9.402999020328161e-05</v>
+        <v>1.940079907739869e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004340505611831282</v>
+        <v>8.218973096237565e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007195947799872759</v>
+        <v>0.0001343774882327257</v>
       </c>
       <c r="I5" t="n">
-        <v>9.402903630721479e-05</v>
+        <v>1.939984518132728e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004073446096470764</v>
+        <v>7.718084794436346e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>8.586895880594508e-05</v>
+        <v>1.78898052025124e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001449803891216627</v>
+        <v>2.867566923848507e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.039335371088796e-05</v>
+        <v>6.241663403303076e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>3.023975963180232e-05</v>
+        <v>1.667351634887344e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.187455513493099e-05</v>
+        <v>9.227037321286342e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.718582209079531e-05</v>
+        <v>5.87622556288557e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.795646889871906e-05</v>
+        <v>6.011859400345184e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.210312033786814e-05</v>
+        <v>1.173807458397155e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.840259075497005e-05</v>
+        <v>1.448766357747552e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.798960888609365e-05</v>
+        <v>8.067998845225468e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.232444157779924e-05</v>
+        <v>1.152467561704949e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.816338247952668e-05</v>
+        <v>5.97362383363178e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.900996544535151e-05</v>
+        <v>6.504874791589274e-06</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.163437316249728e-05</v>
+        <v>8.51117564310046e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>4.181461362834294e-05</v>
+        <v>1.871069064122699e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>3.457959600354192e-05</v>
+        <v>1.146312450204684e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.095777816763686e-05</v>
+        <v>8.300089819275717e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>3.095777816763686e-05</v>
+        <v>8.300089819275717e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.499807631568045e-05</v>
+        <v>1.195649400627125e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.74417537923713e-05</v>
+        <v>1.431855627297444e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.088456486390604e-05</v>
+        <v>8.28641826752517e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.472256616654732e-05</v>
+        <v>1.159936864715052e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.143211896113822e-05</v>
+        <v>8.308921441741353e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.18960174518386e-05</v>
+        <v>8.772819932441695e-06</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.046846608698235e-05</v>
+        <v>1.534597596077474e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001185456634767563</v>
+        <v>3.221535534133477e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001190720664020549</v>
+        <v>2.633379921160681e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>9.726435049093037e-05</v>
+        <v>1.997004648494053e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>7.096610766691232e-05</v>
+        <v>1.534155577299326e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001116422230948619</v>
+        <v>2.54458637663136e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001140859005716933</v>
+        <v>2.780792603304155e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001075287116430875</v>
+        <v>2.177578802756755e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001113741437028509</v>
+        <v>2.509004622043933e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.956387072370037e-05</v>
+        <v>1.502010971558704e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001480359271060006</v>
+        <v>2.921344392081454e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.149148162026386e-05</v>
+        <v>1.728602668411994e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001111771536589093</v>
+        <v>3.09184976204574e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001039502984517118</v>
+        <v>2.367236806676762e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001227568907470347</v>
+        <v>2.445673354570327e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001002480409562731</v>
+        <v>2.049517600399531e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001043606163462468</v>
+        <v>2.41643009855016e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001068042938229377</v>
+        <v>2.652636325220482e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001002471048944724</v>
+        <v>2.049422524675556e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001040851061971137</v>
+        <v>2.38071756263809e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>8.903461815442813e-05</v>
+        <v>1.619402412458878e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000101258557482405</v>
+        <v>2.098062691167207e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.716482163333416e-06</v>
+        <v>5.716482163333383e-06</v>
       </c>
       <c r="C2" t="n">
         <v>5.171588593100944e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.167156691731688e-05</v>
+        <v>1.167156691731685e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.823127342551885e-06</v>
+        <v>5.823127342551855e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.823127342551889e-06</v>
+        <v>5.823127342551855e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.876235783108258e-05</v>
+        <v>1.876235783108256e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>3.542812877170401e-05</v>
+        <v>3.542812877170403e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.022002939536812e-06</v>
+        <v>6.022002939536779e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.960407520614723e-05</v>
+        <v>3.96040752061472e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.083037438621757e-05</v>
+        <v>2.08303743862175e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>2.152402189498158e-05</v>
+        <v>2.152402189498163e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.421951786029535e-06</v>
+        <v>6.421951786029514e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.875432750308614e-06</v>
+        <v>5.875432750308612e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.327153284520097e-05</v>
+        <v>1.327153284520094e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.575974414556183e-06</v>
+        <v>6.575974414556178e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.575974414556183e-06</v>
+        <v>6.575974414556178e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.142741124894421e-05</v>
+        <v>2.142741124894419e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>4.06087516945553e-05</v>
+        <v>4.060875169455531e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.780773568819326e-06</v>
+        <v>6.780773568819316e-06</v>
       </c>
       <c r="J3" t="n">
         <v>4.525792363795643e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.370863431491037e-05</v>
+        <v>2.370863431491032e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.46043558678099e-05</v>
+        <v>2.460435586780994e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.312142212038126e-05</v>
+        <v>5.015446312155344e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.242396089718851e-05</v>
+        <v>4.902935798349308e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.666146766827814e-05</v>
+        <v>8.555491860052228e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.237321710361895e-05</v>
+        <v>5.038262479989775e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.237321710361892e-05</v>
+        <v>5.038262479989775e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.076359014956201e-05</v>
+        <v>1.275076939927659e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.078014913878561e-05</v>
+        <v>2.26741733305597e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.258013575291219e-05</v>
+        <v>5.073136401885926e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>3.270505401568232e-05</v>
+        <v>2.459907820745635e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.172042538584562e-05</v>
+        <v>1.36144495776197e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.251863585339396e-05</v>
+        <v>1.441266004516805e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.817011430083476e-05</v>
+        <v>1.118401610249011e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>6.79539324553227e-05</v>
+        <v>1.467621073962342e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004087092589960952</v>
+        <v>7.755590275986224e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>8.354660383621255e-05</v>
+        <v>1.756477847705002e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.354660383621255e-05</v>
+        <v>1.756477847705002e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00084091885683283</v>
+        <v>0.0001570980955533704</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002010652994146596</v>
+        <v>0.0003711317921637806</v>
       </c>
       <c r="I5" t="n">
-        <v>8.354473034084806e-05</v>
+        <v>1.756290498168555e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002066999896511439</v>
+        <v>0.0003826349685466547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009029235970429403</v>
+        <v>0.0001687062069488869</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001125167534449403</v>
+        <v>0.0002084788651464976</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.029205489570703e-05</v>
+        <v>5.776075094980263e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.61447213376806e-05</v>
+        <v>5.55778963232752e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067130996744058e-05</v>
+        <v>9.26122410088077e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.54959703292069e-05</v>
+        <v>5.587867044715175e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.682425365450174e-05</v>
+        <v>5.821644908700304e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.508534462084876e-05</v>
+        <v>1.351139818210152e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.976210594758283e-05</v>
+        <v>2.601499771080539e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.975076852823787e-05</v>
+        <v>5.833765184710849e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.062020906892692e-05</v>
+        <v>2.775214547974219e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.671373226628337e-05</v>
+        <v>1.449327158381475e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.71611108352766e-05</v>
+        <v>1.522973563755197e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.191729479395341e-05</v>
+        <v>8.3235198847789e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>3.18608901180928e-05</v>
+        <v>8.323835322691959e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.544880780499284e-05</v>
+        <v>1.1862063706197e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.146922856180968e-05</v>
+        <v>8.399160478419965e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>3.146922856180968e-05</v>
+        <v>8.399160478419965e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.955946282313417e-05</v>
+        <v>1.605884297190016e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.957602181235776e-05</v>
+        <v>2.598224690318322e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.137600842648432e-05</v>
+        <v>8.381209974509483e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>5.150092668925439e-05</v>
+        <v>2.79071517800799e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.051629805941777e-05</v>
+        <v>1.692252315024323e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>4.131450852696614e-05</v>
+        <v>1.772073361779158e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.343361721142166e-05</v>
+        <v>1.563039259066025e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000114272509116186</v>
+        <v>2.282828018776249e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001262207938664614</v>
+        <v>2.78379331664485e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001026204901097228</v>
+        <v>2.092178244299752e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>7.424674242319198e-05</v>
+        <v>1.59280028772274e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001218650057565664</v>
+        <v>3.054461844969153e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001318815647458034</v>
+        <v>4.046802238097699e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001136815513599166</v>
+        <v>2.286698545230087e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001338144858746102</v>
+        <v>4.239433811820218e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>8.127493976453671e-05</v>
+        <v>2.409604405147369e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001662278030296902</v>
+        <v>3.970547333114442e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000101475164721289</v>
+        <v>2.05657049256544e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001269274424924594</v>
+        <v>2.505554844991797e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001305238959202756</v>
+        <v>2.859527912381608e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001558808814670322</v>
+        <v>3.02956112710909e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000126444406777716</v>
+        <v>2.511479175384412e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001346260151975009</v>
+        <v>3.279055609912617e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001446425741867246</v>
+        <v>4.271396003040921e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001264425608008511</v>
+        <v>2.511292310173551e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001465674790636212</v>
+        <v>4.463886490730595e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001034628651188802</v>
+        <v>2.800111889267808e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001363810609013328</v>
+        <v>3.445244674501757e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.82883657387398e-06</v>
+        <v>4.828836573874057e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.71008326839645e-06</v>
+        <v>4.710083268396456e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.197584544180271e-06</v>
+        <v>5.197584544180419e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.199876168580882e-06</v>
+        <v>5.199876168580859e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.199876168580881e-06</v>
+        <v>5.199876168580859e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.754682954978446e-06</v>
+        <v>5.754682954978427e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.419605980133886e-06</v>
+        <v>6.419605980133891e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.061756188844062e-06</v>
+        <v>5.061756188844138e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.411790357477658e-05</v>
+        <v>1.411790357477663e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.184740495145277e-06</v>
+        <v>5.18474049514528e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>6.664431993336501e-06</v>
+        <v>6.664431993336494e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.403151629358808e-06</v>
+        <v>5.403151629358766e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.291343741231839e-06</v>
+        <v>5.291343741231841e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.827288181122967e-06</v>
+        <v>5.827288181122987e-06</v>
       </c>
       <c r="E3" t="n">
         <v>5.81096664331349e-06</v>
@@ -2946,22 +2946,22 @@
         <v>5.81096664331349e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.468066756129023e-06</v>
+        <v>6.468066756129068e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.244408558026262e-06</v>
+        <v>7.24440855802628e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.685987298746233e-06</v>
+        <v>5.685987298746322e-06</v>
       </c>
       <c r="J3" t="n">
         <v>1.595600125589474e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.761721055139906e-06</v>
+        <v>5.761721055139963e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.514873973764477e-06</v>
+        <v>7.514873973764484e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.131817081159873e-05</v>
+        <v>4.409312690568304e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.121507818799823e-05</v>
+        <v>4.428230329654737e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.153737585476885e-05</v>
+        <v>4.628517733738457e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.12370700500294e-05</v>
+        <v>4.514965452299246e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.123707005002971e-05</v>
+        <v>4.514965452299246e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.178000848898653e-05</v>
+        <v>4.944106310186099e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.226388032697589e-05</v>
+        <v>5.355022205945511e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.089264420793388e-05</v>
+        <v>4.454161548300343e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.631969852214921e-05</v>
+        <v>9.410840401118811e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.132871977342023e-05</v>
+        <v>4.419861652389849e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.240957388319895e-05</v>
+        <v>5.50071576216857e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.535993232578991e-05</v>
+        <v>1.04006626846012e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>6.662737637142061e-05</v>
+        <v>1.418079475709182e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.1320835154285e-05</v>
+        <v>1.691040650390262e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.455064332419383e-05</v>
+        <v>1.56581542881716e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>7.455064332419383e-05</v>
+        <v>1.56581542881716e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001141834311868174</v>
+        <v>2.296710860734498e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001652501440245383</v>
+        <v>3.228060447081747e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.455041886288521e-05</v>
+        <v>1.565792982686288e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0005472940150807218</v>
+        <v>0.0001028623196090509</v>
       </c>
       <c r="K5" t="n">
-        <v>6.232866845248472e-05</v>
+        <v>1.339585257126788e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001837372353475684</v>
+        <v>3.565438401650682e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.363230557574375e-05</v>
+        <v>4.816600406850899e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.349521502522885e-05</v>
+        <v>4.829534410832812e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.37111622917738e-05</v>
+        <v>5.035645353141179e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.299878308584541e-05</v>
+        <v>4.825026944922758e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.323725577081933e-05</v>
+        <v>4.866998137250739e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.409414325313159e-05</v>
+        <v>6.971694687188248e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.531807702723803e-05</v>
+        <v>7.652560812742185e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.320677897207913e-05</v>
+        <v>6.481749925302507e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.904880072529271e-05</v>
+        <v>9.891162386269393e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.362655676152237e-05</v>
+        <v>4.824280960104431e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.476468750178986e-05</v>
+        <v>5.915215756794556e-06</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.644615849319677e-05</v>
+        <v>7.071838508102384e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.645440658342168e-05</v>
+        <v>7.110352112715905e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.665728978162015e-05</v>
+        <v>7.289622570444794e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.615518732538021e-05</v>
+        <v>7.140554078533917e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.615518732538021e-05</v>
+        <v>7.140554078533917e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.690799617058467e-05</v>
+        <v>7.606632127720161e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.739186800857402e-05</v>
+        <v>8.017548023479593e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.602063188953199e-05</v>
+        <v>7.116687365834415e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.144768620374731e-05</v>
+        <v>1.207336621865289e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.645670745501835e-05</v>
+        <v>7.082387469923927e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.753756156479707e-05</v>
+        <v>8.163241579702651e-06</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.344362451694225e-05</v>
+        <v>1.358339249299807e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.854862532522165e-05</v>
+        <v>1.979893454251828e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001058614904957056</v>
+        <v>2.122956182058882e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.853861780167937e-05</v>
+        <v>1.812003778286912e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.421117545481501e-05</v>
+        <v>1.383840795302144e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.885674661810239e-05</v>
+        <v>2.026961213786765e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.934061845614651e-05</v>
+        <v>2.06805280336367e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.796938233704974e-05</v>
+        <v>1.977966737598191e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001034033055815295</v>
+        <v>2.473755516052033e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.280493542648577e-05</v>
+        <v>1.347967555823784e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001359958511732362</v>
+        <v>2.725190044735408e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.504748269903836e-05</v>
+        <v>1.562567152198069e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.347750512950607e-05</v>
+        <v>1.890641739290857e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.368846450889462e-05</v>
+        <v>1.90871092585192e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001143022877912802</v>
+        <v>2.265444367646868e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>9.304394987042726e-05</v>
+        <v>1.891297622267211e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.393109471666903e-05</v>
+        <v>1.940269740791283e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>9.441496655465827e-05</v>
+        <v>1.981361330367227e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>9.304373043561643e-05</v>
+        <v>1.891275264602708e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.847078474983183e-05</v>
+        <v>2.386943149884554e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>8.280615862106137e-05</v>
+        <v>1.479590347973824e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.456066011088146e-05</v>
+        <v>1.995930685989531e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.664025498257956e-06</v>
+        <v>4.664025498257948e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.695790043632526e-06</v>
+        <v>4.695790043632522e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.003700617257675e-06</v>
+        <v>5.003700617257668e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.046005536540942e-06</v>
+        <v>5.046005536540932e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.046005536540942e-06</v>
+        <v>5.046005536540932e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.893499441361127e-06</v>
+        <v>4.893499441361107e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.068038152599936e-06</v>
+        <v>5.068038152599931e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.821253436714962e-06</v>
+        <v>4.821253436714957e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.914951623649138e-06</v>
+        <v>5.914951623649127e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.088810956093928e-06</v>
+        <v>5.088810956093934e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.835097258857848e-06</v>
+        <v>4.835097258857842e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.223117756651348e-06</v>
+        <v>5.223117756651338e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.268953823976389e-06</v>
+        <v>5.26895382397638e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.613814506989948e-06</v>
+        <v>5.613814506989941e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.630512571018563e-06</v>
+        <v>5.630512571018551e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.630512571018564e-06</v>
+        <v>5.630512571018551e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.487060326604102e-06</v>
+        <v>5.487060326604093e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.698734920799022e-06</v>
+        <v>5.698734920799017e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.419258405073608e-06</v>
+        <v>5.419258405073599e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.530270978614177e-06</v>
+        <v>6.530270978614164e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.650060764897767e-06</v>
+        <v>5.650060764897774e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.420333209707787e-06</v>
+        <v>5.420333209707777e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.130770220067762e-05</v>
+        <v>4.378783667459582e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.127913679782197e-05</v>
+        <v>4.43463360974635e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.150962466566722e-05</v>
+        <v>4.580706132449187e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.112296778609844e-05</v>
+        <v>4.429149276413964e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.112296778609844e-05</v>
+        <v>4.429149276413965e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.13566138691259e-05</v>
+        <v>4.49979605047429e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.15480471359244e-05</v>
+        <v>4.619128602706356e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.084411192858353e-05</v>
+        <v>4.37995480903797e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.153022573904796e-05</v>
+        <v>4.60130720582992e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.131624089075451e-05</v>
+        <v>4.387322357536454e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.140981142633434e-05</v>
+        <v>4.480892893116269e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.460831752990649e-05</v>
+        <v>1.02396919336459e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>6.861830805778754e-05</v>
+        <v>1.452632769681757e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.898675657360111e-05</v>
+        <v>1.645668128389433e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>6.96305197693791e-05</v>
+        <v>1.472647836967414e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>6.96305197693791e-05</v>
+        <v>1.472647836967414e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>7.423621472630694e-05</v>
+        <v>1.556660574137124e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>9.100283905124123e-05</v>
+        <v>1.860317190402809e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>6.963037919083633e-05</v>
+        <v>1.472633779113139e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.416914519639058e-05</v>
+        <v>1.738575696104838e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.139427677428359e-05</v>
+        <v>1.320105662527943e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.786641830038069e-05</v>
+        <v>1.617725563957044e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.265219437723896e-05</v>
+        <v>6.37541427971543e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.338496427316891e-05</v>
+        <v>4.805259243399134e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.367411536144173e-05</v>
+        <v>4.961656492841272e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.280646112070142e-05</v>
+        <v>4.725444101698585e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.299678844881565e-05</v>
+        <v>4.758941711265189e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.27011060456872e-05</v>
+        <v>6.496426662729923e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.452235086658855e-05</v>
+        <v>6.902606046929978e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.296711213129726e-05</v>
+        <v>4.753602842690882e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.348523704018257e-05</v>
+        <v>6.705389183428346e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.347242115468752e-05</v>
+        <v>4.766810081932416e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.354284421198563e-05</v>
+        <v>4.85630666135668e-06</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.603529461787214e-05</v>
+        <v>6.970839918840482e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.607380751766463e-05</v>
+        <v>7.038495642329368e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.622914241132856e-05</v>
+        <v>7.171341241647952e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.56869102579539e-05</v>
+        <v>6.992403137571262e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.56869102579539e-05</v>
+        <v>6.992403137571262e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.608420628632038e-05</v>
+        <v>7.091852301854973e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.627563955311888e-05</v>
+        <v>7.211184854087254e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5571704345778e-05</v>
+        <v>6.97201106041882e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.625781815624247e-05</v>
+        <v>7.193363457210824e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>2.604383330794904e-05</v>
+        <v>6.979378608917359e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.613740384352883e-05</v>
+        <v>7.072949144497165e-06</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.281869628143552e-05</v>
+        <v>1.344471857654826e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.752597664612962e-05</v>
+        <v>1.961407734079711e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001047248349404734</v>
+        <v>2.098658305191813e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.756147811961687e-05</v>
+        <v>1.788232702221575e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.352362596133524e-05</v>
+        <v>1.365166506528249e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.740936566339613e-05</v>
+        <v>1.964508028419934e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.760079893026888e-05</v>
+        <v>1.976441283644467e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.689686372285377e-05</v>
+        <v>1.95252390427632e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.758976597871091e-05</v>
+        <v>1.974778620593779e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.218560408819573e-05</v>
+        <v>1.334033023177329e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001335443174876242</v>
+        <v>2.597656584342673e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.027869757700977e-05</v>
+        <v>1.475767879745493e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>8.741473249468317e-05</v>
+        <v>1.783449837978535e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>8.757814419197996e-05</v>
+        <v>1.796876549653562e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001066429445936031</v>
+        <v>2.124066510343984e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>8.691276580708899e-05</v>
+        <v>1.776815365582954e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>8.742513126333889e-05</v>
+        <v>1.788785503931097e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>8.761656453013748e-05</v>
+        <v>1.800718759154324e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>8.69126293227965e-05</v>
+        <v>1.776801379787481e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>8.759874313326105e-05</v>
+        <v>1.798936619466683e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>7.747838777744318e-05</v>
+        <v>1.596112327379068e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.747832882054724e-05</v>
+        <v>1.786895188195315e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.973075135845353e-06</v>
+        <v>4.973075135845317e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.762065562019078e-06</v>
+        <v>4.762065562019087e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.059782200356388e-06</v>
+        <v>6.059782200356419e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.347276202773346e-06</v>
+        <v>5.34727620277325e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.347276202773346e-06</v>
+        <v>5.347276202773265e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.835946937938958e-06</v>
+        <v>8.835946937938938e-06</v>
       </c>
       <c r="H2" t="n">
         <v>2.936615702215688e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>5.269441409429348e-06</v>
+        <v>5.269441409429334e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.947821823057943e-06</v>
+        <v>5.947821823057894e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.306943960569163e-06</v>
+        <v>5.306943960569189e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.754531702454684e-05</v>
+        <v>1.754531702454682e-05</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.569082746264596e-06</v>
+        <v>5.569082746264453e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.359704468880016e-06</v>
+        <v>5.359704468880011e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.819020981142533e-06</v>
+        <v>6.819020981142428e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.989499209152501e-06</v>
+        <v>5.98949920915254e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.989499209152501e-06</v>
+        <v>5.989499209152402e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.001218551015538e-05</v>
+        <v>1.001218551015523e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.363787718130028e-05</v>
+        <v>3.363787718130027e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.923103593567139e-06</v>
+        <v>5.923103593567014e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.572774201065391e-06</v>
+        <v>6.572774201065318e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.909896074502785e-06</v>
+        <v>5.909896074502773e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.00298028375154e-05</v>
+        <v>2.002980283751539e-05</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.174557478616951e-05</v>
+        <v>4.528454486587389e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.14633241701821e-05</v>
+        <v>4.498218563177349e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.239157608833692e-05</v>
+        <v>5.174455788754685e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.152692536108904e-05</v>
+        <v>4.640682923515113e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.152692536108905e-05</v>
+        <v>4.640682923515115e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.394719167635944e-05</v>
+        <v>6.808101467878207e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>2.624170830855889e-05</v>
+        <v>1.902458800897663e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.131760769182631e-05</v>
+        <v>4.603333319552839e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.186012617675812e-05</v>
+        <v>4.643005877175927e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.177305825212225e-05</v>
+        <v>4.555937952539928e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.921777921870854e-05</v>
+        <v>1.200065891912652e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5052705670854e-05</v>
+        <v>1.039050949052763e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>6.550390232879537e-05</v>
+        <v>1.400936026755618e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000124533248384158</v>
+        <v>2.491139000587249e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.963221186179533e-05</v>
+        <v>1.662721328268966e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>7.963221186179533e-05</v>
+        <v>1.662721328268966e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002921227385136376</v>
+        <v>5.576699744595011e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001659454783579751</v>
+        <v>0.0003064700876991533</v>
       </c>
       <c r="I5" t="n">
-        <v>7.963159330066543e-05</v>
+        <v>1.662659472155963e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.583238518599405e-05</v>
+        <v>1.59021234017928e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.474795783835852e-05</v>
+        <v>1.387952022919662e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009055865526726476</v>
+        <v>0.0001680015622017125</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.507885964884718e-05</v>
+        <v>4.964618344060191e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.380205409724093e-05</v>
+        <v>4.909835028109313e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.474500334389077e-05</v>
+        <v>5.588658983487674e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.335612870795869e-05</v>
+        <v>4.962622710819713e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.380106143954903e-05</v>
+        <v>5.040930871155277e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.728047653903707e-05</v>
+        <v>9.154759590993741e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.134087964939226e-05</v>
+        <v>2.168204215056356e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.379581144089535e-05</v>
+        <v>6.949991442668553e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.587779928076755e-05</v>
+        <v>7.110116330113097e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.402598858710257e-05</v>
+        <v>4.95245368934779e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>2.195201683765232e-05</v>
+        <v>1.248188473745288e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.828758856098309e-05</v>
+        <v>7.43984889517876e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.826688393175018e-05</v>
+        <v>7.455645065188198e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.892506814072746e-05</v>
+        <v>8.084350374207755e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.79821725351672e-05</v>
+        <v>7.536806410459871e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.79821725351672e-05</v>
+        <v>7.536806410459871e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.048920545117301e-05</v>
+        <v>9.719495876469641e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>4.278372208337247e-05</v>
+        <v>2.19359824175681e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.785962146663985e-05</v>
+        <v>7.514727728144323e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84021399515716e-05</v>
+        <v>7.55440028576723e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>2.831507202693574e-05</v>
+        <v>7.46733236113147e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>3.575979299352221e-05</v>
+        <v>1.491205332771784e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.796427035094331e-05</v>
+        <v>1.442294485237304e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001058369268231897</v>
+        <v>2.110797254010497e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001141984296294402</v>
+        <v>2.309246191489825e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>9.508707605375857e-05</v>
+        <v>1.934726936573577e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.88116351542482e-05</v>
+        <v>1.472279179248019e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000107924542147674</v>
+        <v>2.334811506120583e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001202190587798828</v>
+        <v>3.556460160230575e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001052949581631408</v>
+        <v>2.114334691288045e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001058448973074167</v>
+        <v>2.118432550654091e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.729036741659459e-05</v>
+        <v>1.43269843125415e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001526372020688714</v>
+        <v>3.548247721351647e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.783744298252855e-05</v>
+        <v>1.792062321657971e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001097473654087502</v>
+        <v>2.179620972743434e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001104140599326216</v>
+        <v>2.242641285186738e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001346481589602548</v>
+        <v>2.631001991955071e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001093406968247385</v>
+        <v>2.185590660783494e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001119696869281729</v>
+        <v>2.406006053871588e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001242642035603724</v>
+        <v>3.62765470798143e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001093401029436397</v>
+        <v>2.185529239039049e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001098826214285716</v>
+        <v>2.189496494801344e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>9.657333100714385e-05</v>
+        <v>1.957151849689039e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001172402744705221</v>
+        <v>2.925261798996405e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.646300764181551e-06</v>
+        <v>4.646300764181465e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.689611782809454e-06</v>
+        <v>4.689611782809457e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.976395260888997e-06</v>
+        <v>4.976395260888956e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.161441005383269e-06</v>
+        <v>5.161441005383273e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.161441005383269e-06</v>
+        <v>5.161441005383271e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.863194217245548e-06</v>
+        <v>4.863194217245482e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.061681237326752e-06</v>
+        <v>5.061681237326755e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.895415675501434e-06</v>
+        <v>4.895415675501537e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.894825990441732e-06</v>
+        <v>5.894825990441809e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.164777358935689e-06</v>
+        <v>5.164777358935656e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.76701960852271e-06</v>
+        <v>4.767019608522717e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.20324359246664e-06</v>
+        <v>5.203243592466696e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.255708731832419e-06</v>
+        <v>5.255708731832425e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.582920642549347e-06</v>
+        <v>5.582920642549314e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.757606204364205e-06</v>
+        <v>5.757606204364122e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.757606204364205e-06</v>
+        <v>5.757606204364124e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.452715992833778e-06</v>
+        <v>5.452715992833762e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.692282641138246e-06</v>
+        <v>5.692282641138244e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.505865301413003e-06</v>
+        <v>5.505865301412946e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.508621114451786e-06</v>
+        <v>6.508621114451742e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.727904929194654e-06</v>
+        <v>5.727904929194583e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.342539804039139e-06</v>
+        <v>5.342539804039136e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.112668493663714e-05</v>
+        <v>4.353951532090071e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.106887906348966e-05</v>
+        <v>4.387696582667442e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.132291212763943e-05</v>
+        <v>4.550178723092346e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.120978284381595e-05</v>
+        <v>4.496482891364583e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.120978284381596e-05</v>
+        <v>4.496482891364584e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.116873919742022e-05</v>
+        <v>4.467594671118812e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.137378059514871e-05</v>
+        <v>4.601047190601618e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.072146294088933e-05</v>
+        <v>4.410434735687242e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.135168275406877e-05</v>
+        <v>4.578949349521655e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.115116158138331e-05</v>
+        <v>4.378428176836273e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.119886873027039e-05</v>
+        <v>4.426135325723313e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.566181374061387e-05</v>
+        <v>1.043213416865469e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>6.774249568082533e-05</v>
+        <v>1.436225305327036e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.94432727441426e-05</v>
+        <v>1.653936212663227e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.569773654590476e-05</v>
+        <v>1.584636268143159e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>7.569773654590476e-05</v>
+        <v>1.584636268143159e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>7.454336499139742e-05</v>
+        <v>1.562152875042012e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>9.282672271029792e-05</v>
+        <v>1.893676492518827e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.5697610510434e-05</v>
+        <v>1.58462366459609e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.544475431265223e-05</v>
+        <v>1.761932987317169e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3849371184598e-05</v>
+        <v>1.365331301674509e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.583530037089243e-05</v>
+        <v>1.580214723283067e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.240826108302477e-05</v>
+        <v>4.734677835013392e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.321948853227818e-05</v>
+        <v>4.76620384712325e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.352625651240545e-05</v>
+        <v>4.937965189498159e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.276784790841547e-05</v>
+        <v>4.770702341248203e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29285608223051e-05</v>
+        <v>4.798987813939514e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.333195683938805e-05</v>
+        <v>4.84832097404213e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.411144016908767e-05</v>
+        <v>6.842875263467316e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.288468058285711e-05</v>
+        <v>6.39599212669253e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.37643279269529e-05</v>
+        <v>6.668233978233579e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.335378887661501e-05</v>
+        <v>4.766090578696465e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.336988838920567e-05</v>
+        <v>4.808234783625506e-06</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.561038574605332e-05</v>
+        <v>6.903082860734603e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.562902195942575e-05</v>
+        <v>6.950281718466554e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.579854226237374e-05</v>
+        <v>7.097889613000558e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.537399571085591e-05</v>
+        <v>6.989384342455573e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.537399571085591e-05</v>
+        <v>6.989384342455573e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.565244000683639e-05</v>
+        <v>7.016725999763351e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.585748140456484e-05</v>
+        <v>7.150178519246163e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.520516375030555e-05</v>
+        <v>6.95956606433177e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.583538356348493e-05</v>
+        <v>7.12808067816619e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>2.563486239079957e-05</v>
+        <v>6.927559505480792e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.568256953968653e-05</v>
+        <v>6.975266654367847e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.204075268763732e-05</v>
+        <v>1.331482740771066e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.632611587249637e-05</v>
+        <v>1.939297017974493e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001033940426054135</v>
+        <v>2.075469759937465e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.65584142276041e-05</v>
+        <v>1.775784194305319e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.282166773083714e-05</v>
+        <v>1.358017458225935e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.617138164531469e-05</v>
+        <v>1.942805966088338e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.637642304308227e-05</v>
+        <v>1.956151218037304e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.572410538878378e-05</v>
+        <v>1.937089972545178e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.636102458444474e-05</v>
+        <v>1.954059343059661e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.143201655625683e-05</v>
+        <v>1.32278586044624e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001318098778901534</v>
+        <v>2.565367282283908e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.368209568478451e-05</v>
+        <v>1.53637037641065e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.175737582291075e-05</v>
+        <v>1.858887193537498e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.193496878079421e-05</v>
+        <v>1.873790061716994e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001121706248860271</v>
+        <v>2.226559099450995e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>9.133363982533594e-05</v>
+        <v>1.859828164370002e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.178079387032146e-05</v>
+        <v>1.865531621667177e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>9.198583526804992e-05</v>
+        <v>1.878876873615461e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>9.133351761379055e-05</v>
+        <v>1.85981562812402e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.196373742697014e-05</v>
+        <v>1.876667089507462e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.902667794028076e-05</v>
+        <v>1.672482196787152e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.181092340317175e-05</v>
+        <v>1.861385687127629e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.62161286844689e-06</v>
+        <v>4.621612868446889e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.683333964114169e-06</v>
+        <v>4.683333964114168e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.931998547703127e-06</v>
+        <v>4.93199854770313e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.022727082746456e-06</v>
+        <v>5.022727082746475e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.022727082746457e-06</v>
+        <v>5.022727082746475e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.845819620255863e-06</v>
+        <v>4.845819620255859e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.037013822680729e-06</v>
+        <v>5.037013822680733e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.801665917377424e-06</v>
+        <v>4.801665917377414e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.866346723968646e-06</v>
+        <v>5.866346723968653e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.074407555990008e-06</v>
+        <v>5.074407555989991e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.779908122525931e-06</v>
+        <v>4.779908122525926e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.179189216055297e-06</v>
+        <v>5.179189216055296e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.254521519311678e-06</v>
+        <v>5.254521519311679e-06</v>
       </c>
       <c r="D3" t="n">
         <v>5.536197043399747e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.609149239556907e-06</v>
+        <v>5.609149239556915e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.609149239556907e-06</v>
+        <v>5.609149239556914e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.437073424924339e-06</v>
+        <v>5.437073424924347e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.667698441808721e-06</v>
+        <v>5.667698441808717e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.401938745163686e-06</v>
+        <v>5.401938745163694e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.486239893244257e-06</v>
+        <v>6.486239893244253e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.637702792717934e-06</v>
+        <v>5.63770279271791e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.361706614703085e-06</v>
+        <v>5.361706614703077e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.123632277383436e-05</v>
+        <v>4.357095473428562e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.124221634719959e-05</v>
+        <v>4.417126887538958e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.14208339079953e-05</v>
+        <v>4.5416066075895e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.113467454616259e-05</v>
+        <v>4.433273023124513e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.113467454616262e-05</v>
+        <v>4.433273023124512e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.128209050756373e-05</v>
+        <v>4.47497447937606e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.148343501703644e-05</v>
+        <v>4.604207716630655e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.078619514073617e-05</v>
+        <v>4.371827296051756e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.148294691953795e-05</v>
+        <v>4.603719619132191e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.125895576611053e-05</v>
+        <v>4.379728465704774e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.133083722807032e-05</v>
+        <v>4.451609927664498e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.413554997276006e-05</v>
+        <v>1.014735942906434e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>6.801298430845858e-05</v>
+        <v>1.44087819945797e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.693841218380296e-05</v>
+        <v>1.607270032164921e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>7.043826821879455e-05</v>
+        <v>1.487070545295102e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>7.043826821879455e-05</v>
+        <v>1.487070545295102e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>7.348027663165256e-05</v>
+        <v>1.542185517789873e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>9.120230919388428e-05</v>
+        <v>1.863472949573004e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>7.043813065562689e-05</v>
+        <v>1.487056788978426e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>8.602994617395334e-05</v>
+        <v>1.772399141681572e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>6.224479613647815e-05</v>
+        <v>1.335323632226558e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.654548424897563e-05</v>
+        <v>1.592938774115031e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.266258724723166e-05</v>
+        <v>4.746688658754913e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.340819065223646e-05</v>
+        <v>4.798338363159833e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.367504534482093e-05</v>
+        <v>4.938347818321022e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.284809828423539e-05</v>
+        <v>4.734835599391278e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.303447807532142e-05</v>
+        <v>4.76763844244463e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.270835498096112e-05</v>
+        <v>6.485997015797063e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.45068743509e-05</v>
+        <v>6.896333026970537e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.299979279663059e-05</v>
+        <v>6.382849832472754e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.35248051010541e-05</v>
+        <v>5.038102361371106e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.351309671636638e-05</v>
+        <v>4.776457270800063e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.355477121303922e-05</v>
+        <v>4.84302230689766e-06</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.550159603562328e-05</v>
+        <v>6.867783553898968e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.553785245741746e-05</v>
+        <v>6.933158829303962e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.567803321388435e-05</v>
+        <v>7.050873671829234e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.518711882371308e-05</v>
+        <v>6.906503202571953e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.518711882371308e-05</v>
+        <v>6.906503202571953e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.554736376935267e-05</v>
+        <v>6.985662559846488e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.574870827882537e-05</v>
+        <v>7.114895797101078e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.50514684025251e-05</v>
+        <v>6.8825153765222e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.574822018132684e-05</v>
+        <v>7.114407699602614e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>2.552422902789942e-05</v>
+        <v>6.890416546175187e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.559611048985922e-05</v>
+        <v>6.962298008134922e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.177957513711413e-05</v>
+        <v>1.325270784116403e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.583479933437285e-05</v>
+        <v>1.93054214126077e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001028603159979904</v>
+        <v>2.063495536822518e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.606698233788168e-05</v>
+        <v>1.762135912300602e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.24889487315582e-05</v>
+        <v>1.347162523077883e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.569788113039977e-05</v>
+        <v>1.933215354849003e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.589922563993974e-05</v>
+        <v>1.946138678575646e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.52019857635722e-05</v>
+        <v>1.922900636516568e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.59053944663379e-05</v>
+        <v>1.946207030685743e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.117300834107247e-05</v>
+        <v>1.316460167129631e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001311293264384454</v>
+        <v>2.55361439144418e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.978823019604539e-05</v>
+        <v>1.466223112389822e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>8.678246163201276e-05</v>
+        <v>1.771220998562525e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>8.693071831580549e-05</v>
+        <v>1.783134619135227e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000105865355863592</v>
+        <v>2.110587284464981e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>8.629621141378969e-05</v>
+        <v>1.766170344014728e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>8.679197294394759e-05</v>
+        <v>1.776471371616779e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>8.699331745342032e-05</v>
+        <v>1.789394695342233e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>8.629607757711985e-05</v>
+        <v>1.766156653284344e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>8.699282935592173e-05</v>
+        <v>1.789345885592387e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>7.654468801375773e-05</v>
+        <v>1.587001727902934e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.684071966445408e-05</v>
+        <v>1.774134916445619e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001177616524622835</v>
+        <v>0.0001177616524622836</v>
       </c>
       <c r="C2" t="n">
-        <v>2.441663541404655e-05</v>
+        <v>2.441663541404659e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.653925512676398e-05</v>
+        <v>2.653925512676392e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>2.485643263827367e-05</v>
+        <v>2.485643263827365e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.355100001499699e-05</v>
+        <v>2.355100001499694e-05</v>
       </c>
       <c r="G2" t="n">
         <v>4.927023047624872e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.432291544674061e-05</v>
+        <v>8.432291544674067e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.329145880576127e-05</v>
+        <v>2.329145880576128e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.273961857975727e-05</v>
+        <v>3.273961857975723e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7493139739823e-05</v>
+        <v>5.749313973982298e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>9.21158456901906e-05</v>
+        <v>9.211584569019067e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4917,28 +4917,28 @@
         <v>2.787026576728992e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.048624016039807e-05</v>
+        <v>3.048624016039809e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8316693822435e-05</v>
+        <v>2.831669382243498e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.701126119915831e-05</v>
+        <v>2.701126119915825e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.663157051966364e-05</v>
+        <v>5.663157051966369e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.696133985671492e-05</v>
+        <v>9.696133985671518e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.674627914678782e-05</v>
+        <v>2.674627914678787e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.718328099847723e-05</v>
+        <v>3.71832809984772e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.572266298281369e-05</v>
+        <v>6.572266298281355e-05</v>
       </c>
       <c r="L3" t="n">
         <v>0.0001059116777123292</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.569465198096075e-05</v>
+        <v>7.28477486467677e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.728537668932444e-05</v>
+        <v>1.629673419349565e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.146680218586391e-05</v>
+        <v>1.861989885167093e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.747990432928849e-05</v>
+        <v>1.633097382815279e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.747990432928852e-05</v>
+        <v>1.633097382815279e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.483696311759604e-05</v>
+        <v>3.21074309371531e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>6.580902399486127e-05</v>
+        <v>5.29621206606683e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.862317191359295e-05</v>
+        <v>1.652913636662361e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.343244537032059e-05</v>
+        <v>2.058554203612757e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.841531302241268e-05</v>
+        <v>3.556840968821966e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.044162288419758e-05</v>
+        <v>5.759471955000449e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006264527358142413</v>
+        <v>0.00116032229903859</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009684469163804557</v>
+        <v>0.0001819411642815728</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001191225219801311</v>
+        <v>0.0002227373792459579</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009684469197423561</v>
+        <v>0.0001819411676434771</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009684469197423561</v>
+        <v>0.0001819411676434771</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002557955895769566</v>
+        <v>0.0004744163606872031</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005106351526036205</v>
+        <v>0.00094009759621291</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009684432151849881</v>
+        <v>0.0001819374630861067</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001468089890021102</v>
+        <v>0.0002730852509264683</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002835191065918086</v>
+        <v>0.0005260409395401814</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001081114558633828</v>
+        <v>0.0002354731552780864</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001193271110183958</v>
+        <v>7.876706140528185e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.55652396263485e-05</v>
+        <v>1.77539900625156e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.924589526802168e-05</v>
+        <v>1.998901922671196e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.512645431341533e-05</v>
+        <v>1.767676661806677e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.781611138041246e-05</v>
+        <v>1.815014625929321e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>5.448575615023931e-05</v>
+        <v>3.802674369566724e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>7.646797032288771e-05</v>
+        <v>5.913717348770774e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>6.225563095102803e-05</v>
+        <v>2.244844912513777e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>6.738813590275574e-05</v>
+        <v>2.656174353745354e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.943751534596642e-05</v>
+        <v>3.750831728665351e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.125731047598619e-05</v>
+        <v>5.949828055584461e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001111884624775113</v>
+        <v>7.73346592698479e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>5.412068360560954e-05</v>
+        <v>2.101974818516971e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>5.695184207559524e-05</v>
+        <v>2.310526584795926e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>5.405952294566184e-05</v>
+        <v>2.100898667928621e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>5.405952294566186e-05</v>
+        <v>2.100898667928621e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>7.03307736141465e-05</v>
+        <v>3.659434156023321e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>9.130283449141195e-05</v>
+        <v>5.744903128374844e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>5.411698241014348e-05</v>
+        <v>2.10160469897037e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.892625586687119e-05</v>
+        <v>2.507245265920769e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.390912351896322e-05</v>
+        <v>4.005532031129976e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.59354333807481e-05</v>
+        <v>6.208163017308454e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001592084110931786</v>
+        <v>8.578617018040993e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001525690149587796</v>
+        <v>3.834665440943999e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001659109132699897</v>
+        <v>4.228206227426125e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001387686709312629</v>
+        <v>3.591779664396708e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001037090719695729</v>
+        <v>2.974730726014504e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001688166378442997</v>
+        <v>5.392785357081673e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001897886987215624</v>
+        <v>7.478254329433152e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000152602846640297</v>
+        <v>3.834955900028731e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001574220380937439</v>
+        <v>4.240771023720446e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001209916418431138</v>
+        <v>4.834184349144886e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002471371663596545</v>
+        <v>8.8693135033175e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0002203355805782204</v>
+        <v>9.654455195148188e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002021382877839713</v>
+        <v>4.707084637940077e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002049782291218868</v>
+        <v>4.915790982693763e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000246993940139528</v>
+        <v>5.496544392141002e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000202138228076745</v>
+        <v>4.707083864113789e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002183483777925084</v>
+        <v>6.264543975446428e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002393204386697736</v>
+        <v>8.350012947797955e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002021345865885055</v>
+        <v>4.706714518393481e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000206943860045233</v>
+        <v>5.112355085343878e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001994050205647675</v>
+        <v>6.214259807167906e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002439530375591098</v>
+        <v>8.813272836731567e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,13 +5267,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.741807225470617e-05</v>
+        <v>9.741807225470612e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>3.477311491123018e-05</v>
+        <v>3.477311491123015e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.672015955729943e-05</v>
+        <v>2.672015955729919e-05</v>
       </c>
       <c r="E2" t="n">
         <v>3.519796121020251e-05</v>
@@ -5282,22 +5282,22 @@
         <v>3.392904819519584e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>4.990874819338614e-05</v>
+        <v>4.990874819338606e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>7.716959063423321e-05</v>
+        <v>7.716959063423322e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.335854020528744e-05</v>
+        <v>3.335854020528745e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.096312941795248e-05</v>
+        <v>3.096312941795246e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.922106971970889e-05</v>
+        <v>5.92210697197089e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>8.857255741694448e-05</v>
+        <v>8.857255741694462e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001119835014687705</v>
+        <v>0.0001119835014687704</v>
       </c>
       <c r="C3" t="n">
-        <v>3.971149174454209e-05</v>
+        <v>3.971149174454206e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.066625683825717e-05</v>
+        <v>3.066625683825665e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.014257906025162e-05</v>
+        <v>4.014257906025163e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8873666045245e-05</v>
+        <v>3.887366604524497e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.733793727142181e-05</v>
+        <v>5.733793727142173e-05</v>
       </c>
       <c r="H3" t="n">
         <v>8.870469058329019e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.830496691162236e-05</v>
+        <v>3.83049669116224e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.509271332137982e-05</v>
+        <v>3.50927133213798e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.765755704891528e-05</v>
+        <v>6.765755704891529e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000101808305134003</v>
+        <v>0.0001018083051340031</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.548033327546708e-05</v>
+        <v>6.109965944847591e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.584678921292031e-05</v>
+        <v>2.275020300609103e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.345341990153996e-05</v>
+        <v>1.90727460745488e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.602177671395672e-05</v>
+        <v>2.278100277345757e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>3.602177671395674e-05</v>
+        <v>2.278100277345757e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>4.711478389454903e-05</v>
+        <v>3.283568402632554e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>6.343756501475323e-05</v>
+        <v>4.905689118776225e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.661156867906278e-05</v>
+        <v>2.288281080573286e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.417958388590191e-05</v>
+        <v>1.979891005891074e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.122452214805236e-05</v>
+        <v>3.684384832106125e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.021535754659412e-05</v>
+        <v>5.583468371960315e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004856791379195763</v>
+        <v>0.0009026103989706339</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001387715666759884</v>
+        <v>0.0002606791241651143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001095455536851767</v>
+        <v>0.0002059851176449821</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001387715669147446</v>
+        <v>0.0002606791265526765</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001387715669147446</v>
+        <v>0.0002606791265526765</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002379483311359699</v>
+        <v>0.0004433325426358721</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004322594314941307</v>
+        <v>0.0007986684751129891</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001387713247602521</v>
+        <v>0.0002606767050077501</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001249024420411601</v>
+        <v>0.0002336116001288676</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002552984867694045</v>
+        <v>0.0004771536667512911</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005226573160882404</v>
+        <v>0.000287872034535442</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.541980335908999e-05</v>
+        <v>6.684775822116267e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>4.51084206983107e-05</v>
+        <v>2.438025013868714e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>4.155599572393024e-05</v>
+        <v>2.049879941156003e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>4.462164662720186e-05</v>
+        <v>2.429457986998723e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>4.64976850583263e-05</v>
+        <v>2.462476263207602e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>5.705425397817174e-05</v>
+        <v>3.858378279901226e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.741531996519587e-05</v>
+        <v>5.50369760266364e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.655103876268553e-05</v>
+        <v>2.863090957841955e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>4.48625627246706e-05</v>
+        <v>2.560167174749483e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.249586779622579e-05</v>
+        <v>3.882760514439064e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.127350471625991e-05</v>
+        <v>5.778091761091848e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.956940054923104e-05</v>
+        <v>6.53393352656854e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>6.070305511019027e-05</v>
+        <v>2.712490578030578e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>5.753423824088629e-05</v>
+        <v>2.331097007930846e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>6.068800102692832e-05</v>
+        <v>2.712225822901706e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>6.068800102692832e-05</v>
+        <v>2.712225822901706e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>7.120385116831292e-05</v>
+        <v>3.707535984353495e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.752663228851731e-05</v>
+        <v>5.32965670049716e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.070063595282672e-05</v>
+        <v>2.712248662294218e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.826865115966576e-05</v>
+        <v>2.403858587612007e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.531358942181625e-05</v>
+        <v>4.108352413827057e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.430442482035814e-05</v>
+        <v>6.00743595368126e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001442069299387429</v>
+        <v>7.319554039566983e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001526248541676773</v>
+        <v>4.330314232678663e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001592626138951453</v>
+        <v>4.121516409744226e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001396916975811019</v>
+        <v>4.102690874720776e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001068351968630041</v>
+        <v>3.524416465215698e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001631203711873958</v>
+        <v>5.325266727923504e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001794431523075948</v>
+        <v>6.947387444067081e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001526171559719095</v>
+        <v>4.329979405864235e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001501944628513749</v>
+        <v>4.02175286461936e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001190728872876956</v>
+        <v>4.878516052093322e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002356078039533261</v>
+        <v>8.494375412945752e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001936952734078345</v>
+        <v>8.190548879903409e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000189093515015816</v>
+        <v>4.972162660125308e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001859329615142706</v>
+        <v>4.590914525297367e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002286340754643837</v>
+        <v>5.668076716984335e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001890934678736254</v>
+        <v>4.972162027157875e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001995943110739386</v>
+        <v>5.967208066448238e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0002159170921941429</v>
+        <v>7.589328782591898e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001890910958584525</v>
+        <v>4.971920744388958e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001866591110652913</v>
+        <v>4.663530669706744e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001605588142873138</v>
+        <v>5.608668363330198e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002226948847259835</v>
+        <v>8.267108035775988e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.427848138961915e-05</v>
+        <v>8.427848138961908e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>5.749843207677302e-05</v>
+        <v>5.749843207677306e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.621875270823032e-05</v>
+        <v>2.621875270823039e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.789670359564652e-05</v>
+        <v>5.789670359564667e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>5.669406619235064e-05</v>
+        <v>5.669406619235078e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>4.741388824073079e-05</v>
+        <v>4.741388824073073e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>6.892493109744938e-05</v>
+        <v>6.892493109744947e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>5.536108621204425e-05</v>
+        <v>5.536108621204442e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.411636720874563e-05</v>
+        <v>3.411636720874567e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.835056040342767e-05</v>
+        <v>5.835056040342776e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>8.435868435779233e-05</v>
+        <v>8.435868435779243e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.681510049938324e-05</v>
+        <v>9.681510049938311e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.568853204671536e-05</v>
+        <v>6.568853204671545e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.003438547922274e-05</v>
+        <v>3.003438547922281e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.609180428587251e-05</v>
+        <v>6.609180428587258e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.488916688257646e-05</v>
+        <v>6.488916688257671e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.441318190069658e-05</v>
+        <v>5.441318190069683e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.916579631672207e-05</v>
+        <v>7.916579631672203e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.357534255841462e-05</v>
+        <v>6.357534255841486e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.860074137955394e-05</v>
+        <v>3.86007413795537e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.65646140527325e-05</v>
+        <v>6.656461405273248e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.690637032508773e-05</v>
+        <v>9.690637032508762e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.215680307014233e-05</v>
+        <v>5.41369701732989e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>5.501886048778093e-05</v>
+        <v>3.696278218980335e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>3.764275456845398e-05</v>
+        <v>1.962292167161051e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>5.514407525006675e-05</v>
+        <v>3.698481970963898e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.514407525006676e-05</v>
+        <v>3.698481970963898e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>5.016858445668906e-05</v>
+        <v>3.220954633904546e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>6.302519555653326e-05</v>
+        <v>4.500536265968994e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.450053349228152e-05</v>
+        <v>3.687231036809419e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>4.028935579126619e-05</v>
+        <v>2.226952289442275e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>5.504988096767877e-05</v>
+        <v>3.703004807083523e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.219808778588558e-05</v>
+        <v>5.417825488904211e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004009210852777646</v>
+        <v>0.0007470584791671507</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002453654311630376</v>
+        <v>0.0004591226193033837</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001026441318709264</v>
+        <v>0.0001936514680174012</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002453654311292744</v>
+        <v>0.0004591226189657525</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002453654311292744</v>
+        <v>0.0004591226189657525</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00217773878763423</v>
+        <v>0.0004066619000692809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003646201716311546</v>
+        <v>0.0006756444268953894</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002453655226350041</v>
+        <v>0.0004591235340230465</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0013916695400902</v>
+        <v>0.000260112434042258</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002351026625306375</v>
+        <v>0.0004411219528848325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004869376862815384</v>
+        <v>0.0008984817147192882</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.401497279120837e-05</v>
+        <v>5.622400803289763e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>6.749126054069115e-05</v>
+        <v>3.915792458722099e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>7.192756421621176e-05</v>
+        <v>2.565704813691936e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>6.683757943461583e-05</v>
+        <v>3.904287643496789e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>6.703022411740028e-05</v>
+        <v>3.907678189895422e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>6.202675417775502e-05</v>
+        <v>3.42965841986442e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.853204117088155e-05</v>
+        <v>5.125456745395323e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.876096525142955e-05</v>
+        <v>4.290214632503105e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>7.481031292409694e-05</v>
+        <v>2.453236716661043e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>6.804202441391681e-05</v>
+        <v>3.931666530498286e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>8.519463926177635e-05</v>
+        <v>5.646564793640442e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.682345566321181e-05</v>
+        <v>5.847830100615513e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>7.916627136568666e-05</v>
+        <v>4.121272648128606e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>6.230099038128283e-05</v>
+        <v>2.396277115115245e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>7.926290903807377e-05</v>
+        <v>4.122973443332672e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>7.926290903807377e-05</v>
+        <v>4.122973443332672e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>7.483523704975828e-05</v>
+        <v>3.655087717190161e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.769184814960262e-05</v>
+        <v>4.93466934925462e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>7.916718608535086e-05</v>
+        <v>4.121364120095048e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>6.495600838433551e-05</v>
+        <v>2.661085372727898e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.971653356074796e-05</v>
+        <v>4.13713789036915e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>9.686474037895483e-05</v>
+        <v>5.851958572189843e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001408402599503849</v>
+        <v>6.622525851871992e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001705951660617883</v>
+        <v>5.730421186060648e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001634339131694138</v>
+        <v>4.176216546541563e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001576449130107222</v>
+        <v>5.502496705776205e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001247450757008976</v>
+        <v>4.923459572260864e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001661518248228117</v>
+        <v>5.262259653287268e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001790084359226557</v>
+        <v>6.541841285351712e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001704837738584042</v>
+        <v>5.728536056192159e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001562818919147883</v>
+        <v>4.268420914154342e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000122854720086444</v>
+        <v>4.896369969107417e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002375899071414782</v>
+        <v>8.328721493789641e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001852932881541148</v>
+        <v>7.404899144018268e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002005172056315629</v>
+        <v>6.257049079635093e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001836603492977792</v>
+        <v>4.532201820471846e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002384612613358979</v>
+        <v>6.924864428592043e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002005171690306237</v>
+        <v>6.25704840763785e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001961861713156344</v>
+        <v>5.790864148696662e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000209042782415479</v>
+        <v>7.070445780761109e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002005181203512273</v>
+        <v>6.25714055160154e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001863069426502117</v>
+        <v>4.796861804234395e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001820160316344397</v>
+        <v>5.937609046710079e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002182156746448311</v>
+        <v>7.987735003696333e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.474982453879925e-05</v>
+        <v>1.474982453879929e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>8.981860666573738e-06</v>
+        <v>8.981860666573743e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150061356632055e-05</v>
+        <v>1.150061356632056e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>9.322785319812072e-06</v>
+        <v>9.322785319812062e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.318001689061943e-06</v>
+        <v>8.318001689061926e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.573822936174602e-05</v>
+        <v>1.5738229361746e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86340108857399e-05</v>
+        <v>2.863401088573988e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>7.996985790602273e-06</v>
+        <v>7.996985790602259e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.955639136125945e-05</v>
+        <v>1.95563913612594e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.429597153220777e-05</v>
+        <v>1.429597153220776e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.155981074293444e-05</v>
+        <v>3.155981074293445e-05</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.684226219230019e-05</v>
+        <v>1.68422621923002e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.005657361383591e-05</v>
+        <v>1.00565736138359e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.310499650192448e-05</v>
+        <v>1.310499650192445e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.040248520493739e-05</v>
+        <v>1.040248520493738e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>9.397701574187269e-06</v>
+        <v>9.397701574187256e-06</v>
       </c>
       <c r="G3" t="n">
         <v>1.797913248613117e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.282263161860866e-05</v>
+        <v>3.282263161860864e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.083499158821303e-06</v>
+        <v>9.083499158821286e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.200857450062175e-05</v>
+        <v>2.20085745006217e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.615724653970875e-05</v>
+        <v>1.615724653970873e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>3.617691086313218e-05</v>
+        <v>3.617691086313219e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.823197278858477e-05</v>
+        <v>1.06783067897761e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.315387591959615e-05</v>
+        <v>6.481971657560941e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.630045454619423e-05</v>
+        <v>8.746788547385521e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.323268917735142e-05</v>
+        <v>6.495843973165345e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.323268917735142e-05</v>
+        <v>6.495843973165349e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.871684420446153e-05</v>
+        <v>1.124779754188914e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.648280064817773e-05</v>
+        <v>1.892913464936903e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.356199945033458e-05</v>
+        <v>6.552817569568555e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.965569628326362e-05</v>
+        <v>1.210203028445494e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.731712686796324e-05</v>
+        <v>9.763460869154545e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>2.822199103785145e-05</v>
+        <v>2.066832503904277e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0006147526118002582</v>
+        <v>0.0001156659386869445</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002458046111701856</v>
+        <v>4.742850083979166e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004254564881851455</v>
+        <v>8.075825007763929e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002458046126050335</v>
+        <v>4.742850227463946e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002458046126050335</v>
+        <v>4.742850227463946e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0006750398929778542</v>
+        <v>0.0001267606535000878</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001471748001370848</v>
+        <v>0.0002732958085982467</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002458034172029378</v>
+        <v>4.742730687254408e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0008184953550880853</v>
+        <v>0.0001526978094722705</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005203377862699324</v>
+        <v>9.829509644418319e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001442931963130741</v>
+        <v>0.0003337766901353727</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.243654489453845e-05</v>
+        <v>1.141831147641414e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.702067010826719e-05</v>
+        <v>7.162527431079363e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.037786490916841e-05</v>
+        <v>1.186960005175791e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.679529782691388e-05</v>
+        <v>7.122863092090755e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.771387400200952e-05</v>
+        <v>7.284532498031556e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.630767113669496e-05</v>
+        <v>1.198780222852719e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>4.495580012148067e-05</v>
+        <v>2.218038253905313e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.115282638256801e-05</v>
+        <v>7.292822256206614e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.737741494865807e-05</v>
+        <v>1.522105275266358e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.15682246560032e-05</v>
+        <v>1.051165407579541e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>3.291614402239067e-05</v>
+        <v>2.149449595984497e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.537004872340095e-05</v>
+        <v>1.369460813795962e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.070126935239823e-05</v>
+        <v>9.570312884999663e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.342982223039837e-05</v>
+        <v>1.176155724346962e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>3.070427385378376e-05</v>
+        <v>9.570842859555257e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>3.070427385378376e-05</v>
+        <v>9.570842859555257e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.585492013927769e-05</v>
+        <v>1.426409889007266e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.362087658299392e-05</v>
+        <v>2.194543599755256e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.070007538515077e-05</v>
+        <v>9.569118917752088e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.679377221807978e-05</v>
+        <v>1.511833163263844e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.44552028027794e-05</v>
+        <v>1.277976221733806e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>4.53600669726676e-05</v>
+        <v>2.368462638722635e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.581557833508957e-05</v>
+        <v>2.081302131104494e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001098828559365634</v>
+        <v>2.350627204828417e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001206263771592225</v>
+        <v>2.71081508277856e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>9.929012253645804e-05</v>
+        <v>2.164195216229738e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>7.238097961290679e-05</v>
+        <v>1.690594303341487e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001150150435840128</v>
+        <v>2.819628054085306e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000122781000027728</v>
+        <v>3.587761764833284e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001098601988298857</v>
+        <v>2.35013005685325e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001159615041906441</v>
+        <v>2.905185238430955e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.418158895795817e-05</v>
+        <v>1.977160614276348e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000164960820938289</v>
+        <v>4.47343589711155e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001054690758713328</v>
+        <v>2.603203684914398e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001258517853657798</v>
+        <v>2.631680361261222e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001285890475994077</v>
+        <v>2.85095808176643e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001547606464937077</v>
+        <v>3.140476432587245e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001258517641771908</v>
+        <v>2.631680106573513e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001310054361526591</v>
+        <v>3.101058961768518e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001387713925963754</v>
+        <v>3.869192672516506e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001258505913985321</v>
+        <v>2.631560964536458e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001319442882314611</v>
+        <v>3.186482236025093e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>9.8061422373261e-05</v>
+        <v>2.697162517871444e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001405105829860491</v>
+        <v>4.043111711483881e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.609181476329521e-06</v>
+        <v>4.609181476329582e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.670609126658847e-06</v>
+        <v>6.670609126658843e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.752379852030029e-06</v>
+        <v>5.752379852030127e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.967485575218021e-06</v>
+        <v>6.96748557521798e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.088666186825729e-06</v>
+        <v>6.088666186825708e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.348200482727331e-06</v>
+        <v>6.348200482727361e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.883287477215868e-06</v>
+        <v>5.883287477215858e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.689489369551276e-06</v>
+        <v>5.689489369551336e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.971802560979583e-06</v>
+        <v>9.97180256097961e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.199843295497795e-06</v>
+        <v>6.199843295497749e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.543658304939888e-06</v>
+        <v>5.54365830493989e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.15911247693303e-06</v>
+        <v>5.159112476933095e-06</v>
       </c>
       <c r="C3" t="n">
         <v>7.379839628622392e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.474027421818723e-06</v>
+        <v>6.474027421818794e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.68145834465839e-06</v>
+        <v>7.681458344658468e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.80263895626609e-06</v>
+        <v>6.802638956266114e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.159344570992433e-06</v>
+        <v>7.159344570992564e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>6.634879357603022e-06</v>
+        <v>6.634879357603021e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.414701972499426e-06</v>
+        <v>6.414701972499444e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.099640293146163e-05</v>
+        <v>1.09964029314616e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.857673788908389e-06</v>
+        <v>6.857673788908373e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>6.23437392266124e-06</v>
+        <v>6.234373922661241e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.075753573963513e-05</v>
+        <v>4.444834969288296e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.075485791378042e-05</v>
+        <v>4.979311399524974e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.143711873256471e-05</v>
+        <v>5.124417962217904e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.080459582532446e-05</v>
+        <v>4.98806602039235e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.080459582532446e-05</v>
+        <v>4.988066020392348e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.170325383967058e-05</v>
+        <v>5.463110398292016e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.151525746350735e-05</v>
+        <v>5.202556693160522e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.083898223645973e-05</v>
+        <v>4.993933316308552e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.263608032368284e-05</v>
+        <v>6.323379553336006e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.118455720067044e-05</v>
+        <v>4.871856430323616e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.131369276278905e-05</v>
+        <v>5.0009919924422e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.789903993845969e-05</v>
+        <v>1.626173964425029e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000140903704612589</v>
+        <v>2.788550829439568e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001461370961413017</v>
+        <v>2.883161385769561e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001409037055209422</v>
+        <v>2.78855092027489e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001409037055209422</v>
+        <v>2.78855092027489e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001740858626702283</v>
+        <v>3.404244939760971e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00016807086371041</v>
+        <v>3.275634324331232e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001409034813553955</v>
+        <v>2.788528503720206e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002546225618985531</v>
+        <v>4.891300007973681e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001176899305444162</v>
+        <v>2.361680203725144e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.193430292976755e-05</v>
+        <v>1.567021932401807e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.343704896819731e-05</v>
+        <v>6.638758275358274e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.341496636806074e-05</v>
+        <v>5.447490484941436e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.413649818563229e-05</v>
+        <v>5.599508455761945e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.325596902428432e-05</v>
+        <v>5.419507701071475e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.353537258849062e-05</v>
+        <v>5.468682728105326e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.438276706823274e-05</v>
+        <v>5.934704723963588e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.454614442704513e-05</v>
+        <v>5.678243380785157e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.351849546502192e-05</v>
+        <v>5.465527641980103e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.562706209663859e-05</v>
+        <v>8.521082432828972e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.383325971157916e-05</v>
+        <v>5.33802806971754e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.401127994991828e-05</v>
+        <v>5.475767334804345e-06</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.45770362923802e-05</v>
+        <v>6.877067053392145e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.465870604639844e-05</v>
+        <v>7.426388657606006e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.52485206655353e-05</v>
+        <v>7.555224689249148e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.467660503427249e-05</v>
+        <v>7.429539627937818e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.467660503427248e-05</v>
+        <v>7.429539627937818e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.552275439241563e-05</v>
+        <v>7.895342482395862e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.533475801625239e-05</v>
+        <v>7.634788777264345e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.465848278920479e-05</v>
+        <v>7.426165400412367e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.645558087642786e-05</v>
+        <v>8.75561163743982e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>2.500405775341551e-05</v>
+        <v>7.304088514427454e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.513319331553411e-05</v>
+        <v>7.433224076546028e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.02231070328139e-05</v>
+        <v>1.315077546971369e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.337664667282783e-05</v>
+        <v>1.952074614232303e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001007913839648322</v>
+        <v>2.085076855788208e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.433524522063053e-05</v>
+        <v>1.79294602438419e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.136754087121709e-05</v>
+        <v>1.388714430024886e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.420686606234186e-05</v>
+        <v>1.998374607080061e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.401886968617904e-05</v>
+        <v>1.972319236566915e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.334259445913104e-05</v>
+        <v>1.951456898881706e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.514618546870086e-05</v>
+        <v>2.084515798017137e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>6.003642992185918e-05</v>
+        <v>1.346978598266405e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001283283013328113</v>
+        <v>2.559556298917224e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.535960999321419e-05</v>
+        <v>1.581479997630887e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>9.400727754945709e-05</v>
+        <v>1.963173717600833e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>9.460519456359627e-05</v>
+        <v>1.97619992291642e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001154320454664035</v>
+        <v>2.34024970574417e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>9.400727509360838e-05</v>
+        <v>1.963173749226206e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>9.487132589547428e-05</v>
+        <v>2.010069100079818e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>9.468332951931112e-05</v>
+        <v>1.984013729566669e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>9.400705429226348e-05</v>
+        <v>1.963151391881473e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>9.580415237948654e-05</v>
+        <v>2.096096015584218e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>8.315898503377713e-05</v>
+        <v>1.753935566031022e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.448176481859278e-05</v>
+        <v>1.96385725949484e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.886406197238547e-06</v>
+        <v>4.886406197238557e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>7.563131361780112e-06</v>
+        <v>7.563131361780123e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.772177573468278e-06</v>
+        <v>4.772177573468281e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8528366747839e-06</v>
+        <v>7.852836674783911e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.992885863945371e-06</v>
+        <v>6.992885863945375e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.848816905066027e-06</v>
+        <v>5.848816905066047e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.828183774819408e-06</v>
+        <v>5.828183774819421e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.557155799166588e-06</v>
+        <v>6.557155799166596e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.339254419668391e-06</v>
+        <v>7.339254419668408e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.73440958402311e-06</v>
+        <v>5.734409584023117e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.960820586377629e-06</v>
+        <v>7.960820586377636e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.476093409108949e-06</v>
+        <v>5.476093409108954e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.400663414874916e-06</v>
+        <v>8.400663414874919e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.344706829385008e-06</v>
+        <v>5.344706829385019e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.695290965943414e-06</v>
+        <v>8.695290965943426e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.835340155104877e-06</v>
+        <v>7.835340155104889e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.583065085888012e-06</v>
+        <v>6.58306508588808e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>6.56932091773626e-06</v>
+        <v>6.569320917736269e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.411987462857717e-06</v>
+        <v>7.411987462857727e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.970113017885794e-06</v>
+        <v>7.970113017885811e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.320268593292573e-06</v>
+        <v>6.320268593292581e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.012570669092391e-06</v>
+        <v>9.012570669092389e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.112581304847907e-05</v>
+        <v>4.649856817730441e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.154880293823186e-05</v>
+        <v>5.54858854127616e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1057908971925e-05</v>
+        <v>4.581952741176393e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>1.15993435844171e-05</v>
+        <v>5.557484376912337e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.15993435844171e-05</v>
+        <v>5.557484376912345e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.161257491251185e-05</v>
+        <v>5.206947511123581e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.168587547079831e-05</v>
+        <v>5.209919240049613e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.157584807703022e-05</v>
+        <v>5.553318163289347e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.128875232737063e-05</v>
+        <v>4.812796096621979e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.11106626096285e-05</v>
+        <v>4.634706378879815e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.295338075143284e-05</v>
+        <v>6.477424520684165e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.323834309376196e-05</v>
+        <v>1.910166202739162e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001833603402572441</v>
+        <v>3.578741894556948e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>9.449384280127337e-05</v>
+        <v>1.9266677015571e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001833603410848604</v>
+        <v>3.578741977318598e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001833603410848604</v>
+        <v>3.578741977318598e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001483629332475226</v>
+        <v>2.927501044767094e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001617602284610027</v>
+        <v>3.162300522320355e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000183360303458228</v>
+        <v>3.578738214655366e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001134974421786522</v>
+        <v>2.280152541297376e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>9.564365202868773e-05</v>
+        <v>1.951251243601734e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001373994503159563</v>
+        <v>5.541016001141043e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.377797115807514e-05</v>
+        <v>5.116636642490048e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.425246104313295e-05</v>
+        <v>6.024432365160365e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.360584723743103e-05</v>
+        <v>5.036887265552843e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>1.409268932807571e-05</v>
+        <v>5.996313225418408e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.427616195422223e-05</v>
+        <v>6.028604407445223e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.426473302210774e-05</v>
+        <v>7.421067353024297e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.475732001314071e-05</v>
+        <v>7.510493467035983e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>1.422800618662629e-05</v>
+        <v>6.020097988048967e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.420684532021462e-05</v>
+        <v>7.012053421169423e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.370176266189058e-05</v>
+        <v>5.090739985606872e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.567189299624559e-05</v>
+        <v>6.955882673178632e-06</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.486094621693992e-05</v>
+        <v>7.067240242280696e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.53110180445074e-05</v>
+        <v>7.970738386856002e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>2.478494021157963e-05</v>
+        <v>6.997910226264507e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.533268764624754e-05</v>
+        <v>7.974552918697373e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.533268764624754e-05</v>
+        <v>7.974552918697373e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.534770808097271e-05</v>
+        <v>7.624330935673844e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.542100863925912e-05</v>
+        <v>7.627302664599895e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>2.531098124549105e-05</v>
+        <v>7.970701587839616e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.502388549583147e-05</v>
+        <v>7.230179521172228e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>2.484579577808911e-05</v>
+        <v>7.052089803430079e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>2.668851391989368e-05</v>
+        <v>8.894807945234428e-06</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.032932463658499e-05</v>
+        <v>1.330967481031292e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>9.370323844418499e-05</v>
+        <v>2.000776911199038e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>9.996706834382527e-05</v>
+        <v>2.022996470584042e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>8.470291874255239e-05</v>
+        <v>1.842371353502715e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.183960607212582e-05</v>
+        <v>1.439977052683627e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>9.370251839576607e-05</v>
+        <v>1.965477748588927e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>9.377581895405723e-05</v>
+        <v>1.965774921481613e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>9.366579156028449e-05</v>
+        <v>2.000114813805506e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>9.338515893700428e-05</v>
+        <v>1.926176358162428e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.970329184142916e-05</v>
+        <v>1.31870090773352e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001293959522679136</v>
+        <v>2.697131699653659e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.177347504946772e-05</v>
+        <v>1.532384527206636e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>8.970241893251108e-05</v>
+        <v>1.930362488173625e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>8.918444533675013e-05</v>
+        <v>1.833222306687838e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001098726657512624</v>
+        <v>2.285358898455642e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>8.970241669153923e-05</v>
+        <v>1.930362516928096e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>8.973910896897625e-05</v>
+        <v>1.895721743055408e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>8.981240952726273e-05</v>
+        <v>1.896018915948014e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>8.970238213349481e-05</v>
+        <v>1.930358808271989e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>8.941528638383496e-05</v>
+        <v>1.856306601605248e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>7.910987052324358e-05</v>
+        <v>1.653025228980593e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.107991480789724e-05</v>
+        <v>2.022769444011467e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.455381063605288e-05</v>
+        <v>6.455381063605283e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.894676363974633e-05</v>
+        <v>1.894676363974634e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.481626151198042e-05</v>
+        <v>2.481626151198043e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>1.935028803664268e-05</v>
+        <v>1.935028803664269e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.815859866674576e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>4.066204014111108e-05</v>
+        <v>4.06620401411111e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>7.980514127846331e-05</v>
+        <v>7.980514127846337e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.794823970873341e-05</v>
+        <v>1.794823970873342e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>2.955062865619612e-05</v>
+        <v>2.955062865619615e-05</v>
       </c>
       <c r="K2" t="n">
         <v>4.052573755392844e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.987647328404922e-05</v>
+        <v>7.987647328404937e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7287,31 +7287,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.416822861252703e-05</v>
+        <v>7.416822861252702e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.155573163476351e-05</v>
+        <v>2.15557316347635e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.846181551134132e-05</v>
+        <v>2.846181551134131e-05</v>
       </c>
       <c r="E3" t="n">
         <v>2.196541100493841e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.077372163504145e-05</v>
+        <v>2.077372163504146e-05</v>
       </c>
       <c r="G3" t="n">
         <v>4.668774337799585e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.172140933410765e-05</v>
+        <v>9.17214093341075e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.056075906862975e-05</v>
+        <v>2.056075906862977e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.351017861736719e-05</v>
+        <v>3.351017861736722e-05</v>
       </c>
       <c r="K3" t="n">
         <v>4.625725816070823e-05</v>
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.202278301023824e-05</v>
+        <v>4.090102365833259e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.232335011922465e-05</v>
+        <v>1.284886737985339e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.840049387876829e-05</v>
+        <v>1.727873452686263e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.248612907223723e-05</v>
+        <v>1.287751879936094e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.248612907223725e-05</v>
+        <v>1.287751879936093e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.76852556978703e-05</v>
+        <v>2.667463922394794e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>6.10803521358822e-05</v>
+        <v>4.995859278397665e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.345351940290776e-05</v>
+        <v>1.304509929763331e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.964315972346395e-05</v>
+        <v>1.852140037155828e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.66558849394427e-05</v>
+        <v>2.553412558753705e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>6.11242620519557e-05</v>
+        <v>5.000250270005009e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003299173980277163</v>
+        <v>0.0006123996312805865</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007067230652035595</v>
+        <v>0.0001333032165820017</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00108612900370729</v>
+        <v>0.0002034389512479539</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007067230680238657</v>
+        <v>0.0001333032194023082</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0007067230680238654</v>
+        <v>0.0001333032194023082</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002028451412130471</v>
+        <v>0.0003770494808575432</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004463131231511768</v>
+        <v>0.0008247195433560109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007067198153551758</v>
+        <v>0.0001332999667336189</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001324206670349609</v>
+        <v>0.0002463645770071684</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001881375727058416</v>
+        <v>0.0003502048160412145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005029759856506446</v>
+        <v>0.0009244823625855813</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.012060366140698e-05</v>
+        <v>4.23262400852156e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.928084353628684e-05</v>
+        <v>1.407338621462114e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5428622004681e-05</v>
+        <v>1.851568507032061e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.890838776265182e-05</v>
+        <v>1.400783632274918e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.120256492203024e-05</v>
+        <v>1.441161150061188e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>6.686648116347983e-05</v>
+        <v>3.181053487806584e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.188668080580056e-05</v>
+        <v>5.538050660050305e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.155134005407649e-05</v>
+        <v>1.818099495175122e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.924593204011667e-05</v>
+        <v>2.373148827105782e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.524532519737926e-05</v>
+        <v>2.704586706474237e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>7.032373815350564e-05</v>
+        <v>5.162161048514952e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.475422030063358e-05</v>
+        <v>4.49017565997638e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>4.618820654168579e-05</v>
+        <v>1.704908208744724e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>5.112318352480414e-05</v>
+        <v>2.127792788289488e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>4.614917873034627e-05</v>
+        <v>1.704221551662133e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>4.614917873034628e-05</v>
+        <v>1.704221551662133e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>6.041669298826554e-05</v>
+        <v>3.067537216537914e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>8.381178942627751e-05</v>
+        <v>5.39593257254078e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>4.618495669330304e-05</v>
+        <v>1.704583223906452e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.237459701385922e-05</v>
+        <v>2.25221333129895e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>5.938732222983796e-05</v>
+        <v>2.953485852896826e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>8.38556993423509e-05</v>
+        <v>5.400323564148125e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0001203708308444373</v>
+        <v>5.293028001196986e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000138449840963422</v>
+        <v>3.328712965770362e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001530864048261732</v>
+        <v>3.922345473469615e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001256876230065785</v>
+        <v>3.104098163338442e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>9.326587306246405e-05</v>
+        <v>2.533475367414005e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001526954637487098</v>
+        <v>4.691643573121349e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001760905601867287</v>
+        <v>7.020038929124331e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001384637274537472</v>
+        <v>3.328689580489877e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001446625382247325</v>
+        <v>3.876481087809058e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001041371591914449</v>
+        <v>3.741082979153429e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002248769982742376</v>
+        <v>7.882298411900493e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001736410715348022</v>
+        <v>6.230584232267165e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001801170834412963</v>
+        <v>4.062056429405423e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000185060809128632</v>
+        <v>4.485094986143572e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002205547647906528</v>
+        <v>4.773759849690913e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001801170246327216</v>
+        <v>4.062055626767771e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001943455698878761</v>
+        <v>5.424685437198608e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000217740666325888</v>
+        <v>7.753080793201468e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001801138335929135</v>
+        <v>4.061731444567141e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001863034739134697</v>
+        <v>4.609361551959645e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001721889741325524</v>
+        <v>4.953292707014741e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002177845762419612</v>
+        <v>7.757471784808809e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,19 +7643,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.407105974897554e-06</v>
+        <v>5.407105974897548e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>7.602301758685792e-06</v>
+        <v>7.602301758685784e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.860820676678514e-05</v>
+        <v>1.860820676678518e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>7.952101415197652e-06</v>
+        <v>7.952101415197647e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.918426067462392e-06</v>
+        <v>6.918426067462394e-06</v>
       </c>
       <c r="G2" t="n">
         <v>2.214803893549439e-05</v>
@@ -7664,16 +7664,16 @@
         <v>1.491335337294451e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>6.748377126117804e-06</v>
+        <v>6.748377126117802e-06</v>
       </c>
       <c r="J2" t="n">
         <v>1.271492619918667e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>9.657210440905511e-06</v>
+        <v>9.657210440905515e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.129281189361711e-05</v>
+        <v>5.129281189361702e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.097767629107471e-06</v>
+        <v>6.09776762910747e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.490235155214337e-06</v>
+        <v>8.49023515521434e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>2.128176813956897e-05</v>
+        <v>2.1281768139569e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.845606344214842e-06</v>
+        <v>8.845606344214839e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.811930996479592e-06</v>
+        <v>7.811930996479581e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.535330840760925e-05</v>
+        <v>2.535330840760929e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.704295925980816e-05</v>
+        <v>1.704295925980814e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>7.644746902960077e-06</v>
+        <v>7.64474690296008e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.415747852230372e-05</v>
+        <v>1.415747852230373e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.086215464459826e-05</v>
+        <v>1.086215464459825e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.887494596810432e-05</v>
+        <v>5.887494596810428e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.282417731883718e-05</v>
+        <v>5.107433832023085e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.214558652361516e-05</v>
+        <v>5.64948236541713e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>2.067167236152306e-05</v>
+        <v>1.295492887470902e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.225177442431557e-05</v>
+        <v>5.66817306581005e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.225177442431557e-05</v>
+        <v>5.668173065810051e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.265825210113508e-05</v>
+        <v>1.503849381759412e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.847718752684227e-05</v>
+        <v>1.07604440400282e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.286845009939541e-05</v>
+        <v>5.774860856089206e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.579984887782766e-05</v>
+        <v>8.083105391013581e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>1.485949444546878e-05</v>
+        <v>7.142750958654705e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.009566655779048e-05</v>
+        <v>3.237892307097633e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.464266583937076e-05</v>
+        <v>1.59874877526823e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001517792109067272</v>
+        <v>3.022500012367992e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007313352727715153</v>
+        <v>0.0001380317218691261</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001517792128848473</v>
+        <v>3.022500210179997e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001517792128848473</v>
+        <v>3.022500210179997e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009443724970187509</v>
+        <v>0.0001772602000440797</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0006117483476038917</v>
+        <v>0.0001151761676478012</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001517769712247205</v>
+        <v>3.022276044167296e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000360474926458586</v>
+        <v>6.874591871651945e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000249822043548259</v>
+        <v>4.849615937666799e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002898709042893066</v>
+        <v>6.577248608702113e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.683480869502883e-05</v>
+        <v>8.379151540387239e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.561373071361167e-05</v>
+        <v>6.259875739549053e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.497424085188173e-05</v>
+        <v>1.371218092490851e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.541873722569822e-05</v>
+        <v>6.225558515833183e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>1.676213095005845e-05</v>
+        <v>6.461995810039401e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>4.124755736302313e-05</v>
+        <v>1.574436493597902e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.787399054956043e-05</v>
+        <v>1.417428135352837e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.145775536128344e-05</v>
+        <v>9.04657856445336e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.471735534225367e-05</v>
+        <v>8.86828348385847e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.80833120622774e-05</v>
+        <v>7.710142856138557e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.494876458101853e-05</v>
+        <v>3.32330683184362e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.983746709860702e-05</v>
+        <v>8.101772817037452e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>2.98839795611722e-05</v>
+        <v>8.771439523110523e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>3.767686043229149e-05</v>
+        <v>1.594784195894684e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.987020868114141e-05</v>
+        <v>8.769017478209157e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.987020868114143e-05</v>
+        <v>8.769017478209157e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>3.967154188090493e-05</v>
+        <v>1.803283280260845e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.549047730661208e-05</v>
+        <v>1.375478302504257e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.988173987916522e-05</v>
+        <v>8.769199841103552e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.281313865759749e-05</v>
+        <v>1.107744437602793e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.187278422523862e-05</v>
+        <v>1.013708994366905e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.710895633756037e-05</v>
+        <v>3.537326205599071e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.874659487155792e-05</v>
+        <v>1.494977926797018e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001066047492998879</v>
+        <v>2.227429492397311e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001222408155594035</v>
+        <v>3.08310979806721e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>9.626215770921005e-05</v>
+        <v>2.045400044383297e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>6.998815491476146e-05</v>
+        <v>1.582977597706682e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001163878335702023</v>
+        <v>3.153490006676249e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0001122067689959023</v>
+        <v>2.725685028919528e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001065980315684628</v>
+        <v>2.227126710525756e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0001095368605376852</v>
+        <v>2.458081935375391e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>7.007962451834033e-05</v>
+        <v>1.686149379881807e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000173317992120754</v>
+        <v>5.582605224300721e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.436377569900044e-05</v>
+        <v>1.94584030691696e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001179505288647331</v>
+        <v>2.427115211655042e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001257515347357575</v>
+        <v>3.144898455236229e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001451154772477764</v>
+        <v>2.905218463603048e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001179505202129463</v>
+        <v>2.427115222380689e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001277380911844658</v>
+        <v>3.353254539604839e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001235570266101729</v>
+        <v>2.925449561848248e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001179482891827261</v>
+        <v>2.426891243454345e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0001208796879611583</v>
+        <v>2.657715696946787e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001063000354118221</v>
+        <v>2.041992126940316e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001451755056411211</v>
+        <v>5.08729746494306e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001385122794605194</v>
+        <v>1.570778702707871e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>3.625612813026399e-05</v>
+        <v>1.147949003391009e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.708970575188187e-05</v>
+        <v>9.843838275849462e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>3.670506773261651e-05</v>
+        <v>1.188373024162623e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>3.536482442033259e-05</v>
+        <v>1.076852046677038e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>4.940853905205301e-05</v>
+        <v>1.101843414366405e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.915285760095603e-05</v>
+        <v>1.311593165682023e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.472419768657004e-05</v>
+        <v>1.024613227131663e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>4.415516815248734e-05</v>
+        <v>1.33067223911271e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>6.849658550064606e-05</v>
+        <v>1.434055268977168e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>9.482868977935949e-05</v>
+        <v>1.343335717409049e-05</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001592734425647052</v>
+        <v>5.676376663871405e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>4.142342151776641e-05</v>
+        <v>2.000785023316678e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.111440168316289e-05</v>
+        <v>1.509029372923066e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.187796269063379e-05</v>
+        <v>2.065059224954099e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>4.053771937834982e-05</v>
+        <v>1.880949500506249e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.678568331074939e-05</v>
+        <v>2.347100836623213e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001025126958175935</v>
+        <v>3.853758243294182e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.989956026744259e-05</v>
+        <v>1.794534359946983e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.024915003751872e-05</v>
+        <v>2.480610531641515e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>7.829444414888569e-05</v>
+        <v>3.357417788681089e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001090268979146228</v>
+        <v>4.075785439206606e-05</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.569403166249024e-05</v>
+        <v>8.569403166249032e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.371232111341035e-05</v>
+        <v>2.371232111341032e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.945803296765656e-05</v>
+        <v>1.945803296765658e-05</v>
       </c>
       <c r="E4" t="n">
         <v>2.374510111757816e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.374510111757819e-05</v>
+        <v>2.374510111757817e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.270446960646527e-05</v>
+        <v>3.270446960646537e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.634315073910036e-05</v>
+        <v>5.634315073910026e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.386407400509712e-05</v>
+        <v>2.386407400509709e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.764740891634929e-05</v>
+        <v>2.764740891634932e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.230581764258649e-05</v>
+        <v>4.23058176425865e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.971771766680642e-05</v>
+        <v>5.971771766680634e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001470536052262903</v>
+        <v>0.001470536052262904</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003241519350910872</v>
+        <v>0.0003241519350910874</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002423737592336268</v>
+        <v>0.0002423737592336275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003241519377304019</v>
+        <v>0.0003241519377304018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003241519377304019</v>
+        <v>0.0003241519377304018</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000508086514575561</v>
+        <v>0.0005080865145755611</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001065262072389386</v>
+        <v>0.001065262072389385</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003241497698026628</v>
+        <v>0.0003241497698026627</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004203600232339448</v>
+        <v>0.000420360023233946</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0006809263376697692</v>
+        <v>0.0006809263376697701</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001502197387609809</v>
+        <v>0.001174452545305074</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.782143543200306e-05</v>
+        <v>8.782143543200312e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.568132321001956e-05</v>
+        <v>2.568132321001952e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.116653608825735e-05</v>
+        <v>2.116651144898412e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.557797469389256e-05</v>
+        <v>2.557797469389257e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.594794757035431e-05</v>
+        <v>2.594794757035433e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.934767427362179e-05</v>
+        <v>3.93476742736218e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>6.323357363770529e-05</v>
+        <v>6.32335736377052e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.599147777460984e-05</v>
+        <v>3.050727867225362e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.993597733509307e-05</v>
+        <v>3.431964490425821e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.484681259384713e-05</v>
+        <v>4.484681259384755e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>6.205428115070378e-05</v>
+        <v>6.205428115070375e-05</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.06665418635669e-05</v>
+        <v>9.066654186356674e-05</v>
       </c>
       <c r="C7" t="n">
         <v>2.883874949459845e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.442888489488512e-05</v>
+        <v>2.442888489488511e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.883172303254405e-05</v>
+        <v>2.883172303254403e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.883172303254405e-05</v>
+        <v>2.883172303254404e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.767697980754179e-05</v>
+        <v>3.767697980754177e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.131566094017683e-05</v>
+        <v>6.131566094017674e-05</v>
       </c>
       <c r="I7" t="n">
         <v>2.883658420617354e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.261991911742577e-05</v>
+        <v>3.261991911742574e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.727832784366296e-05</v>
+        <v>4.727832784366297e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.469022786788288e-05</v>
+        <v>6.469022786788283e-05</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.974658366118132e-05</v>
+        <v>9.974658366118129e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>4.755962396546824e-05</v>
+        <v>4.755962396548615e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.515381643637234e-05</v>
+        <v>4.515381643637232e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>4.492204264601733e-05</v>
+        <v>4.492204264601727e-05</v>
       </c>
       <c r="F8" t="n">
         <v>3.822127636641335e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.640059525654405e-05</v>
+        <v>5.640059525654401e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.003927638917946e-05</v>
+        <v>8.00392763891793e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.756019965517577e-05</v>
+        <v>4.756019965517581e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.13454298048272e-05</v>
+        <v>5.134542980482719e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.617923530972313e-05</v>
+        <v>5.617923530972316e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.348736237809161e-05</v>
+        <v>9.348736237809141e-05</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000114687162717011</v>
+        <v>0.0001146871627170107</v>
       </c>
       <c r="C9" t="n">
-        <v>6.11886624390141e-05</v>
+        <v>6.118866243901407e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>5.678045674579624e-05</v>
+        <v>5.678045674579618e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>7.080047708800903e-05</v>
+        <v>7.080047708800898e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>6.118865305776819e-05</v>
+        <v>6.118865305776814e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>7.00268927519574e-05</v>
+        <v>7.002689275195744e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>9.366557388459248e-05</v>
+        <v>9.366557388459236e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>6.11864971505892e-05</v>
+        <v>6.118649715058918e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>6.49698320618414e-05</v>
+        <v>6.496983206184136e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>7.480221650501158e-05</v>
+        <v>6.914017510820507e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>9.704014081229855e-05</v>
+        <v>9.704014081229836e-05</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.601796685271349e-06</v>
+        <v>4.487495119932236e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>8.143175991594609e-06</v>
+        <v>5.475092828653056e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.165877783908721e-06</v>
+        <v>4.675065629318302e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>8.45882247480791e-06</v>
+        <v>5.743394794227629e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>7.521373656342797e-06</v>
+        <v>4.96343848720271e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.492035251783212e-06</v>
+        <v>4.692230649051629e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>8.110982787150012e-06</v>
+        <v>4.666141995128379e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.092655095024555e-06</v>
+        <v>4.619197886202236e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.926320054702644e-06</v>
+        <v>6.53615610539605e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.058914196204912e-06</v>
+        <v>5.26700704125067e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>8.229032605996393e-06</v>
+        <v>4.676611514640637e-06</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.156144607568395e-06</v>
+        <v>4.454665627844304e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>9.068309616752099e-06</v>
+        <v>6.810408816366463e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>9.255576168176749e-06</v>
+        <v>5.786915140363948e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>9.389067103875526e-06</v>
+        <v>7.248946349035013e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>8.451618285410426e-06</v>
+        <v>5.961259584040696e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>9.630724819548325e-06</v>
+        <v>5.910861591812218e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.202448733969378e-06</v>
+        <v>5.770860040762221e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>8.034960502208852e-06</v>
+        <v>5.391138411795318e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.77943664085568e-06</v>
+        <v>8.410138886467364e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.696741070330762e-06</v>
+        <v>5.90188230065384e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.328640837476434e-06</v>
+        <v>5.823339538619724e-06</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.541596705601712e-06</v>
+        <v>4.541596705601725e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.908966911653498e-06</v>
+        <v>5.908966911653507e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>6.660291895814565e-06</v>
+        <v>6.660291895814574e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.919112804576492e-06</v>
+        <v>5.919112804576522e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.919112804576502e-06</v>
+        <v>5.91911280457651e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>6.838440443559681e-06</v>
+        <v>6.838440443559697e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>6.627971099327545e-06</v>
+        <v>6.627971099327561e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.927515155798204e-06</v>
+        <v>5.927515155798222e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>5.723999217719703e-06</v>
+        <v>5.723999217719708e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8719717893787e-06</v>
+        <v>4.871971789378706e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>6.698447132357081e-06</v>
+        <v>6.698447132357086e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.48983159382635e-05</v>
+        <v>1.489831593826351e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.929641011172657e-05</v>
+        <v>3.929641011172659e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.902809519193747e-05</v>
+        <v>4.90280951919375e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.929641103054187e-05</v>
+        <v>3.929641103054188e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.929641103054187e-05</v>
+        <v>3.929641103054188e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.318721236610582e-05</v>
+        <v>5.318721236610587e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.38610506369442e-05</v>
+        <v>5.38610506369444e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.929608469240384e-05</v>
+        <v>3.92960846924039e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.553816424527997e-05</v>
+        <v>3.553816424528007e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.075275334241414e-05</v>
+        <v>2.075275334241418e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.703478044387972e-05</v>
+        <v>5.703478044387979e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.888397356064295e-06</v>
+        <v>5.041200565203788e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.405576558661675e-06</v>
+        <v>6.405576558661683e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>9.037703690169963e-06</v>
+        <v>9.037703690169969e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.375770871451425e-06</v>
+        <v>6.375770871451445e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.433654035794381e-06</v>
+        <v>6.433654035794393e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.338044303161744e-06</v>
+        <v>9.185241094022282e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>9.093107774986429e-06</v>
+        <v>9.093107774986437e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.427119015400268e-06</v>
+        <v>6.427119015400286e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>8.090114956730423e-06</v>
+        <v>6.278383484060813e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>5.332885525541871e-06</v>
+        <v>5.332885525542378e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.209681478846175e-06</v>
+        <v>7.209681478846184e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.138822598198759e-06</v>
+        <v>7.138822598198779e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.525066467717898e-06</v>
+        <v>8.525066467717932e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>9.256089968410073e-06</v>
+        <v>9.256089968410076e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>8.528567012293206e-06</v>
+        <v>8.528567012293231e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.528567012293206e-06</v>
+        <v>8.528567012293231e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.435666336156718e-06</v>
+        <v>9.435666336156743e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>9.225196991924608e-06</v>
+        <v>9.225196991924621e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.524741048395257e-06</v>
+        <v>8.524741048395291e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>8.321225110316745e-06</v>
+        <v>8.321225110316779e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.469197681975739e-06</v>
+        <v>7.469197681975762e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>9.29567302495412e-06</v>
+        <v>9.295673024954139e-06</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.354662727343965e-05</v>
+        <v>1.354662727343968e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.097834774654783e-05</v>
+        <v>2.097834774656322e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.295671898517908e-05</v>
+        <v>2.295671898517911e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.93256368027935e-05</v>
+        <v>1.932563680279354e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.51272429746746e-05</v>
+        <v>1.512724297467464e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.188261225476102e-05</v>
+        <v>2.188261225476104e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.167214291052797e-05</v>
+        <v>2.167214291052801e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.097168696699953e-05</v>
+        <v>2.097168696699955e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.076935789329649e-05</v>
+        <v>2.076935789329653e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.376482220812983e-05</v>
+        <v>1.376482220812986e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.805100695707434e-05</v>
+        <v>2.805100695707437e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1194,25 +1194,25 @@
         <v>1.575696014758203e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.03830395504179e-05</v>
+        <v>2.038303955041792e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.111549182443729e-05</v>
+        <v>2.111549182443731e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.412174182456793e-05</v>
+        <v>2.412174182456798e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.038303965618843e-05</v>
+        <v>2.038303965618844e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.129363941885674e-05</v>
+        <v>2.129363941885672e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.108317007462461e-05</v>
+        <v>2.108317007462463e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.038271413109529e-05</v>
+        <v>2.038271413109528e-05</v>
       </c>
       <c r="J9" t="n">
         <v>2.01791981930168e-05</v>
@@ -1221,7 +1221,7 @@
         <v>1.744999773382702e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.115364610765418e-05</v>
+        <v>2.115364610765416e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.154091671158337e-05</v>
+        <v>9.027628087210144e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>5.618271697718503e-05</v>
+        <v>1.066127035980484e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.960536594488944e-05</v>
+        <v>8.399483756272279e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.192338845442425e-05</v>
+        <v>8.494999409607859e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>2.192338845442425e-05</v>
+        <v>8.495356414920502e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>3.020782572633892e-05</v>
+        <v>8.957470156388719e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.567445539929082e-05</v>
+        <v>9.768674193067619e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.194246184944976e-05</v>
+        <v>8.523046332347579e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.990111518087525e-05</v>
+        <v>1.009804034435718e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.389488268498797e-05</v>
+        <v>9.832448254289217e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>2.413197463399529e-05</v>
+        <v>8.62792018313862e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.609811388385375e-05</v>
+        <v>1.673046136046668e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.43692044434306e-05</v>
+        <v>2.641561563423438e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.236975806026298e-05</v>
+        <v>1.224774590663362e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.504044412229731e-05</v>
+        <v>1.308652264994524e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.504044412229731e-05</v>
+        <v>1.308687965525793e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.456478310185705e-05</v>
+        <v>1.62349494185004e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>5.236725921670894e-05</v>
+        <v>2.211119454207998e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.506579405624984e-05</v>
+        <v>1.313072330860035e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>4.559262940209755e-05</v>
+        <v>2.069492325128658e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.867448889998001e-05</v>
+        <v>1.847834220646533e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.757732598219433e-05</v>
+        <v>1.398755801447322e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.135691294441773e-05</v>
+        <v>2.135691294441772e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.593013772499266e-05</v>
+        <v>3.593013772499263e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.426173376580597e-05</v>
+        <v>1.426173376580598e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.546535247348163e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.546535247348162e-05</v>
+        <v>1.546535247348164e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.054610246798489e-05</v>
+        <v>2.054610246798493e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.975544556412702e-05</v>
+        <v>2.975544556412704e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.553828064644813e-05</v>
+        <v>1.553828064644814e-05</v>
       </c>
       <c r="J4" t="n">
         <v>2.584606957453024e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.223711573221282e-05</v>
+        <v>2.223711573221284e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.695540201969e-05</v>
+        <v>1.695540201969002e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0002812346412914289</v>
+        <v>0.0002812346412914291</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005474332232628834</v>
+        <v>0.000547433223262884</v>
       </c>
       <c r="D5" t="n">
         <v>0.0001493508819976453</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001758216780741254</v>
+        <v>0.0001758216780741252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001758216780741254</v>
+        <v>0.0001758216780741252</v>
       </c>
       <c r="G5" t="n">
         <v>0.0002693125739814497</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004794998444018604</v>
+        <v>0.0004794998444018606</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001758204071767958</v>
+        <v>0.0001758204071767954</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003741677798901796</v>
+        <v>0.0003741677798901792</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002931629152682991</v>
+        <v>0.0002931629152682987</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002256804863092949</v>
+        <v>0.0002256804863092948</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.31169290679448e-05</v>
+        <v>2.616202059433354e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.798993203963785e-05</v>
+        <v>3.79899320396378e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.583347414943119e-05</v>
+        <v>1.583346431987104e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.701032304462922e-05</v>
+        <v>1.701032304462921e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.725401363931838e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.535121011790069e-05</v>
+        <v>2.230611859151192e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.493481777273823e-05</v>
+        <v>3.493481777273825e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.034338829636394e-05</v>
+        <v>1.729829676997518e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.079919230251035e-05</v>
+        <v>3.079919230251036e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.408230831328277e-05</v>
+        <v>2.408230831328279e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.869247773524867e-05</v>
+        <v>1.869247773524869e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1510,31 +1510,31 @@
         <v>2.52023523580778e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.957496688437644e-05</v>
+        <v>3.957496688437641e-05</v>
       </c>
       <c r="D7" t="n">
         <v>1.810564350789082e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.938230396897281e-05</v>
+        <v>1.938230396897279e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.938230396897281e-05</v>
+        <v>1.938230396897279e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.439154188164495e-05</v>
+        <v>2.439154188164498e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>3.360088497778704e-05</v>
+        <v>3.360088497778703e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.938372006010817e-05</v>
+        <v>1.938372006010818e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.969150898819027e-05</v>
+        <v>2.969150898819032e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.608255514587288e-05</v>
+        <v>2.608255514587289e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.080084143335004e-05</v>
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.293638753760538e-05</v>
+        <v>3.293638753760542e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>5.521031162245087e-05</v>
+        <v>5.521031162245093e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.537978611178324e-05</v>
+        <v>3.537978611178325e-05</v>
       </c>
       <c r="E8" t="n">
         <v>3.285912541464621e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.736876565375178e-05</v>
+        <v>2.736876565375181e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.002595912650079e-05</v>
+        <v>4.002595912650084e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>4.923530222265092e-05</v>
+        <v>4.92353022226509e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.501813730496405e-05</v>
+        <v>3.501813730496408e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.532747888445096e-05</v>
+        <v>4.532747888445094e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.366983667248117e-05</v>
+        <v>3.366983667248121e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>4.468786836462024e-05</v>
+        <v>4.468786836462032e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.03980093168867e-05</v>
+        <v>4.039800931688671e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>6.027284331092722e-05</v>
+        <v>6.02728433109272e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.880504891966596e-05</v>
+        <v>3.880504891966595e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.643230178433638e-05</v>
+        <v>4.643230178433643e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.008285972070852e-05</v>
+        <v>4.008285972070854e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.508941830819565e-05</v>
+        <v>4.508941830819567e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>5.429876140433775e-05</v>
+        <v>5.429876140433777e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.008159648665886e-05</v>
+        <v>4.008159648665889e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.038938541474101e-05</v>
+        <v>5.0389385414741e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.359242371526063e-05</v>
+        <v>4.359242371526062e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.149871785990071e-05</v>
+        <v>4.149871785990077e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.512730186874158e-05</v>
+        <v>6.889935748051137e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>3.839626396517912e-05</v>
+        <v>8.387063664722275e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.477583314065554e-05</v>
+        <v>6.871438646965099e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.31935530373283e-05</v>
+        <v>6.866586663872706e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.31935530373283e-05</v>
+        <v>6.86693880273574e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.930764861246443e-05</v>
+        <v>7.109939094335877e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>2.65046987750821e-05</v>
+        <v>7.484033898262197e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>1.307783014272801e-05</v>
+        <v>6.782656358938777e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.579455882524256e-05</v>
+        <v>8.20135948164701e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.420541361440489e-05</v>
+        <v>7.192982833866226e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.101492059182573e-05</v>
+        <v>6.664011024645704e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.72571854022024e-05</v>
+        <v>9.755314899251208e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.396204446852381e-05</v>
+        <v>1.884384520882424e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.685292355837582e-05</v>
+        <v>9.623680635195934e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.501724733715508e-05</v>
+        <v>9.13348157047952e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>1.501724733715507e-05</v>
+        <v>9.133833709342552e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.206545011370285e-05</v>
+        <v>1.132999403452754e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.03555388024702e-05</v>
+        <v>1.406662499795157e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.491004409372543e-05</v>
+        <v>8.992846110359335e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.938225754013013e-05</v>
+        <v>1.473393054603943e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.612909861945695e-05</v>
+        <v>9.861027997989072e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>1.252810804743871e-05</v>
+        <v>8.222653603642546e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.121808055312186e-05</v>
+        <v>1.121808055312192e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.495688669621401e-05</v>
+        <v>2.495688669621403e-05</v>
       </c>
       <c r="D4" t="n">
         <v>1.10091472872681e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>9.87256947068063e-06</v>
+        <v>9.872569470680638e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.872569470680614e-06</v>
+        <v>9.872569470680643e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.368560661552766e-05</v>
+        <v>1.36856066155277e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.798007511422025e-05</v>
+        <v>1.79800751142203e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.892692699958203e-06</v>
+        <v>9.892692699958245e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.698750868014106e-05</v>
+        <v>1.698750868014104e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.040203226064384e-05</v>
+        <v>1.040203226064386e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.776326053503319e-06</v>
+        <v>8.776326053503353e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001060867181777401</v>
+        <v>0.0001060867181777399</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003462954245275838</v>
+        <v>0.0003462954245275841</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001025885567762941</v>
+        <v>0.000102588556776294</v>
       </c>
       <c r="E5" t="n">
-        <v>8.619484198687575e-05</v>
+        <v>8.619484198687585e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.619484198687575e-05</v>
+        <v>8.619484198687585e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001523554524113872</v>
+        <v>0.0001523554524113883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000248114979316814</v>
+        <v>0.0002481149793168142</v>
       </c>
       <c r="I5" t="n">
-        <v>8.619385578050571e-05</v>
+        <v>8.619385578050582e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002141279493554282</v>
+        <v>0.0002141279493554279</v>
       </c>
       <c r="K5" t="n">
-        <v>9.260955422890922e-05</v>
+        <v>9.260955422890903e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.322204900949607e-05</v>
+        <v>7.322204900949611e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.472478475871675e-05</v>
+        <v>1.47247847587167e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.63229413265008e-05</v>
+        <v>2.632294132650081e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.466685238338608e-05</v>
+        <v>1.466685238338619e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.084351872401105e-05</v>
+        <v>1.084351872401108e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.100776847726206e-05</v>
+        <v>1.100776847726205e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.481277221064254e-05</v>
+        <v>1.719231082112246e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.188553606399276e-05</v>
+        <v>2.188553606399277e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.101985829507306e-05</v>
+        <v>1.101985829507308e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.824061584908351e-05</v>
+        <v>1.82406158490836e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.14713305932168e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>9.890876588528505e-06</v>
+        <v>9.890876588528546e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.449219827784422e-05</v>
+        <v>1.449219827784427e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.810165457563413e-05</v>
+        <v>2.810165457563417e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.428182276381225e-05</v>
+        <v>1.428182276381228e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.317718866959418e-05</v>
+        <v>1.317718866959416e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.317718866959418e-05</v>
+        <v>1.317718866959416e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.695972434024999e-05</v>
+        <v>1.695972434025008e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.125419283894265e-05</v>
+        <v>2.125419283894264e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.316681042468055e-05</v>
+        <v>1.316681042468061e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.026162640486332e-05</v>
+        <v>2.026162640486342e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.36761499853662e-05</v>
+        <v>1.367614998536623e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.205044377822571e-05</v>
+        <v>1.20504437782257e-05</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.15341071050215e-05</v>
+        <v>2.153410710502148e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>4.217083887973409e-05</v>
+        <v>4.217083887970225e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.979488337299975e-05</v>
+        <v>2.979488337299979e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.531672341081182e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.04385360239698e-05</v>
+        <v>2.043853602396983e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.101671896260571e-05</v>
+        <v>3.101671896260575e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.531118746132092e-05</v>
+        <v>3.531118746132102e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.722380504703625e-05</v>
+        <v>2.722380504703627e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.431999969233284e-05</v>
+        <v>3.431999969233277e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.058774999236577e-05</v>
+        <v>2.058774999236591e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.343528210537361e-05</v>
+        <v>3.343528210537359e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.545191041666231e-05</v>
+        <v>2.545191041666235e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.319819630533855e-05</v>
+        <v>4.319819630533859e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.937980659315284e-05</v>
+        <v>2.93798065931529e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.303814612895355e-05</v>
+        <v>3.303814612895358e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.826433377638184e-05</v>
+        <v>2.826433377638185e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.205626606995447e-05</v>
+        <v>3.205626606995458e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.635073456864715e-05</v>
+        <v>3.635073456864714e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.826335215438505e-05</v>
+        <v>2.826335215438513e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.535816813456777e-05</v>
+        <v>3.535816813456789e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.637579634105737e-05</v>
+        <v>2.637579634105743e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.714698550793015e-05</v>
+        <v>2.714698550793025e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.089271343763648e-06</v>
+        <v>5.5142393396175e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>2.345776678131599e-05</v>
+        <v>6.575155863521789e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.105747320194788e-05</v>
+        <v>5.775705935770038e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.019365635738689e-06</v>
+        <v>5.599282425200429e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.019365635738689e-06</v>
+        <v>5.599631617965376e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.191433032894795e-05</v>
+        <v>5.820800624508694e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.585959839839792e-05</v>
+        <v>6.023847674140602e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.890496285473104e-06</v>
+        <v>5.504354245878432e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.225463762284655e-05</v>
+        <v>6.5953639816135e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.07391683631717e-06</v>
+        <v>5.766752622809337e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>6.52617433740438e-06</v>
+        <v>5.531195216348877e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.883778930580886e-06</v>
+        <v>5.792890786685054e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.682625788869674e-05</v>
+        <v>1.250696428652983e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.259824022740721e-05</v>
+        <v>7.660092658400564e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.785659888182849e-06</v>
+        <v>5.886566341260092e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.785659888182848e-06</v>
+        <v>5.886915534025004e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.358380342087641e-05</v>
+        <v>7.985249964319912e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.813316504816494e-05</v>
+        <v>9.482832082908165e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.665590809464912e-06</v>
+        <v>5.727769605284946e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.382946772090135e-05</v>
+        <v>9.084964818193871e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.817318968875038e-06</v>
+        <v>6.116861563063651e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.387089230877387e-06</v>
+        <v>5.962372958006001e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.52575458471137e-06</v>
+        <v>5.525754584711373e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.578962170627047e-05</v>
+        <v>1.578962170627046e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>8.479140068831208e-06</v>
+        <v>8.479140068831199e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.288712621528354e-06</v>
+        <v>5.28871262152835e-06</v>
       </c>
       <c r="F4" t="n">
         <v>5.288712621528354e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>8.971072947882143e-06</v>
+        <v>8.97107294788217e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.133313521458535e-05</v>
+        <v>1.133313521458534e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.300997209136089e-06</v>
+        <v>5.300997209136078e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.613947588761432e-06</v>
+        <v>8.613947588761428e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>5.323500383352273e-06</v>
+        <v>5.323500383352269e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.787398874052602e-06</v>
+        <v>5.787398874052599e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.867421993847419e-05</v>
+        <v>1.867421993847418e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001997348805056785</v>
+        <v>0.0001997348805056784</v>
       </c>
       <c r="D5" t="n">
         <v>7.148066473663862e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.940079907739869e-05</v>
+        <v>1.940079907739867e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.940079907739869e-05</v>
+        <v>1.940079907739867e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.218973096237565e-05</v>
+        <v>8.218973096237569e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001343774882327257</v>
+        <v>0.0001343774882327255</v>
       </c>
       <c r="I5" t="n">
-        <v>1.939984518132728e-05</v>
+        <v>1.939984518132729e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.718084794436346e-05</v>
+        <v>7.718084794436349e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.78898052025124e-05</v>
+        <v>1.788980520251235e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.867566923848507e-05</v>
+        <v>2.867566923848506e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.241663403303076e-06</v>
+        <v>6.241663403303065e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.667351634887344e-05</v>
+        <v>1.667351634887343e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.227037321286342e-06</v>
+        <v>9.22703718583698e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.87622556288557e-06</v>
+        <v>5.876225562885552e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.011859400345184e-06</v>
+        <v>6.011859400345178e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.173807458397155e-05</v>
+        <v>1.173807458397154e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.448766357747552e-05</v>
+        <v>1.44876635774755e-05</v>
       </c>
       <c r="I6" t="n">
         <v>8.067998845225468e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.152467561704949e-05</v>
+        <v>1.152467561704948e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.97362383363178e-06</v>
+        <v>5.973623833631732e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>6.504874791589274e-06</v>
+        <v>6.504874791589047e-06</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.51117564310046e-06</v>
+        <v>8.511175643100449e-06</v>
       </c>
       <c r="C7" t="n">
         <v>1.871069064122699e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.146312450204684e-05</v>
+        <v>1.146312450204682e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>8.300089819275717e-06</v>
+        <v>8.300089819275712e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.300089819275717e-06</v>
+        <v>8.300089819275712e-06</v>
       </c>
       <c r="G7" t="n">
         <v>1.195649400627125e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.431855627297444e-05</v>
+        <v>1.431855627297443e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.28641826752517e-06</v>
+        <v>8.286418267525163e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.159936864715052e-05</v>
+        <v>1.159936864715054e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>8.308921441741353e-06</v>
+        <v>8.308921441741343e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>8.772819932441695e-06</v>
+        <v>8.772819932441687e-06</v>
       </c>
     </row>
     <row r="8">
@@ -2339,34 +2339,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.534597596077474e-05</v>
+        <v>1.534597596077473e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.221535534133477e-05</v>
+        <v>3.221535534137129e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.633379921160681e-05</v>
+        <v>2.633379921160682e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.997004648494053e-05</v>
+        <v>1.997004648494047e-05</v>
       </c>
       <c r="F8" t="n">
         <v>1.534155577299326e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54458637663136e-05</v>
+        <v>2.544586376631359e-05</v>
       </c>
       <c r="H8" t="n">
         <v>2.780792603304155e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.177578802756755e-05</v>
+        <v>2.177578802756756e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.509004622043933e-05</v>
+        <v>2.509004622043931e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.502010971558704e-05</v>
+        <v>1.502010971558701e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.921344392081454e-05</v>
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.728602668411994e-05</v>
+        <v>1.728602668411993e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.09184976204574e-05</v>
+        <v>3.091849762045737e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.367236806676762e-05</v>
+        <v>2.367236806676761e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.445673354570327e-05</v>
+        <v>2.445673354570326e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.049517600399531e-05</v>
+        <v>2.049517600399529e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.41643009855016e-05</v>
+        <v>2.416430098550161e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.652636325220482e-05</v>
+        <v>2.652636325220483e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.049422524675556e-05</v>
+        <v>2.049422524675555e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.38071756263809e-05</v>
+        <v>2.380717562638091e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.619402412458878e-05</v>
+        <v>1.844696124482633e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.098062691167207e-05</v>
+        <v>2.098062691167205e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.716482163333383e-06</v>
+        <v>5.973400598749905e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>5.171588593100944e-06</v>
+        <v>5.488207879389741e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.167156691731685e-05</v>
+        <v>6.286804881601087e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.823127342551855e-06</v>
+        <v>5.813007481137756e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.823127342551855e-06</v>
+        <v>5.813359722367706e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.876235783108256e-05</v>
+        <v>6.659979123947451e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.542812877170403e-05</v>
+        <v>7.538023962432395e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.022002939536779e-06</v>
+        <v>5.9900002151347e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.96040752061472e-05</v>
+        <v>8.49283222855971e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.08303743862175e-05</v>
+        <v>7.274555056898532e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>2.152402189498163e-05</v>
+        <v>6.804101006204491e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.421951786029514e-06</v>
+        <v>5.96133033141526e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.875432750308612e-06</v>
+        <v>5.186393188498719e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.327153284520094e-05</v>
+        <v>8.198963989044027e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.575974414556178e-06</v>
+        <v>5.795254856130014e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.575974414556178e-06</v>
+        <v>5.795607097359932e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.142741124894419e-05</v>
+        <v>1.086431413051454e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>4.060875169455531e-05</v>
+        <v>1.717730256669799e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.780773568819316e-06</v>
+        <v>6.085318646067926e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>4.525792363795643e-05</v>
+        <v>1.964469787249013e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.370863431491032e-05</v>
+        <v>1.228109015015391e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>2.460435586780994e-05</v>
+        <v>1.193856523415746e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2575,34 +2575,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.015446312155344e-06</v>
+        <v>5.015446312155355e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.902935798349308e-06</v>
+        <v>4.90293579834932e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>8.555491860052228e-06</v>
+        <v>8.555491860052232e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.038262479989775e-06</v>
+        <v>5.038262479989769e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.038262479989775e-06</v>
+        <v>5.038262479989769e-06</v>
       </c>
       <c r="G4" t="n">
         <v>1.275076939927659e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26741733305597e-05</v>
+        <v>2.267417333055969e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.073136401885926e-06</v>
+        <v>5.073136401885929e-06</v>
       </c>
       <c r="J4" t="n">
         <v>2.459907820745635e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.36144495776197e-05</v>
+        <v>1.361444957761971e-05</v>
       </c>
       <c r="L4" t="n">
         <v>1.441266004516805e-05</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.118401610249011e-05</v>
+        <v>1.118401610249012e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.467621073962342e-05</v>
+        <v>1.467621073962344e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>7.755590275986224e-05</v>
+        <v>7.755590275986221e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.756477847705002e-05</v>
+        <v>1.756477847704997e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.756477847705002e-05</v>
+        <v>1.756477847704997e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001570980955533704</v>
+        <v>0.0001570980955533706</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003711317921637806</v>
+        <v>0.0003711317921637804</v>
       </c>
       <c r="I5" t="n">
-        <v>1.756290498168555e-05</v>
+        <v>1.756290498168549e-05</v>
       </c>
       <c r="J5" t="n">
         <v>0.0003826349685466547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001687062069488869</v>
+        <v>0.0001687062069488872</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002084788651464976</v>
+        <v>0.0002084788651464974</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.776075094980263e-06</v>
+        <v>5.776075094980276e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>5.55778963232752e-06</v>
+        <v>5.557789632327526e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>9.26122410088077e-06</v>
+        <v>9.261229013348756e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.587867044715175e-06</v>
+        <v>5.587867044715167e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.821644908700304e-06</v>
+        <v>5.821644908700297e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.351139818210152e-05</v>
+        <v>1.351139818210151e-05</v>
       </c>
       <c r="H6" t="n">
         <v>2.601499771080539e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>5.833765184710849e-06</v>
+        <v>8.095167753968058e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>2.775214547974219e-05</v>
+        <v>2.554552054856372e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.449327158381475e-05</v>
+        <v>1.449327158381476e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.522973563755197e-05</v>
+        <v>1.522973563755199e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.3235198847789e-06</v>
+        <v>8.323519884778913e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.323835322691959e-06</v>
+        <v>8.323835322691981e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1862063706197e-05</v>
+        <v>1.186206370619701e-05</v>
       </c>
       <c r="E7" t="n">
         <v>8.399160478419965e-06</v>
@@ -2710,22 +2710,22 @@
         <v>8.399160478419965e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.605884297190016e-05</v>
+        <v>1.605884297190017e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.598224690318322e-05</v>
+        <v>2.598224690318324e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.381209974509483e-06</v>
+        <v>8.38120997450949e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.79071517800799e-05</v>
+        <v>2.790715178007992e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.692252315024323e-05</v>
+        <v>1.692252315024327e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.772073361779158e-05</v>
+        <v>1.772073361779161e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.563039259066025e-05</v>
+        <v>1.563039259066027e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.282828018776249e-05</v>
+        <v>2.282828018777904e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.78379331664485e-05</v>
+        <v>2.783793316644856e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.092178244299752e-05</v>
+        <v>2.092178244299755e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.59280028772274e-05</v>
+        <v>1.592800287722741e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.054461844969153e-05</v>
+        <v>3.054461844969156e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>4.046802238097699e-05</v>
+        <v>4.046802238097703e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.286698545230087e-05</v>
+        <v>2.286698545230088e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.239433811820218e-05</v>
+        <v>4.239433811820222e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.409604405147369e-05</v>
+        <v>2.409604405147372e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.970547333114442e-05</v>
+        <v>3.970547333114446e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.05657049256544e-05</v>
+        <v>2.056570492565438e-05</v>
       </c>
       <c r="C9" t="n">
         <v>2.505554844991797e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.859527912381608e-05</v>
+        <v>2.859527912381609e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.02956112710909e-05</v>
+        <v>3.029561127109093e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.511479175384412e-05</v>
+        <v>2.511479175384406e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.279055609912617e-05</v>
+        <v>3.279055609912616e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.271396003040921e-05</v>
+        <v>4.271396003040926e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.511292310173551e-05</v>
+        <v>2.51129231017355e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.463886490730595e-05</v>
+        <v>4.463886490730593e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.800111889267808e-05</v>
+        <v>3.105298630968693e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.445244674501757e-05</v>
+        <v>3.445244674501763e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.828836573874057e-06</v>
+        <v>4.748167455536049e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.710083268396456e-06</v>
+        <v>4.581983559856807e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.197584544180419e-06</v>
+        <v>4.767573928820927e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.199876168580859e-06</v>
+        <v>4.862879474520079e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.199876168580859e-06</v>
+        <v>4.863223871512612e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.754682954978427e-06</v>
+        <v>4.796892911694572e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.419605980133891e-06</v>
+        <v>4.827080842746126e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.061756188844138e-06</v>
+        <v>4.761052443242604e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.411790357477663e-05</v>
+        <v>5.919671797117856e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.18474049514528e-06</v>
+        <v>5.030574094212216e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>6.664431993336494e-06</v>
+        <v>4.844529416316124e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.403151629358766e-06</v>
+        <v>4.894551297143202e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.291343741231841e-06</v>
+        <v>4.65375454421624e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.827288181122987e-06</v>
+        <v>5.038136572305373e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.81096664331349e-06</v>
+        <v>5.162066438737476e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.81096664331349e-06</v>
+        <v>5.162410835729887e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.468066756129068e-06</v>
+        <v>5.247802439119195e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>7.24440855802628e-06</v>
+        <v>5.497232165826888e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.685987298746322e-06</v>
+        <v>4.991883921445059e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.595600125589474e-05</v>
+        <v>9.265368689186753e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.761721055139963e-06</v>
+        <v>5.371258620555473e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>7.514873973764484e-06</v>
+        <v>5.595376812739608e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2977,31 +2977,31 @@
         <v>4.428230329654737e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.628517733738457e-06</v>
+        <v>4.628517733738446e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.514965452299246e-06</v>
+        <v>4.514965452299245e-06</v>
       </c>
       <c r="F4" t="n">
         <v>4.514965452299246e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.944106310186099e-06</v>
+        <v>4.944106310186097e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.355022205945511e-06</v>
+        <v>5.355022205945516e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.454161548300343e-06</v>
+        <v>4.454161548300335e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>9.410840401118811e-06</v>
+        <v>9.410840401118824e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.419861652389849e-06</v>
+        <v>4.419861652389838e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.50071576216857e-06</v>
+        <v>5.500715762168567e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3011,34 +3011,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.04006626846012e-05</v>
+        <v>1.040066268460121e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.418079475709182e-05</v>
+        <v>1.41807947570918e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.691040650390262e-05</v>
+        <v>1.691040650390261e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.56581542881716e-05</v>
+        <v>1.565815428817158e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.56581542881716e-05</v>
+        <v>1.565815428817158e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.296710860734498e-05</v>
+        <v>2.296710860734494e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.228060447081747e-05</v>
+        <v>3.22806044708174e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.565792982686288e-05</v>
+        <v>1.565792982686294e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001028623196090509</v>
+        <v>0.000102862319609051</v>
       </c>
       <c r="K5" t="n">
-        <v>1.339585257126788e-05</v>
+        <v>1.339585257126785e-05</v>
       </c>
       <c r="L5" t="n">
         <v>3.565438401650682e-05</v>
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.816600406850899e-06</v>
+        <v>4.8166004068509e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.829534410832812e-06</v>
+        <v>4.829534410832805e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.035645353141179e-06</v>
+        <v>6.7711041350415e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.825026944922758e-06</v>
+        <v>4.825026944922751e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.866998137250739e-06</v>
+        <v>4.866998137250748e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>6.971694687188248e-06</v>
+        <v>5.351394026468672e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>7.652560812742185e-06</v>
+        <v>7.652560812742188e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.481749925302507e-06</v>
+        <v>6.481749925302544e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>9.891162386269393e-06</v>
+        <v>1.154455574040096e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.824280960104431e-06</v>
+        <v>4.824280960104428e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>5.915215756794556e-06</v>
+        <v>5.91521575679455e-06</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.071838508102384e-06</v>
+        <v>7.071838508102382e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.110352112715905e-06</v>
+        <v>7.110352112715904e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.289622570444794e-06</v>
+        <v>7.289622570444782e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.140554078533917e-06</v>
+        <v>7.140554078533922e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.140554078533917e-06</v>
+        <v>7.140554078533922e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.606632127720161e-06</v>
+        <v>7.606632127720174e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>8.017548023479593e-06</v>
+        <v>8.017548023479583e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.116687365834415e-06</v>
+        <v>7.116687365834423e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.207336621865289e-05</v>
+        <v>1.20733662186529e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.082387469923927e-06</v>
+        <v>7.082387469923919e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>8.163241579702651e-06</v>
+        <v>8.163241579702645e-06</v>
       </c>
     </row>
     <row r="8">
@@ -3134,34 +3134,34 @@
         <v>1.358339249299807e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.979893454251828e-05</v>
+        <v>1.979893454249982e-05</v>
       </c>
       <c r="D8" t="n">
         <v>2.122956182058882e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.812003778286912e-05</v>
+        <v>1.812003778286906e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.383840795302144e-05</v>
+        <v>1.383840795302141e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.026961213786765e-05</v>
+        <v>2.026961213786764e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.06805280336367e-05</v>
+        <v>2.068052803363667e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.977966737598191e-05</v>
+        <v>1.977966737598194e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.473755516052033e-05</v>
+        <v>2.473755516052035e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.347967555823784e-05</v>
+        <v>1.347967555823782e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.725190044735408e-05</v>
+        <v>2.725190044735409e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.562567152198069e-05</v>
+        <v>1.562567152198068e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.890641739290857e-05</v>
+        <v>1.890641739290854e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.90871092585192e-05</v>
+        <v>1.908710925851919e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.265444367646868e-05</v>
+        <v>2.265444367646866e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.891297622267211e-05</v>
+        <v>1.891297622267212e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.940269740791283e-05</v>
+        <v>1.940269740791284e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.981361330367227e-05</v>
+        <v>1.981361330367224e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.891275264602708e-05</v>
+        <v>1.891275264602709e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.386943149884554e-05</v>
+        <v>2.386943149884553e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.479590347973824e-05</v>
+        <v>1.699989082140851e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.995930685989531e-05</v>
+        <v>1.995930685989529e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.664025498257948e-06</v>
+        <v>4.57865693995822e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.695790043632522e-06</v>
+        <v>4.500332479798862e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.003700617257668e-06</v>
+        <v>4.596533366822046e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.046005536540932e-06</v>
+        <v>4.761441061737567e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.046005536540932e-06</v>
+        <v>4.761785933769798e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.893499441361107e-06</v>
+        <v>4.59073369781178e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.068038152599931e-06</v>
+        <v>4.595043478092111e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.821253436714957e-06</v>
+        <v>4.587561504042281e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.914951623649127e-06</v>
+        <v>5.328008756495446e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.088810956093934e-06</v>
+        <v>4.921035311200113e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.835097258857842e-06</v>
+        <v>4.586824848236488e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.223117756651338e-06</v>
+        <v>4.690066215502148e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.26895382397638e-06</v>
+        <v>4.607817791005768e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.613814506989941e-06</v>
+        <v>4.822756397492864e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.630512571018551e-06</v>
+        <v>5.048159388627634e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.630512571018551e-06</v>
+        <v>5.048504260659872e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.487060326604093e-06</v>
+        <v>4.781911848814847e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.698734920799017e-06</v>
+        <v>4.844972882415391e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.419258405073599e-06</v>
+        <v>4.759035319496176e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.530270978614164e-06</v>
+        <v>6.041286380259014e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.650060764897774e-06</v>
+        <v>5.264794782640829e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.420333209707777e-06</v>
+        <v>4.761684704192599e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.378783667459582e-06</v>
+        <v>4.378783667459606e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.43463360974635e-06</v>
+        <v>4.434633609746361e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.580706132449187e-06</v>
+        <v>4.580706132449209e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.429149276413964e-06</v>
+        <v>4.429149276413981e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.429149276413965e-06</v>
+        <v>4.429149276413981e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.49979605047429e-06</v>
+        <v>4.499796050474566e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.619128602706356e-06</v>
+        <v>4.619128602706348e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.37995480903797e-06</v>
+        <v>4.37995480903783e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.60130720582992e-06</v>
+        <v>4.601307205829956e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.387322357536454e-06</v>
+        <v>4.387322357536467e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.480892893116269e-06</v>
+        <v>4.480892893116267e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.02396919336459e-05</v>
+        <v>1.023969193364609e-05</v>
       </c>
       <c r="C5" t="n">
         <v>1.452632769681757e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.645668128389433e-05</v>
+        <v>1.645668128389434e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.472647836967414e-05</v>
+        <v>1.472647836967428e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.472647836967414e-05</v>
+        <v>1.472647836967428e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.556660574137124e-05</v>
+        <v>1.556660574137129e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.860317190402809e-05</v>
+        <v>1.86031719040281e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.472633779113139e-05</v>
+        <v>1.472633779113154e-05</v>
       </c>
       <c r="J5" t="n">
         <v>1.738575696104838e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.320105662527943e-05</v>
+        <v>1.320105662527945e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.617725563957044e-05</v>
+        <v>1.617725563957048e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.37541427971543e-06</v>
+        <v>6.37541427971545e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.805259243399134e-06</v>
+        <v>4.805259243399146e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.961656492841272e-06</v>
+        <v>4.961656492841274e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.725444101698585e-06</v>
+        <v>4.7254441016986e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.758941711265189e-06</v>
+        <v>4.758941711265203e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>6.496426662729923e-06</v>
+        <v>6.496426662729925e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.902606046929978e-06</v>
+        <v>4.994218436558538e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>4.753602842690882e-06</v>
+        <v>6.376585421293773e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>6.705389183428346e-06</v>
+        <v>5.020042579765926e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.766810081932416e-06</v>
+        <v>4.76681008193238e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.85630666135668e-06</v>
+        <v>4.856306661356683e-06</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.970839918840482e-06</v>
+        <v>6.970839918840498e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.038495642329368e-06</v>
+        <v>7.038495642329374e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.171341241647952e-06</v>
+        <v>7.171341241647971e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.992403137571262e-06</v>
+        <v>6.992403137571281e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.992403137571262e-06</v>
+        <v>6.992403137571281e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.091852301854973e-06</v>
+        <v>7.091852301855013e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.211184854087254e-06</v>
+        <v>7.211184854087259e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.97201106041882e-06</v>
+        <v>6.972011060418834e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.193363457210824e-06</v>
+        <v>7.193363457210845e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>6.979378608917359e-06</v>
+        <v>6.979378608917361e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.072949144497165e-06</v>
+        <v>7.072949144497159e-06</v>
       </c>
     </row>
     <row r="8">
@@ -3530,34 +3530,34 @@
         <v>1.344471857654826e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.961407734079711e-05</v>
+        <v>1.9614077340822e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.098658305191813e-05</v>
+        <v>2.098658305191811e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.788232702221575e-05</v>
+        <v>1.788232702221577e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.365166506528249e-05</v>
+        <v>1.36516650652825e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.964508028419934e-05</v>
+        <v>1.964508028419938e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.976441283644467e-05</v>
+        <v>1.976441283644469e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.95252390427632e-05</v>
+        <v>1.952523904276321e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.974778620593779e-05</v>
+        <v>1.97477862059378e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.334033023177329e-05</v>
+        <v>1.334033023177332e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.597656584342673e-05</v>
+        <v>2.597656584342674e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.475767879745493e-05</v>
+        <v>1.475767879745494e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.783449837978535e-05</v>
+        <v>1.783449837978538e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.796876549653562e-05</v>
+        <v>1.796876549653563e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.124066510343984e-05</v>
+        <v>2.124066510343986e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.776815365582954e-05</v>
+        <v>1.776815365582956e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.788785503931097e-05</v>
+        <v>1.788785503931101e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.800718759154324e-05</v>
+        <v>1.80071875915433e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.776801379787481e-05</v>
+        <v>1.776801379787484e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.798936619466683e-05</v>
+        <v>1.798936619466684e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.596112327379068e-05</v>
+        <v>1.603186014649654e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.786895188195315e-05</v>
+        <v>1.78689518819532e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.973075135845317e-06</v>
+        <v>5.009074305657922e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.762065562019087e-06</v>
+        <v>4.792515402381494e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.059782200356419e-06</v>
+        <v>5.066265540089394e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.34727620277325e-06</v>
+        <v>5.077415781308588e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.347276202773265e-06</v>
+        <v>5.077761885865493e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.835946937938938e-06</v>
+        <v>5.212369576321169e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>2.936615702215688e-05</v>
+        <v>6.298755686008157e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.269441409429334e-06</v>
+        <v>5.025266773914852e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.947821823057894e-06</v>
+        <v>5.670168291369107e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.306943960569189e-06</v>
+        <v>5.25092685886346e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.754531702454682e-05</v>
+        <v>5.675695052639393e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.569082746264453e-06</v>
+        <v>5.09818757557404e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.359704468880011e-06</v>
+        <v>4.765815291641474e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.819020981142428e-06</v>
+        <v>5.510922839182705e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.98949920915254e-06</v>
+        <v>5.30730433669428e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.989499209152402e-06</v>
+        <v>5.307650441251195e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.001218551015523e-05</v>
+        <v>6.553945125096924e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.363787718130027e-05</v>
+        <v>1.43117980915748e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.923103593567014e-06</v>
+        <v>5.21912571404539e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.572774201065318e-06</v>
+        <v>6.251259356304667e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.909896074502773e-06</v>
+        <v>5.516200396033495e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.002980283751539e-05</v>
+        <v>9.858418283992393e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.528454486587389e-06</v>
+        <v>4.528454486587206e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.498218563177349e-06</v>
+        <v>4.49821856317735e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.174455788754685e-06</v>
+        <v>5.174455788754736e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.640682923515113e-06</v>
+        <v>4.640682923515105e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.640682923515115e-06</v>
+        <v>4.640682923515106e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>6.808101467878207e-06</v>
+        <v>6.808101467878121e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.902458800897663e-05</v>
+        <v>1.90245880089766e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.603333319552839e-06</v>
+        <v>4.603333319552845e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.643005877175927e-06</v>
+        <v>4.64300587717578e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.555937952539928e-06</v>
+        <v>4.555937952539917e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.200065891912652e-05</v>
+        <v>1.200065891912655e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.039050949052763e-05</v>
+        <v>1.039050949052765e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.400936026755618e-05</v>
+        <v>1.400936026755616e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.491139000587249e-05</v>
+        <v>2.49113900058724e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.662721328268966e-05</v>
+        <v>1.662721328268917e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.662721328268966e-05</v>
+        <v>1.662721328268917e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.576699744595011e-05</v>
+        <v>5.576699744594999e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003064700876991533</v>
+        <v>0.0003064700876991528</v>
       </c>
       <c r="I5" t="n">
-        <v>1.662659472155963e-05</v>
+        <v>1.662659472155926e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.59021234017928e-05</v>
+        <v>1.590212340179275e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.387952022919662e-05</v>
+        <v>1.387952022919668e-05</v>
       </c>
       <c r="L5" t="n">
         <v>0.0001680015622017125</v>
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.964618344060191e-06</v>
+        <v>4.964618344059976e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.909835028109313e-06</v>
+        <v>4.90983502810932e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.588658983487674e-06</v>
+        <v>5.588658983487557e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.962622710819713e-06</v>
+        <v>4.962622710819698e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.040930871155277e-06</v>
+        <v>5.040930871155282e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>9.154759590993741e-06</v>
+        <v>7.244265325350946e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.168204215056356e-05</v>
+        <v>2.168204215056375e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>6.949991442668553e-06</v>
+        <v>5.039497177025593e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>7.110116330113097e-06</v>
+        <v>5.129775247840603e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.95245368934779e-06</v>
+        <v>4.952453689347819e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.248188473745288e-05</v>
+        <v>1.248188473745302e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.43984889517876e-06</v>
+        <v>7.439848895178857e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.455645065188198e-06</v>
+        <v>7.455645065188215e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>8.084350374207755e-06</v>
+        <v>8.08435037420789e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.536806410459871e-06</v>
+        <v>7.536806410459905e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.536806410459871e-06</v>
+        <v>7.536806410459901e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.719495876469641e-06</v>
+        <v>9.719495876469621e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.19359824175681e-05</v>
+        <v>2.193598241756811e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>7.514727728144323e-06</v>
+        <v>7.514727728144326e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.55440028576723e-06</v>
+        <v>7.554400285767335e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.46733236113147e-06</v>
+        <v>7.467332361131474e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>1.491205332771784e-05</v>
+        <v>1.491205332771786e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.442294485237304e-05</v>
+        <v>1.442294485237325e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.110797254010497e-05</v>
+        <v>2.110797254009026e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.309246191489825e-05</v>
+        <v>2.309246191489822e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.934726936573577e-05</v>
+        <v>1.934726936573578e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.472279179248019e-05</v>
+        <v>1.472279179248017e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.334811506120583e-05</v>
+        <v>2.334811506120581e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.556460160230575e-05</v>
+        <v>3.556460160230588e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.114334691288045e-05</v>
+        <v>2.114334691288044e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.118432550654091e-05</v>
+        <v>2.118432550654066e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.43269843125415e-05</v>
+        <v>1.432698431254161e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.548247721351647e-05</v>
+        <v>3.548247721351635e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.792062321657971e-05</v>
+        <v>1.792062321657957e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.179620972743434e-05</v>
+        <v>2.179620972743435e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.242641285186738e-05</v>
+        <v>2.242641285186715e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.631001991955071e-05</v>
+        <v>2.631001991955068e-05</v>
       </c>
       <c r="F9" t="n">
         <v>2.185590660783494e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.406006053871588e-05</v>
+        <v>2.406006053871572e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.62765470798143e-05</v>
+        <v>3.627654707981416e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.185529239039049e-05</v>
+        <v>2.185529239039047e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.189496494801344e-05</v>
+        <v>2.189496494801338e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.957151849689039e-05</v>
+        <v>1.957151849689032e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.925261798996405e-05</v>
+        <v>2.925261798996396e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.646300764181465e-06</v>
+        <v>4.561324630416131e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.689611782809457e-06</v>
+        <v>4.519901793216451e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.976395260888956e-06</v>
+        <v>4.578696848157356e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.161441005383273e-06</v>
+        <v>4.783284544023614e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.161441005383271e-06</v>
+        <v>4.78362886439264e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.863194217245482e-06</v>
+        <v>4.572739302065797e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.061681237326755e-06</v>
+        <v>4.578387894140945e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.895415675501537e-06</v>
+        <v>4.57506695544115e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.894825990441809e-06</v>
+        <v>5.305432535804088e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.164777358935656e-06</v>
+        <v>4.960783059552466e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.767019608522717e-06</v>
+        <v>4.566798855351552e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.203243592466696e-06</v>
+        <v>4.645685745349148e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.255708731832425e-06</v>
+        <v>4.614159502088721e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.582920642549314e-06</v>
+        <v>4.774759934749387e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.757606204364122e-06</v>
+        <v>5.094901754231996e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.757606204364124e-06</v>
+        <v>5.095246074601e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.452715992833762e-06</v>
+        <v>4.732795697794227e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.692282641138244e-06</v>
+        <v>4.804978917329391e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.505865301412946e-06</v>
+        <v>4.749105596118445e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.508621114451742e-06</v>
+        <v>5.9894465905362e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.727904929194583e-06</v>
+        <v>5.322334093535797e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.342539804039136e-06</v>
+        <v>4.698277615342986e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.353951532090071e-06</v>
+        <v>4.353951532090063e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.387696582667442e-06</v>
+        <v>4.387696582667433e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.550178723092346e-06</v>
+        <v>4.550178723092333e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.496482891364583e-06</v>
+        <v>4.496482891364577e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.496482891364584e-06</v>
+        <v>4.496482891364576e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.467594671118812e-06</v>
+        <v>4.467594671118788e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.601047190601618e-06</v>
+        <v>4.601047190601625e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.410434735687242e-06</v>
+        <v>4.410434735687232e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.578949349521655e-06</v>
+        <v>4.578949349521645e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.378428176836273e-06</v>
+        <v>4.378428176836254e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.426135325723313e-06</v>
+        <v>4.426135325723311e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.043213416865469e-05</v>
+        <v>1.043213416865467e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.436225305327036e-05</v>
+        <v>1.436225305327035e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.653936212663227e-05</v>
+        <v>1.653936212663222e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.584636268143159e-05</v>
+        <v>1.584636268143158e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.584636268143159e-05</v>
+        <v>1.584636268143158e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.562152875042012e-05</v>
+        <v>1.562152875041972e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.893676492518827e-05</v>
+        <v>1.893676492518824e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.58462366459609e-05</v>
+        <v>1.584623664596091e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.761932987317169e-05</v>
+        <v>1.761932987317168e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.365331301674509e-05</v>
+        <v>1.365331301674507e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.580214723283067e-05</v>
+        <v>1.580214723283066e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.734677835013392e-06</v>
+        <v>6.33950892309534e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.76620384712325e-06</v>
+        <v>4.766203847123241e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.937965189498159e-06</v>
+        <v>4.937967332710172e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.770702341248203e-06</v>
+        <v>4.770702341248196e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.798987813939514e-06</v>
+        <v>4.798987813939503e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>4.84832097404213e-06</v>
+        <v>4.848320974042119e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.842875263467316e-06</v>
+        <v>6.842875263467305e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.39599212669253e-06</v>
+        <v>6.395992126692516e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>6.668233978233579e-06</v>
+        <v>5.003574897648381e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.766090578696465e-06</v>
+        <v>4.766090578696453e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.808234783625506e-06</v>
+        <v>4.808234783625492e-06</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.903082860734603e-06</v>
+        <v>6.903082860734595e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>6.950281718466554e-06</v>
+        <v>6.950281718466548e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.097889613000558e-06</v>
+        <v>7.097889613000544e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.989384342455573e-06</v>
+        <v>6.989384342455557e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.989384342455573e-06</v>
+        <v>6.989384342455557e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.016725999763351e-06</v>
+        <v>7.01672599976332e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.150178519246163e-06</v>
+        <v>7.150178519246149e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.95956606433177e-06</v>
+        <v>6.959566064331763e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.12808067816619e-06</v>
+        <v>7.128080678166177e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>6.927559505480792e-06</v>
+        <v>6.927559505480775e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>6.975266654367847e-06</v>
+        <v>6.975266654367837e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.331482740771066e-05</v>
+        <v>1.331482740771065e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.939297017974493e-05</v>
+        <v>1.93929701797449e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.075469759937465e-05</v>
+        <v>2.07546975993746e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.775784194305319e-05</v>
+        <v>1.775784194305316e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.358017458225935e-05</v>
+        <v>1.358017458225934e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.942805966088338e-05</v>
+        <v>1.942805966088333e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.956151218037304e-05</v>
+        <v>1.956151218037301e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.937089972545178e-05</v>
+        <v>1.937089972545177e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.954059343059661e-05</v>
+        <v>1.954059343059658e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.32278586044624e-05</v>
+        <v>1.322785860446238e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.565367282283908e-05</v>
+        <v>2.565367282283902e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.53637037641065e-05</v>
+        <v>1.536370376410649e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.858887193537498e-05</v>
+        <v>1.858887193537496e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.873790061716994e-05</v>
+        <v>1.87379006171699e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.226559099450995e-05</v>
+        <v>2.226559099450991e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.859828164370002e-05</v>
+        <v>1.859828164369997e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.865531621667177e-05</v>
+        <v>1.865531621667173e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.878876873615461e-05</v>
+        <v>1.878876873615456e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.85981562812402e-05</v>
+        <v>1.859815628124016e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.876667089507462e-05</v>
+        <v>1.876667089507457e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.672482196787152e-05</v>
+        <v>1.456451900080778e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.861385687127629e-05</v>
+        <v>1.861385687127625e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.621612868446889e-06</v>
+        <v>4.598385347472674e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.683333964114168e-06</v>
+        <v>4.548509349156774e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.93199854770313e-06</v>
+        <v>4.61472032929632e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.022727082746475e-06</v>
+        <v>4.77928698910926e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.022727082746475e-06</v>
+        <v>4.779632344597319e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.845819620255859e-06</v>
+        <v>4.610184903510134e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.037013822680733e-06</v>
+        <v>4.615486132397775e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.801665917377414e-06</v>
+        <v>4.608492041143502e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.866346723968653e-06</v>
+        <v>5.310970490043709e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.074407555989991e-06</v>
+        <v>4.945590454411099e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.779908122525926e-06</v>
+        <v>4.605841999337523e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.179189216055296e-06</v>
+        <v>4.640185780076052e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.254521519311679e-06</v>
+        <v>4.60347750522029e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.536197043399747e-06</v>
+        <v>4.761906044851698e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.609149239556915e-06</v>
+        <v>5.001758900049501e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.609149239556914e-06</v>
+        <v>5.002104255537452e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.437073424924347e-06</v>
+        <v>4.730058728297885e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.667698441808717e-06</v>
+        <v>4.799491610679038e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.401938745163694e-06</v>
+        <v>4.717727635552563e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.486239893244253e-06</v>
+        <v>5.942430141788768e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.63770279271791e-06</v>
+        <v>5.229718360476071e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.361706614703077e-06</v>
+        <v>4.706925693901528e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.357095473428562e-06</v>
+        <v>4.35709547342855e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.417126887538958e-06</v>
+        <v>4.417126887538953e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5416066075895e-06</v>
+        <v>4.54160660758949e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.433273023124513e-06</v>
+        <v>4.43327302312448e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.433273023124512e-06</v>
+        <v>4.433273023124479e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.47497447937606e-06</v>
+        <v>4.474974479376056e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.604207716630655e-06</v>
+        <v>4.604207716630637e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.371827296051756e-06</v>
+        <v>4.371827296051742e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.603719619132191e-06</v>
+        <v>4.603719619132179e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.379728465704774e-06</v>
+        <v>4.379728465704764e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.451609927664498e-06</v>
+        <v>4.451609927664493e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.014735942906434e-05</v>
+        <v>1.014735942906432e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.44087819945797e-05</v>
+        <v>1.440878199457968e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.607270032164921e-05</v>
+        <v>1.607270032164918e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.487070545295102e-05</v>
+        <v>1.487070545295134e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.487070545295102e-05</v>
+        <v>1.487070545295134e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.542185517789873e-05</v>
+        <v>1.542185517789874e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.863472949573004e-05</v>
+        <v>1.863472949572999e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.487056788978426e-05</v>
+        <v>1.487056788978401e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.772399141681572e-05</v>
+        <v>1.772399141681571e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.335323632226558e-05</v>
+        <v>1.335323632226556e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.592938774115031e-05</v>
+        <v>1.592938774115028e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.746688658754913e-06</v>
+        <v>6.368118009849542e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.798338363159833e-06</v>
+        <v>4.798338363159828e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.938347818321022e-06</v>
+        <v>4.938345431729957e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.734835599391278e-06</v>
+        <v>4.734835599391239e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.76763844244463e-06</v>
+        <v>4.767638442444629e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>6.485997015797063e-06</v>
+        <v>4.864567664702426e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.896333026970537e-06</v>
+        <v>6.896333026970516e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.382849832472754e-06</v>
+        <v>4.761420481378105e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.038102361371106e-06</v>
+        <v>6.72308664759501e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.776457270800063e-06</v>
+        <v>4.77645727080007e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.84302230689766e-06</v>
+        <v>4.843022306898104e-06</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.867783553898968e-06</v>
+        <v>6.867783553898974e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>6.933158829303962e-06</v>
+        <v>6.933158829303943e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.050873671829234e-06</v>
+        <v>7.050873671829236e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.906503202571953e-06</v>
+        <v>6.906503202571917e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.906503202571953e-06</v>
+        <v>6.906503202571917e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.985662559846488e-06</v>
+        <v>6.985662559846481e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.114895797101078e-06</v>
+        <v>7.114895797101059e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8825153765222e-06</v>
+        <v>6.882515376522159e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.114407699602614e-06</v>
+        <v>7.114407699602595e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>6.890416546175187e-06</v>
+        <v>6.890416546175185e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>6.962298008134922e-06</v>
+        <v>6.962298008134913e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.325270784116403e-05</v>
+        <v>1.325270784116399e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.93054214126077e-05</v>
+        <v>1.930542141258137e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.063495536822518e-05</v>
+        <v>2.063495536822514e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.762135912300602e-05</v>
+        <v>1.762135912300599e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.347162523077883e-05</v>
+        <v>1.347162523077886e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.933215354849003e-05</v>
+        <v>1.933215354849e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.946138678575646e-05</v>
+        <v>1.946138678575644e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.922900636516568e-05</v>
+        <v>1.922900636516569e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.946207030685743e-05</v>
+        <v>1.946207030685744e-05</v>
       </c>
       <c r="K8" t="n">
         <v>1.316460167129631e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.55361439144418e-05</v>
+        <v>2.553614391444179e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.466223112389822e-05</v>
+        <v>1.466223112389821e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.771220998562525e-05</v>
+        <v>1.771220998562523e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.783134619135227e-05</v>
+        <v>1.783134619135223e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.110587284464981e-05</v>
+        <v>2.110587284464979e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.766170344014728e-05</v>
+        <v>1.766170344014721e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.776471371616779e-05</v>
+        <v>1.776471371616775e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.789394695342233e-05</v>
+        <v>1.789394695342234e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.766156653284344e-05</v>
+        <v>1.766156653284342e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.789345885592387e-05</v>
+        <v>1.789345885592386e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.587001727902934e-05</v>
+        <v>1.587001727902932e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.774134916445619e-05</v>
+        <v>1.774134916445617e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0001177616524622836</v>
+        <v>1.426200401018757e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.441663541404659e-05</v>
+        <v>1.018820959862699e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.653925512676392e-05</v>
+        <v>9.461150420693664e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.485643263827365e-05</v>
+        <v>1.058383590819806e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>2.355100001499694e-05</v>
+        <v>9.497603908501801e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.927023047624872e-05</v>
+        <v>1.06574365059836e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>8.432291544674067e-05</v>
+        <v>1.250535423289187e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.329145880576128e-05</v>
+        <v>9.290617196458022e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.273961857975723e-05</v>
+        <v>1.204383798109377e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.749313973982298e-05</v>
+        <v>1.299510283860444e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>9.211584569019067e-05</v>
+        <v>1.293496924688113e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001354108937589252</v>
+        <v>4.880828125721692e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.787026576728992e-05</v>
+        <v>1.498828054781519e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.048624016039809e-05</v>
+        <v>1.470213054652823e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.831669382243498e-05</v>
+        <v>1.561423891305974e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.701126119915825e-05</v>
+        <v>1.38209732165802e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.663157051966369e-05</v>
+        <v>2.323326762036771e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.696133985671518e-05</v>
+        <v>3.652745788633553e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.674627914678787e-05</v>
+        <v>1.347744930638327e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.71832809984772e-05</v>
+        <v>1.994377180110075e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.572266298281355e-05</v>
+        <v>2.873685059494035e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001059116777123292</v>
+        <v>3.955506151300247e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.28477486467677e-05</v>
+        <v>7.284774864676768e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.629673419349565e-05</v>
+        <v>1.629673419349562e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.861989885167093e-05</v>
+        <v>1.861989885167094e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.633097382815279e-05</v>
+        <v>1.633097382815276e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.633097382815279e-05</v>
+        <v>1.633097382815276e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.21074309371531e-05</v>
+        <v>3.210743093715314e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.29621206606683e-05</v>
+        <v>5.296212066066826e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.652913636662361e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.058554203612757e-05</v>
+        <v>2.05855420361276e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.556840968821966e-05</v>
+        <v>3.556840968821964e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.759471955000449e-05</v>
+        <v>5.759471955000446e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00116032229903859</v>
+        <v>0.001160322299038592</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001819411642815728</v>
+        <v>0.0001819411642815725</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002227373792459579</v>
+        <v>0.0002227373792459577</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001819411676434771</v>
+        <v>0.0001819411676434765</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001819411676434771</v>
+        <v>0.0001819411676434765</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004744163606872031</v>
+        <v>0.000474416360687204</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00094009759621291</v>
+        <v>0.0009400975962129091</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001819374630861067</v>
+        <v>0.0001819374630861064</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002730852509264683</v>
+        <v>0.0002730852509264685</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005260409395401814</v>
+        <v>0.0005260409395401833</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002354731552780864</v>
+        <v>0.0002354731552780863</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.876706140528185e-05</v>
+        <v>7.454593621131129e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.77539900625156e-05</v>
+        <v>1.775399006251556e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.998901922671196e-05</v>
+        <v>1.998899680422175e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.767676661806677e-05</v>
+        <v>1.767676661806674e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.815014625929321e-05</v>
+        <v>1.815014625929319e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.802674369566724e-05</v>
+        <v>3.380561850169649e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.913717348770774e-05</v>
+        <v>5.913717348770766e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.244844912513777e-05</v>
+        <v>2.244844912513775e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.656174353745354e-05</v>
+        <v>2.240067767506775e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.750831728665351e-05</v>
+        <v>3.750831728665335e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.949828055584461e-05</v>
+        <v>5.949828055584465e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.73346592698479e-05</v>
+        <v>7.733465926984793e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.101974818516971e-05</v>
+        <v>2.101974818516967e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.310526584795926e-05</v>
+        <v>2.310526584795919e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.100898667928621e-05</v>
+        <v>2.100898667928619e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.100898667928621e-05</v>
+        <v>2.100898667928619e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.659434156023321e-05</v>
+        <v>3.659434156023322e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.744903128374844e-05</v>
+        <v>5.744903128374839e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.10160469897037e-05</v>
+        <v>2.101604698970371e-05</v>
       </c>
       <c r="J7" t="n">
         <v>2.507245265920769e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.005532031129976e-05</v>
+        <v>4.005532031129977e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.208163017308454e-05</v>
+        <v>6.208163017308451e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.578617018040993e-05</v>
+        <v>8.578617018041003e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.834665440943999e-05</v>
+        <v>3.834665440945888e-05</v>
       </c>
       <c r="D8" t="n">
         <v>4.228206227426125e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.591779664396708e-05</v>
+        <v>3.591779664396705e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.974730726014504e-05</v>
+        <v>2.974730726014499e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.392785357081673e-05</v>
+        <v>5.39278535708168e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.478254329433152e-05</v>
+        <v>7.478254329433151e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.834955900028731e-05</v>
+        <v>3.834955900028728e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.240771023720446e-05</v>
+        <v>4.240771023720442e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.834184349144886e-05</v>
+        <v>4.834184349144892e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.8693135033175e-05</v>
+        <v>8.869313503317479e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5151,16 +5151,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.654455195148188e-05</v>
+        <v>9.654455195148192e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.707084637940077e-05</v>
+        <v>4.70708463794007e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.915790982693763e-05</v>
+        <v>4.915790982693756e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.496544392141002e-05</v>
+        <v>5.496544392140999e-05</v>
       </c>
       <c r="F9" t="n">
         <v>4.707083864113789e-05</v>
@@ -5169,19 +5169,19 @@
         <v>6.264543975446428e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>8.350012947797955e-05</v>
+        <v>8.350012947797958e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.706714518393481e-05</v>
+        <v>4.706714518393475e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.112355085343878e-05</v>
+        <v>5.11235508534388e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.214259807167906e-05</v>
+        <v>6.214259807167912e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.813272836731567e-05</v>
+        <v>8.813272836731563e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.741807225470612e-05</v>
+        <v>1.345048840330389e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>3.477311491123015e-05</v>
+        <v>1.121600613056201e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.672015955729919e-05</v>
+        <v>9.729797675403951e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>3.519796121020251e-05</v>
+        <v>1.159983150235722e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>3.392904819519584e-05</v>
+        <v>1.054399646058545e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>4.990874819338606e-05</v>
+        <v>1.095016703907456e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>7.716959063423322e-05</v>
+        <v>1.238339335644911e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.335854020528745e-05</v>
+        <v>1.007964889452381e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.096312941795246e-05</v>
+        <v>1.230901747845895e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.92210697197089e-05</v>
+        <v>1.347246569537302e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>8.857255741694462e-05</v>
+        <v>1.300439647980043e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001119835014687704</v>
+        <v>4.1390536801927e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>3.971149174454206e-05</v>
+        <v>1.92963887722398e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.066625683825665e-05</v>
+        <v>1.492587771091564e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.014257906025163e-05</v>
+        <v>1.990514636597635e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.887366604524497e-05</v>
+        <v>1.816205696584126e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.733793727142173e-05</v>
+        <v>2.36232975598465e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.870469058329019e-05</v>
+        <v>3.399080262789787e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.83049669116224e-05</v>
+        <v>1.739372327967024e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.50927133213798e-05</v>
+        <v>1.956458680594799e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.765755704891529e-05</v>
+        <v>2.96522644530377e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001018083051340031</v>
+        <v>3.838078213677709e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.109965944847591e-05</v>
+        <v>6.109965944847599e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.275020300609103e-05</v>
+        <v>2.275020300609105e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.90727460745488e-05</v>
+        <v>1.907274607454893e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.278100277345757e-05</v>
+        <v>2.278100277345758e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.278100277345757e-05</v>
+        <v>2.278100277345758e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.283568402632554e-05</v>
+        <v>3.283568402632567e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.905689118776225e-05</v>
+        <v>4.905689118776218e-05</v>
       </c>
       <c r="I4" t="n">
         <v>2.288281080573286e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.979891005891074e-05</v>
+        <v>1.979891005891073e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.684384832106125e-05</v>
+        <v>3.684384832106126e-05</v>
       </c>
       <c r="L4" t="n">
         <v>5.583468371960315e-05</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009026103989706339</v>
+        <v>0.0009026103989706341</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002606791241651143</v>
+        <v>0.0002606791241651138</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002059851176449821</v>
+        <v>0.0002059851176449837</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002606791265526765</v>
+        <v>0.0002606791265526759</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0002606791265526765</v>
+        <v>0.000260679126552676</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004433325426358721</v>
+        <v>0.0004433325426358731</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007986684751129891</v>
+        <v>0.0007986684751129859</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002606767050077501</v>
+        <v>0.0002606767050077497</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002336116001288676</v>
+        <v>0.0002336116001288675</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004771536667512911</v>
+        <v>0.000477153666751292</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000287872034535442</v>
+        <v>0.0002878720345354421</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.684775822116267e-05</v>
+        <v>6.284900617371462e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.438025013868714e-05</v>
+        <v>2.438025013868719e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049879941156003e-05</v>
+        <v>2.049879941156239e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.429457986998723e-05</v>
+        <v>2.429457986998726e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>2.462476263207602e-05</v>
+        <v>2.462476263207604e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.858378279901226e-05</v>
+        <v>3.458503075156423e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.50369760266364e-05</v>
+        <v>5.503697602663635e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.863090957841955e-05</v>
+        <v>2.863090957841952e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.560167174749483e-05</v>
+        <v>2.167911432434589e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.882760514439064e-05</v>
+        <v>3.882760514439062e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.778091761091848e-05</v>
+        <v>5.778091761091855e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5470,34 +5470,34 @@
         <v>6.53393352656854e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.712490578030578e-05</v>
+        <v>2.71249057803058e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.331097007930846e-05</v>
+        <v>2.331097007930864e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.712225822901706e-05</v>
+        <v>2.712225822901705e-05</v>
       </c>
       <c r="F7" t="n">
         <v>2.712225822901706e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.707535984353495e-05</v>
+        <v>3.707535984353501e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.32965670049716e-05</v>
+        <v>5.32965670049715e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.712248662294218e-05</v>
+        <v>2.71224866229422e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.403858587612007e-05</v>
+        <v>2.403858587612011e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.108352413827057e-05</v>
+        <v>4.108352413827066e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.00743595368126e-05</v>
+        <v>6.007435953681259e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5507,22 +5507,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.319554039566983e-05</v>
+        <v>7.319554039566986e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>4.330314232678663e-05</v>
+        <v>4.330314232678671e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.121516409744226e-05</v>
+        <v>4.121516409744244e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>4.102690874720776e-05</v>
+        <v>4.102690874720782e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>3.524416465215698e-05</v>
+        <v>3.524416465215699e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.325266727923504e-05</v>
+        <v>5.325266727923513e-05</v>
       </c>
       <c r="H8" t="n">
         <v>6.947387444067081e-05</v>
@@ -5531,13 +5531,13 @@
         <v>4.329979405864235e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.02175286461936e-05</v>
+        <v>4.021752864619367e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.878516052093322e-05</v>
+        <v>4.878516052093324e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.494375412945752e-05</v>
+        <v>8.494375412945756e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.190548879903409e-05</v>
+        <v>8.190548879903419e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.972162660125308e-05</v>
+        <v>4.972162660125315e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.590914525297367e-05</v>
+        <v>4.590914525297361e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.668076716984335e-05</v>
+        <v>5.668076716984342e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.972162027157875e-05</v>
+        <v>4.972162027157876e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.967208066448238e-05</v>
+        <v>5.96720806644824e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>7.589328782591898e-05</v>
+        <v>7.5893287825919e-05</v>
       </c>
       <c r="I9" t="n">
         <v>4.971920744388958e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.663530669706744e-05</v>
+        <v>4.663530669706747e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>5.608668363330198e-05</v>
+        <v>6.018611165735115e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.267108035775988e-05</v>
+        <v>8.267108035775992e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.427848138961908e-05</v>
+        <v>1.303476151884155e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>5.749843207677306e-05</v>
+        <v>1.324793014651292e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>2.621875270823039e-05</v>
+        <v>9.979193314249374e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.789670359564667e-05</v>
+        <v>1.360949343395519e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>5.669406619235078e-05</v>
+        <v>1.26088184042447e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>4.741388824073073e-05</v>
+        <v>1.109465120039501e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>6.892493109744947e-05</v>
+        <v>1.222271642245763e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>5.536108621204442e-05</v>
+        <v>1.151362559142755e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.411636720874567e-05</v>
+        <v>1.308141803743823e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>5.835056040342776e-05</v>
+        <v>1.389205355541622e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>8.435868435779243e-05</v>
+        <v>1.305762119976556e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.681510049938311e-05</v>
+        <v>3.662682994379204e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>6.568853204671545e-05</v>
+        <v>2.868391125146181e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>3.003438547922281e-05</v>
+        <v>1.492913785000422e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>6.609180428587258e-05</v>
+        <v>2.92630325666843e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>6.488916688257671e-05</v>
+        <v>2.761099862807209e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>5.441318190069683e-05</v>
+        <v>2.287126423352183e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>7.916579631672203e-05</v>
+        <v>3.102724969878666e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.357534255841486e-05</v>
+        <v>2.580135606488941e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.86007413795537e-05</v>
+        <v>2.137334054240586e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>6.656461405273248e-05</v>
+        <v>2.972636264605146e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.690637032508762e-05</v>
+        <v>3.6962907530611e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.41369701732989e-05</v>
+        <v>5.413697017329898e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.696278218980335e-05</v>
+        <v>3.696278218980337e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.962292167161051e-05</v>
+        <v>1.962292167161053e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.698481970963898e-05</v>
+        <v>3.698481970963906e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>3.698481970963898e-05</v>
+        <v>3.698481970963904e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.220954633904546e-05</v>
+        <v>3.220954633904538e-05</v>
       </c>
       <c r="H4" t="n">
         <v>4.500536265968994e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.687231036809419e-05</v>
+        <v>3.687231036809418e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.226952289442275e-05</v>
+        <v>2.226952289442276e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.703004807083523e-05</v>
+        <v>3.703004807083531e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.417825488904211e-05</v>
+        <v>5.417825488904219e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0007470584791671507</v>
+        <v>0.000747058479167152</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004591226193033837</v>
+        <v>0.0004591226193033833</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001936514680174012</v>
+        <v>0.0001936514680174013</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004591226189657525</v>
+        <v>0.0004591226189657529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0004591226189657525</v>
+        <v>0.0004591226189657529</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004066619000692809</v>
+        <v>0.0004066619000692817</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0006756444268953894</v>
+        <v>0.0006756444268953889</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004591235340230465</v>
+        <v>0.0004591235340230474</v>
       </c>
       <c r="J5" t="n">
         <v>0.000260112434042258</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004411219528848325</v>
+        <v>0.0004411219528848326</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008984817147192882</v>
+        <v>0.0002590622450451358</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.622400803289763e-05</v>
+        <v>5.622400803289777e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.915792458722099e-05</v>
+        <v>3.915792458722095e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.565704813691936e-05</v>
+        <v>2.136279440772934e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.904287643496789e-05</v>
+        <v>3.904287643496779e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.907678189895422e-05</v>
+        <v>3.907678189895416e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.42965841986442e-05</v>
+        <v>3.823938229598209e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.125456745395323e-05</v>
+        <v>5.125456745395325e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>4.290214632503105e-05</v>
+        <v>3.895934822769298e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.453236716661043e-05</v>
+        <v>2.83452113168793e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.931666530498286e-05</v>
+        <v>3.931666530498287e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.646564793640442e-05</v>
+        <v>5.646564793640448e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5863,16 +5863,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.847830100615513e-05</v>
+        <v>5.847830100615526e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>4.121272648128606e-05</v>
+        <v>4.121272648128595e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.396277115115245e-05</v>
+        <v>2.396277115115243e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>4.122973443332672e-05</v>
+        <v>4.122973443332673e-05</v>
       </c>
       <c r="F7" t="n">
         <v>4.122973443332672e-05</v>
@@ -5881,19 +5881,19 @@
         <v>3.655087717190161e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.93466934925462e-05</v>
+        <v>4.934669349254625e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>4.121364120095048e-05</v>
+        <v>4.121364120095041e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.661085372727898e-05</v>
+        <v>2.6610853727279e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.13713789036915e-05</v>
+        <v>4.137137890369152e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.851958572189843e-05</v>
+        <v>5.851958572189838e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.622525851871992e-05</v>
+        <v>6.62252585187201e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>5.730421186060648e-05</v>
+        <v>5.730421186060645e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.176216546541563e-05</v>
+        <v>4.176216546541571e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>5.502496705776205e-05</v>
+        <v>5.502496705776199e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>4.923459572260864e-05</v>
+        <v>4.923459572260857e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.262259653287268e-05</v>
+        <v>5.262259653287275e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>6.541841285351712e-05</v>
+        <v>6.541841285351716e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>5.728536056192159e-05</v>
+        <v>5.728536056192156e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.268420914154342e-05</v>
+        <v>4.268420914154345e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.896369969107417e-05</v>
+        <v>4.896369969107422e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.328721493789641e-05</v>
+        <v>8.328721493789652e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.404899144018268e-05</v>
+        <v>7.404899144018273e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>6.257049079635093e-05</v>
+        <v>6.257049079635094e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.532201820471846e-05</v>
+        <v>4.532201820471847e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>6.924864428592043e-05</v>
+        <v>6.924864428592038e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>6.25704840763785e-05</v>
+        <v>6.257048407637843e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.790864148696662e-05</v>
+        <v>5.790864148696658e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>7.070445780761109e-05</v>
+        <v>7.070445780761114e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>6.25714055160154e-05</v>
+        <v>6.257140551601539e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.796861804234395e-05</v>
+        <v>4.796861804234397e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>5.937609046710079e-05</v>
+        <v>5.937609046710083e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>7.987735003696333e-05</v>
+        <v>7.98773500369634e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.474982453879929e-05</v>
+        <v>5.611574896293885e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>8.981860666573743e-06</v>
+        <v>6.054714258577602e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150061356632056e-05</v>
+        <v>5.440575376265112e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.322785319812062e-06</v>
+        <v>6.348255342573665e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.318001689061926e-06</v>
+        <v>5.512255541763187e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5738229361746e-05</v>
+        <v>5.663592678995471e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>2.863401088573988e-05</v>
+        <v>6.341945756421682e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>7.996985790602259e-06</v>
+        <v>5.256742403221318e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.95563913612594e-05</v>
+        <v>7.744936898830573e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>1.429597153220776e-05</v>
+        <v>6.43379165208948e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>3.155981074293445e-05</v>
+        <v>6.505062065789903e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.68422621923002e-05</v>
+        <v>8.567364258039663e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.00565736138359e-05</v>
+        <v>7.376884301853954e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.310499650192445e-05</v>
+        <v>7.349832936311985e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>1.040248520493738e-05</v>
+        <v>7.852538886136056e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.397701574187256e-06</v>
+        <v>6.472339505623507e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.797913248613117e-05</v>
+        <v>8.938623466247355e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>3.282263161860864e-05</v>
+        <v>1.37834953571724e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.083499158821286e-06</v>
+        <v>6.048683277881515e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>2.20085745006217e-05</v>
+        <v>1.27985742075003e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.615724653970873e-05</v>
+        <v>9.480098464274932e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>3.617691086313219e-05</v>
+        <v>1.494116895743677e-05</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.06783067897761e-05</v>
+        <v>1.067830678977612e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>6.481971657560941e-06</v>
+        <v>6.481971657560936e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>8.746788547385521e-06</v>
+        <v>8.746788547385513e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>6.495843973165345e-06</v>
+        <v>6.495843973165334e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>6.495843973165349e-06</v>
+        <v>6.495843973165334e-06</v>
       </c>
       <c r="G4" t="n">
         <v>1.124779754188914e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.892913464936903e-05</v>
+        <v>1.892913464936902e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>6.552817569568555e-06</v>
+        <v>6.552817569568544e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.210203028445494e-05</v>
+        <v>1.210203028445493e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>9.763460869154545e-06</v>
+        <v>9.763460869154557e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>2.066832503904277e-05</v>
+        <v>2.066832503904278e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,16 +6179,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001156659386869445</v>
+        <v>0.0001156659386869449</v>
       </c>
       <c r="C5" t="n">
-        <v>4.742850083979166e-05</v>
+        <v>4.742850083979159e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.075825007763929e-05</v>
+        <v>8.075825007763938e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.742850227463946e-05</v>
+        <v>4.742850227463945e-05</v>
       </c>
       <c r="F5" t="n">
         <v>4.742850227463946e-05</v>
@@ -6197,19 +6197,19 @@
         <v>0.0001267606535000878</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002732958085982467</v>
+        <v>0.0002732958085982468</v>
       </c>
       <c r="I5" t="n">
-        <v>4.742730687254408e-05</v>
+        <v>4.742730687254401e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001526978094722705</v>
+        <v>0.0001526978094722707</v>
       </c>
       <c r="K5" t="n">
-        <v>9.829509644418319e-05</v>
+        <v>9.829509644418346e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003337766901353727</v>
+        <v>0.0003337766901353726</v>
       </c>
     </row>
     <row r="6">
@@ -6219,31 +6219,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.141831147641414e-05</v>
+        <v>1.377429231307329e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>7.162527431079363e-06</v>
+        <v>7.162527431079366e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.186960005175791e-05</v>
+        <v>1.186960005175787e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>7.122863092090755e-06</v>
+        <v>7.122863092090753e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>7.284532498031556e-06</v>
+        <v>7.284532498031554e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.198780222852719e-05</v>
+        <v>1.434378306518631e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.218038253905313e-05</v>
+        <v>1.974452025901032e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>7.292822256206614e-06</v>
+        <v>9.648803092865707e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.522105275266358e-05</v>
+        <v>1.522105275266357e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.051165407579541e-05</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.369460813795962e-05</v>
+        <v>1.369460813795961e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.570312884999663e-06</v>
+        <v>9.570312884999647e-06</v>
       </c>
       <c r="D7" t="n">
         <v>1.176155724346962e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>9.570842859555257e-06</v>
+        <v>9.570842859555259e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.570842859555257e-06</v>
+        <v>9.570842859555262e-06</v>
       </c>
       <c r="G7" t="n">
         <v>1.426409889007266e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.194543599755256e-05</v>
+        <v>2.194543599755255e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.569118917752088e-06</v>
+        <v>9.569118917752062e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.511833163263844e-05</v>
+        <v>1.511833163263843e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.277976221733806e-05</v>
+        <v>1.277976221733805e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.368462638722635e-05</v>
+        <v>2.368462638722631e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.081302131104494e-05</v>
+        <v>2.081302131104497e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.350627204828417e-05</v>
+        <v>2.350627204828414e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.71081508277856e-05</v>
+        <v>2.710815082778556e-05</v>
       </c>
       <c r="E8" t="n">
         <v>2.164195216229738e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.690594303341487e-05</v>
+        <v>1.690594303341486e-05</v>
       </c>
       <c r="G8" t="n">
         <v>2.819628054085306e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.587761764833284e-05</v>
+        <v>3.587761764833282e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.35013005685325e-05</v>
+        <v>2.350130056853248e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.905185238430955e-05</v>
+        <v>2.905185238430948e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.977160614276348e-05</v>
+        <v>1.97716061427635e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>4.47343589711155e-05</v>
+        <v>4.473435897111545e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6339,31 +6339,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.603203684914398e-05</v>
+        <v>2.603203684914395e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.631680361261222e-05</v>
+        <v>2.631680361261218e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.85095808176643e-05</v>
+        <v>2.850958081766432e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.140476432587245e-05</v>
+        <v>3.140476432587249e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.631680106573513e-05</v>
+        <v>2.631680106573512e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.101058961768518e-05</v>
+        <v>3.101058961768515e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.869192672516506e-05</v>
+        <v>3.869192672516507e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.631560964536458e-05</v>
+        <v>2.631560964536457e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.186482236025093e-05</v>
+        <v>3.186482236025097e-05</v>
       </c>
       <c r="K9" t="n">
         <v>2.697162517871444e-05</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.609181476329582e-06</v>
+        <v>4.25153122165063e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.670609126658843e-06</v>
+        <v>5.108450981399838e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.752379852030127e-06</v>
+        <v>4.311695481588892e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.96748557521798e-06</v>
+        <v>5.359698161806719e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.088666186825708e-06</v>
+        <v>4.628542463947673e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.348200482727361e-06</v>
+        <v>4.343052337987406e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.883287477215858e-06</v>
+        <v>4.313130891597899e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.689489369551336e-06</v>
+        <v>4.309006465116446e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>9.97180256097961e-06</v>
+        <v>6.251153581677886e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.199843295497749e-06</v>
+        <v>5.015431695117575e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.54365830493989e-06</v>
+        <v>4.298907799266124e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.159112476933095e-06</v>
+        <v>4.318763352898118e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.379839628622392e-06</v>
+        <v>6.054380024414111e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>6.474027421818794e-06</v>
+        <v>4.749220623234083e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.681458344658468e-06</v>
+        <v>6.46590962605693e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.802638956266114e-06</v>
+        <v>5.258777681013128e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.159344570992564e-06</v>
+        <v>4.971012878658787e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>6.634879357603021e-06</v>
+        <v>4.798016963950279e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>6.414701972499444e-06</v>
+        <v>4.729432694315135e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09964029314616e-05</v>
+        <v>8.530834715075564e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.857673788908373e-06</v>
+        <v>5.786750232674453e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>6.234373922661241e-06</v>
+        <v>4.672798442254763e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.444834969288296e-06</v>
+        <v>4.444834969288316e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.979311399524974e-06</v>
+        <v>4.97931139952497e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.124417962217904e-06</v>
+        <v>5.124417962217917e-06</v>
       </c>
       <c r="E4" t="n">
         <v>4.98806602039235e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.988066020392348e-06</v>
+        <v>4.988066020392353e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.463110398292016e-06</v>
+        <v>5.463110398292054e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.202556693160522e-06</v>
+        <v>5.202556693160536e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.993933316308552e-06</v>
+        <v>4.993933316308542e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>6.323379553336006e-06</v>
+        <v>6.323379553336012e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.871856430323616e-06</v>
+        <v>4.871856430323619e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.0009919924422e-06</v>
+        <v>5.000991992442212e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6578,34 +6578,34 @@
         <v>1.626173964425029e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.788550829439568e-05</v>
+        <v>2.788550829439569e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.883161385769561e-05</v>
+        <v>2.883161385769564e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.78855092027489e-05</v>
+        <v>2.788550920274892e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.78855092027489e-05</v>
+        <v>2.788550920274892e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.404244939760971e-05</v>
+        <v>3.404244939761019e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.275634324331232e-05</v>
+        <v>3.275634324331236e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.788528503720206e-05</v>
+        <v>2.788528503720204e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.891300007973681e-05</v>
+        <v>4.891300007973684e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.361680203725144e-05</v>
+        <v>2.361680203725142e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.567021932401807e-05</v>
+        <v>1.567021932401809e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.638758275358274e-06</v>
+        <v>6.638758275358278e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>5.447490484941436e-06</v>
+        <v>5.447490484941444e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.599508455761945e-06</v>
+        <v>5.599508743383474e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.419507701071475e-06</v>
+        <v>5.419507701071471e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.468682728105326e-06</v>
+        <v>5.468682728105321e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>5.934704723963588e-06</v>
+        <v>7.657033704361992e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>5.678243380785157e-06</v>
+        <v>7.495992786315948e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>5.465527641980103e-06</v>
+        <v>7.187856622378507e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>8.521082432828972e-06</v>
+        <v>6.84979234252379e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>5.33802806971754e-06</v>
+        <v>5.338028069717551e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>5.475767334804345e-06</v>
+        <v>5.475767334804357e-06</v>
       </c>
     </row>
     <row r="7">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.877067053392145e-06</v>
+        <v>6.877067053392156e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.426388657606006e-06</v>
+        <v>7.426388657606002e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.555224689249148e-06</v>
+        <v>7.555224689249154e-06</v>
       </c>
       <c r="E7" t="n">
         <v>7.429539627937818e-06</v>
@@ -6670,22 +6670,22 @@
         <v>7.429539627937818e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.895342482395862e-06</v>
+        <v>7.895342482395886e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.634788777264345e-06</v>
+        <v>7.634788777264364e-06</v>
       </c>
       <c r="I7" t="n">
         <v>7.426165400412367e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>8.75561163743982e-06</v>
+        <v>8.755611637439837e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.304088514427454e-06</v>
+        <v>7.304088514427457e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.433224076546028e-06</v>
+        <v>7.433224076546041e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.315077546971369e-05</v>
+        <v>1.315077546971371e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.952074614232303e-05</v>
+        <v>1.9520746142323e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.085076855788208e-05</v>
+        <v>2.08507685578821e-05</v>
       </c>
       <c r="E8" t="n">
         <v>1.79294602438419e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.388714430024886e-05</v>
+        <v>1.388714430024885e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.998374607080061e-05</v>
+        <v>1.998374607080059e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.972319236566915e-05</v>
+        <v>1.972319236566914e-05</v>
       </c>
       <c r="I8" t="n">
         <v>1.951456898881706e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.084515798017137e-05</v>
+        <v>2.084515798017138e-05</v>
       </c>
       <c r="K8" t="n">
         <v>1.346978598266405e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.559556298917224e-05</v>
+        <v>2.559556298917227e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.581479997630887e-05</v>
+        <v>1.581479997630888e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.963173717600833e-05</v>
+        <v>1.963173717600837e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.97619992291642e-05</v>
+        <v>1.976199922916423e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.34024970574417e-05</v>
+        <v>2.340249705744173e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.963173749226206e-05</v>
+        <v>1.963173749226208e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.010069100079818e-05</v>
+        <v>2.010069100079823e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.984013729566669e-05</v>
+        <v>1.984013729566673e-05</v>
       </c>
       <c r="I9" t="n">
         <v>1.963151391881473e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.096096015584218e-05</v>
+        <v>2.096096015584221e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.753935566031022e-05</v>
+        <v>1.761616800335551e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.96385725949484e-05</v>
+        <v>1.963857259494843e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.886406197238557e-06</v>
+        <v>4.249827610241904e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>7.563131361780123e-06</v>
+        <v>5.158855744710395e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.772177573468281e-06</v>
+        <v>4.2438159846492e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.852836674783911e-06</v>
+        <v>5.403598843233459e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.992885863945375e-06</v>
+        <v>4.68814855380179e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.848816905066047e-06</v>
+        <v>4.300477374293239e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.828183774819421e-06</v>
+        <v>4.294404122884953e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.557155799166596e-06</v>
+        <v>4.338389502284985e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.339254419668408e-06</v>
+        <v>6.077778498459387e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.734409584023117e-06</v>
+        <v>4.975552352929829e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.960820586377636e-06</v>
+        <v>4.412046953473473e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.476093409108954e-06</v>
+        <v>4.415751616498853e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.400663414874919e-06</v>
+        <v>6.404980595592875e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.344706829385019e-06</v>
+        <v>4.37548228779893e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>8.695290965943426e-06</v>
+        <v>6.8065061555392e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.835340155104889e-06</v>
+        <v>5.625299005127015e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.58306508588808e-06</v>
+        <v>4.777375847947076e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>6.569320917736269e-06</v>
+        <v>4.769668723568191e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.411987462857727e-06</v>
+        <v>5.046065899386197e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.970113017885811e-06</v>
+        <v>7.513839634675274e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.320268593292581e-06</v>
+        <v>5.607644255148303e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.012570669092389e-06</v>
+        <v>5.578614740413729e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.649856817730441e-06</v>
+        <v>4.649856817730433e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.54858854127616e-06</v>
+        <v>5.548588541276161e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.581952741176393e-06</v>
+        <v>4.58195274117639e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.557484376912337e-06</v>
+        <v>5.557484376912347e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.557484376912345e-06</v>
+        <v>5.557484376912347e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.206947511123581e-06</v>
+        <v>5.206947511123564e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.209919240049613e-06</v>
+        <v>5.209919240049616e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.553318163289347e-06</v>
+        <v>5.553318163289356e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.812796096621979e-06</v>
+        <v>4.812796096621974e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.634706378879815e-06</v>
+        <v>4.634706378879814e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>6.477424520684165e-06</v>
+        <v>6.47742452068416e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.910166202739162e-05</v>
+        <v>1.910166202739161e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.578741894556948e-05</v>
+        <v>3.578741894557012e-05</v>
       </c>
       <c r="D5" t="n">
         <v>1.9266677015571e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.578741977318598e-05</v>
+        <v>3.578741977318635e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.578741977318598e-05</v>
+        <v>3.578741977318635e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.927501044767094e-05</v>
+        <v>2.927501044767068e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.162300522320355e-05</v>
+        <v>3.162300522320353e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.578738214655366e-05</v>
+        <v>3.578738214655375e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.280152541297376e-05</v>
+        <v>2.280152541297377e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.951251243601734e-05</v>
+        <v>1.95125124360173e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.541016001141043e-05</v>
+        <v>2.837993264535931e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.116636642490048e-06</v>
+        <v>5.116636642490041e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.024432365160365e-06</v>
+        <v>6.024432365160348e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.036887265552843e-06</v>
+        <v>5.036887265552839e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.996313225418408e-06</v>
+        <v>5.996313225418413e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.028604407445223e-06</v>
+        <v>6.028604407445236e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.421067353024297e-06</v>
+        <v>5.673727335883191e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>7.510493467035983e-06</v>
+        <v>7.510493467036001e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.020097988048967e-06</v>
+        <v>6.020097988048965e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>7.012053421169423e-06</v>
+        <v>5.326380460579607e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>5.090739985606872e-06</v>
+        <v>5.090739985606881e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>6.955882673178632e-06</v>
+        <v>6.955882673178644e-06</v>
       </c>
     </row>
     <row r="7">
@@ -7051,34 +7051,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.067240242280696e-06</v>
+        <v>7.06724024228069e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.970738386856002e-06</v>
+        <v>7.97073838685599e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>6.997910226264507e-06</v>
+        <v>6.997910226264499e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.974552918697373e-06</v>
+        <v>7.974552918697369e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.974552918697373e-06</v>
+        <v>7.974552918697369e-06</v>
       </c>
       <c r="G7" t="n">
         <v>7.624330935673844e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.627302664599895e-06</v>
+        <v>7.627302664599884e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.970701587839616e-06</v>
+        <v>7.970701587839614e-06</v>
       </c>
       <c r="J7" t="n">
         <v>7.230179521172228e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.052089803430079e-06</v>
+        <v>7.052089803430068e-06</v>
       </c>
       <c r="L7" t="n">
         <v>8.894807945234428e-06</v>
@@ -7091,22 +7091,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.330967481031292e-05</v>
+        <v>1.330967481031293e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.000776911199038e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.022996470584042e-05</v>
+        <v>2.022996470584046e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.842371353502715e-05</v>
+        <v>1.842371353502719e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.439977052683627e-05</v>
+        <v>1.439977052683626e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.965477748588927e-05</v>
+        <v>1.965477748588925e-05</v>
       </c>
       <c r="H8" t="n">
         <v>1.965774921481613e-05</v>
@@ -7115,13 +7115,13 @@
         <v>2.000114813805506e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.926176358162428e-05</v>
+        <v>1.926176358162427e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.31870090773352e-05</v>
+        <v>1.318700907733521e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.697131699653659e-05</v>
+        <v>2.697131699653655e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.532384527206636e-05</v>
+        <v>1.532384527206634e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.930362488173625e-05</v>
+        <v>1.930362488173623e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.833222306687838e-05</v>
+        <v>1.833222306687836e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.285358898455642e-05</v>
+        <v>2.28535889845564e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.930362516928096e-05</v>
+        <v>1.930362516928095e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.895721743055408e-05</v>
+        <v>1.895721743055407e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.896018915948014e-05</v>
+        <v>1.896018915948013e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.930358808271989e-05</v>
+        <v>1.930358808271988e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.856306601605248e-05</v>
+        <v>1.856306601605246e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.653025228980593e-05</v>
+        <v>1.653025228980591e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.022769444011467e-05</v>
+        <v>2.022769444011465e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.455381063605283e-05</v>
+        <v>1.05039691345961e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.894676363974634e-05</v>
+        <v>8.848905555385009e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>2.481626151198043e-05</v>
+        <v>8.412660849325788e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.935028803664269e-05</v>
+        <v>9.208801128604186e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.815859866674576e-05</v>
+        <v>8.217240628322382e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.06620401411111e-05</v>
+        <v>9.246592706325652e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.980514127846337e-05</v>
+        <v>1.131469362059884e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.794823970873342e-05</v>
+        <v>8.0516291754714e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>2.955062865619615e-05</v>
+        <v>1.072341674081306e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>4.052573755392844e-05</v>
+        <v>1.066027224871073e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>7.987647328404937e-05</v>
+        <v>1.133191194273542e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.416822861252702e-05</v>
+        <v>2.841639637059071e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.15557316347635e-05</v>
+        <v>1.233514548284616e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>2.846181551134131e-05</v>
+        <v>1.355838925303969e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.196541100493841e-05</v>
+        <v>1.290672149046735e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.077372163504146e-05</v>
+        <v>1.126973163167851e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>4.668774337799585e-05</v>
+        <v>1.950216249790586e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>9.17214093341075e-05</v>
+        <v>3.422210889633797e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.056075906862977e-05</v>
+        <v>1.099449660240173e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.351017861736722e-05</v>
+        <v>1.801123091958512e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>4.625725816070823e-05</v>
+        <v>2.126147577012818e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>9.179127065246735e-05</v>
+        <v>3.444107192985705e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.090102365833259e-05</v>
+        <v>4.090102365833258e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.284886737985339e-05</v>
+        <v>1.284886737985334e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.727873452686263e-05</v>
+        <v>1.727873452686262e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.287751879936094e-05</v>
+        <v>1.287751879936092e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.287751879936093e-05</v>
+        <v>1.287751879936091e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.667463922394794e-05</v>
+        <v>2.667463922394788e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.995859278397665e-05</v>
+        <v>4.995859278397646e-05</v>
       </c>
       <c r="I4" t="n">
         <v>1.304509929763331e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.852140037155828e-05</v>
+        <v>1.852140037155825e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.553412558753705e-05</v>
+        <v>2.553412558753704e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.000250270005009e-05</v>
+        <v>5.000250270005002e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0006123996312805865</v>
+        <v>0.0006123996312805864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001333032165820017</v>
+        <v>0.0001333032165820013</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002034389512479539</v>
+        <v>0.0002034389512479537</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001333032194023082</v>
+        <v>0.0001333032194023081</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001333032194023082</v>
+        <v>0.0001333032194023081</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003770494808575432</v>
+        <v>0.0003770494808575419</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0008247195433560109</v>
+        <v>0.000824719543356011</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001332999667336189</v>
+        <v>0.0001332999667336188</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002463645770071684</v>
+        <v>0.0002463645770071681</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003502048160412145</v>
+        <v>0.0003502048160412139</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009244823625855813</v>
+        <v>0.0001232049292870906</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.23262400852156e-05</v>
+        <v>4.232624008521557e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.407338621462114e-05</v>
+        <v>1.40733862146211e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.851568507032061e-05</v>
+        <v>1.851568507032096e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.400783632274918e-05</v>
+        <v>1.400783632274916e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.441161150061188e-05</v>
+        <v>1.441161150061186e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.181053487806584e-05</v>
+        <v>3.181053487806575e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.538050660050305e-05</v>
+        <v>5.538050660050291e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.818099495175122e-05</v>
+        <v>1.818099495175113e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.373148827105782e-05</v>
+        <v>2.373148827105778e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.704586706474237e-05</v>
+        <v>2.704586706474213e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.162161048514952e-05</v>
+        <v>5.162161048514942e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.49017565997638e-05</v>
+        <v>4.490175659976368e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.704908208744724e-05</v>
+        <v>1.704908208744721e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.127792788289488e-05</v>
+        <v>2.127792788289483e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.704221551662133e-05</v>
+        <v>1.704221551662128e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.704221551662133e-05</v>
+        <v>1.704221551662128e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.067537216537914e-05</v>
+        <v>3.067537216537907e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.39593257254078e-05</v>
+        <v>5.395932572540772e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.704583223906452e-05</v>
+        <v>1.704583223906447e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.25221333129895e-05</v>
+        <v>2.252213331298942e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.953485852896826e-05</v>
+        <v>2.953485852896822e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.400323564148125e-05</v>
+        <v>5.400323564148108e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.293028001196986e-05</v>
+        <v>5.293028001196972e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.328712965770362e-05</v>
+        <v>3.328712965768518e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.922345473469615e-05</v>
+        <v>3.922345473469608e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.104098163338442e-05</v>
+        <v>3.104098163338429e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.533475367414005e-05</v>
+        <v>2.533475367413997e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.691643573121349e-05</v>
+        <v>4.691643573121331e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.020038929124331e-05</v>
+        <v>7.020038929124311e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.328689580489877e-05</v>
+        <v>3.328689580489868e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.876481087809058e-05</v>
+        <v>3.876481087809047e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.741082979153429e-05</v>
+        <v>3.741082979153419e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.882298411900493e-05</v>
+        <v>7.882298411900466e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.230584232267165e-05</v>
+        <v>6.230584232267151e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.062056429405423e-05</v>
+        <v>4.062056429405404e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.485094986143572e-05</v>
+        <v>4.485094986143559e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.773759849690913e-05</v>
+        <v>4.773759849690918e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.062055626767771e-05</v>
+        <v>4.062055626767788e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.424685437198608e-05</v>
+        <v>5.424685437198585e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>7.753080793201468e-05</v>
+        <v>7.753080793201458e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.061731444567141e-05</v>
+        <v>4.061731444567132e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.609361551959645e-05</v>
+        <v>4.609361551959621e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.953292707014741e-05</v>
+        <v>4.953292707014727e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>7.757471784808809e-05</v>
+        <v>7.757471784808786e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.407105974897548e-06</v>
+        <v>5.549673665586068e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>7.602301758685784e-06</v>
+        <v>6.307625939525108e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.860820676678518e-05</v>
+        <v>6.244421380765071e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>7.952101415197647e-06</v>
+        <v>6.611823520942342e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.918426067462394e-06</v>
+        <v>5.7517794933751e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.214803893549439e-05</v>
+        <v>6.430715717131272e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.491335337294451e-05</v>
+        <v>6.036174160469625e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.748377126117802e-06</v>
+        <v>5.620743775885512e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.271492619918667e-05</v>
+        <v>7.729334844686709e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>9.657210440905515e-06</v>
+        <v>6.417634881535111e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.129281189361702e-05</v>
+        <v>7.982016555616028e-06</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.09776762910747e-06</v>
+        <v>5.336902618776092e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>8.49023515521434e-06</v>
+        <v>6.993604551244154e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1281768139569e-05</v>
+        <v>1.026302659544318e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>8.845606344214839e-06</v>
+        <v>7.482536331542228e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>7.811930996479581e-06</v>
+        <v>6.062644718315214e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.535330840760929e-05</v>
+        <v>1.15965387243569e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.704295925980814e-05</v>
+        <v>8.893264464078428e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>7.64474690296008e-06</v>
+        <v>5.844466040224502e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.415747852230373e-05</v>
+        <v>1.038040722049303e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.086215464459825e-05</v>
+        <v>7.751481072540826e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.887494596810428e-05</v>
+        <v>2.265811039632743e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.107433832023085e-06</v>
+        <v>5.10743383202309e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.64948236541713e-06</v>
+        <v>5.649482365417139e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.295492887470902e-05</v>
+        <v>1.295492887470901e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>5.66817306581005e-06</v>
+        <v>5.668173065810081e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.668173065810051e-06</v>
+        <v>5.668173065810077e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.503849381759412e-05</v>
+        <v>1.503849381759411e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.07604440400282e-05</v>
+        <v>1.076044404002819e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.774860856089206e-06</v>
+        <v>5.774860856089209e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.083105391013581e-06</v>
+        <v>8.083105391013571e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.142750958654705e-06</v>
+        <v>7.142750958654692e-06</v>
       </c>
       <c r="L4" t="n">
         <v>3.237892307097633e-05</v>
@@ -7766,10 +7766,10 @@
         <v>1.59874877526823e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.022500012367992e-05</v>
+        <v>3.022500012367991e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001380317218691261</v>
+        <v>0.0001380317218691262</v>
       </c>
       <c r="E5" t="n">
         <v>3.022500210179997e-05</v>
@@ -7781,19 +7781,19 @@
         <v>0.0001772602000440797</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001151761676478012</v>
+        <v>0.0001151761676478015</v>
       </c>
       <c r="I5" t="n">
-        <v>3.022276044167296e-05</v>
+        <v>3.022276044167293e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>6.874591871651945e-05</v>
+        <v>6.874591871651929e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.849615937666799e-05</v>
+        <v>4.8496159376668e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>6.577248608702113e-05</v>
+        <v>0.0005354948745797985</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.379151540387239e-06</v>
+        <v>8.379151540387234e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.259875739549053e-06</v>
+        <v>6.259875739549043e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.371218092490851e-05</v>
+        <v>1.3712174841453e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>6.225558515833183e-06</v>
+        <v>6.225558515833173e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.461995810039401e-06</v>
+        <v>6.461995810039411e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.574436493597902e-05</v>
+        <v>1.831021152595829e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.417428135352837e-05</v>
+        <v>1.417428135352836e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.04657856445336e-06</v>
+        <v>9.046578564453372e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>8.86828348385847e-06</v>
+        <v>8.868283483858455e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>7.710142856138557e-06</v>
+        <v>7.710142856138545e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>3.32330683184362e-05</v>
+        <v>3.323306831843621e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.101772817037452e-06</v>
+        <v>8.101772817037445e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.771439523110523e-06</v>
+        <v>8.771439523110532e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.594784195894684e-05</v>
+        <v>1.594784195894682e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>8.769017478209157e-06</v>
+        <v>8.769017478209161e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.769017478209157e-06</v>
+        <v>8.769017478209161e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.803283280260845e-05</v>
+        <v>1.803283280260846e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.375478302504257e-05</v>
+        <v>1.375478302504256e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.769199841103552e-06</v>
+        <v>8.769199841103559e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.107744437602793e-05</v>
+        <v>1.107744437602791e-05</v>
       </c>
       <c r="K7" t="n">
         <v>1.013708994366905e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.537326205599071e-05</v>
+        <v>3.537326205599075e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.494977926797018e-05</v>
+        <v>1.494977926797016e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.227429492397311e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.08310979806721e-05</v>
+        <v>3.083109798067205e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.045400044383297e-05</v>
+        <v>2.045400044383294e-05</v>
       </c>
       <c r="F8" t="n">
         <v>1.582977597706682e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.153490006676249e-05</v>
+        <v>3.153490006676248e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.725685028919528e-05</v>
+        <v>2.725685028919525e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.227126710525756e-05</v>
+        <v>2.227126710525754e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.458081935375391e-05</v>
+        <v>2.458081935375388e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.686149379881807e-05</v>
+        <v>1.686149379881805e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.582605224300721e-05</v>
+        <v>5.582605224300719e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.94584030691696e-05</v>
+        <v>1.945840306916958e-05</v>
       </c>
       <c r="C9" t="n">
         <v>2.427115211655042e-05</v>
@@ -7932,28 +7932,28 @@
         <v>3.144898455236229e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.905218463603048e-05</v>
+        <v>2.905218463603047e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.427115222380689e-05</v>
+        <v>2.42711522238069e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.353254539604839e-05</v>
+        <v>3.353254539604841e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.925449561848248e-05</v>
+        <v>2.925449561848246e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.426891243454345e-05</v>
+        <v>2.426891243454346e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.657715696946787e-05</v>
+        <v>2.657715696946784e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.041992126940316e-05</v>
+        <v>2.323628608152839e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.08729746494306e-05</v>
+        <v>5.087297464943059e-05</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia eutrophication freshwater results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication freshwater results.xlsx
@@ -515,28 +515,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.570778702707871e-05</v>
+        <v>1.570778702707873e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.147949003391009e-05</v>
+        <v>1.147949003390995e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>9.843838275849462e-06</v>
+        <v>9.843838275849459e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.188373024162623e-05</v>
+        <v>1.188373024162621e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.076852046677038e-05</v>
+        <v>1.076852046677039e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.101843414366405e-05</v>
+        <v>1.101843414366406e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.311593165682023e-05</v>
+        <v>1.311593165682024e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.024613227131663e-05</v>
+        <v>1.024613227131664e-05</v>
       </c>
       <c r="J2" t="n">
         <v>1.33067223911271e-05</v>
@@ -545,7 +545,7 @@
         <v>1.434055268977168e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.343335717409049e-05</v>
+        <v>1.34333571740905e-05</v>
       </c>
     </row>
     <row r="3">
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.676376663871405e-05</v>
+        <v>5.676376663871406e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.000785023316678e-05</v>
+        <v>2.000785023316672e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.509029372923066e-05</v>
+        <v>1.509029372923065e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.065059224954099e-05</v>
+        <v>2.065059224954098e-05</v>
       </c>
       <c r="F3" t="n">
         <v>1.880949500506249e-05</v>
@@ -573,16 +573,16 @@
         <v>2.347100836623213e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.853758243294182e-05</v>
+        <v>3.853758243294185e-05</v>
       </c>
       <c r="I3" t="n">
         <v>1.794534359946983e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.480610531641515e-05</v>
+        <v>2.480610531641514e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.357417788681089e-05</v>
+        <v>3.357417788681087e-05</v>
       </c>
       <c r="L3" t="n">
         <v>4.075785439206606e-05</v>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.569403166249032e-05</v>
+        <v>8.56940316624904e-05</v>
       </c>
       <c r="C4" t="n">
         <v>2.371232111341032e-05</v>
@@ -604,28 +604,28 @@
         <v>1.945803296765658e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.374510111757816e-05</v>
+        <v>2.374510111757819e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.374510111757817e-05</v>
+        <v>2.374510111757819e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.270446960646537e-05</v>
+        <v>3.270446960646533e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.634315073910026e-05</v>
+        <v>5.634315073910022e-05</v>
       </c>
       <c r="I4" t="n">
         <v>2.386407400509709e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.764740891634932e-05</v>
+        <v>2.764740891634927e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>4.23058176425865e-05</v>
+        <v>4.230581764258645e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.971771766680634e-05</v>
+        <v>5.971771766680633e-05</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001470536052262904</v>
+        <v>0.001470536052262905</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003241519350910874</v>
+        <v>0.0003241519350910886</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002423737592336275</v>
+        <v>0.0002423737592336276</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003241519377304018</v>
+        <v>0.0003241519377304027</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003241519377304018</v>
+        <v>0.0003241519377304027</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005080865145755611</v>
+        <v>0.0005080865145755592</v>
       </c>
       <c r="H5" t="n">
         <v>0.001065262072389385</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003241497698026627</v>
+        <v>0.0003241497698026638</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000420360023233946</v>
+        <v>0.0004203600232339457</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0006809263376697701</v>
+        <v>0.0006809263376697707</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001174452545305074</v>
+        <v>0.001174452545305076</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.782143543200312e-05</v>
+        <v>8.782143543200317e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.568132321001952e-05</v>
+        <v>2.568132321001955e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.116651144898412e-05</v>
+        <v>2.116651144898413e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.557797469389257e-05</v>
+        <v>2.557797469389256e-05</v>
       </c>
       <c r="F6" t="n">
         <v>2.594794757035433e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.93476742736218e-05</v>
+        <v>3.934767427362179e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>6.32335736377052e-05</v>
+        <v>6.323357363770527e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>3.050727867225362e-05</v>
+        <v>3.050727867225357e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.431964490425821e-05</v>
+        <v>3.43196449042582e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.484681259384755e-05</v>
+        <v>4.484681259384699e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>6.205428115070375e-05</v>
+        <v>6.205428115070374e-05</v>
       </c>
     </row>
     <row r="7">
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.066654186356674e-05</v>
+        <v>9.066654186356684e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.883874949459845e-05</v>
+        <v>2.883874949459844e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.442888489488511e-05</v>
+        <v>2.44288848948851e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.883172303254403e-05</v>
+        <v>2.883172303254404e-05</v>
       </c>
       <c r="F7" t="n">
         <v>2.883172303254404e-05</v>
@@ -733,19 +733,19 @@
         <v>3.767697980754177e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>6.131566094017674e-05</v>
+        <v>6.131566094017673e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.883658420617354e-05</v>
+        <v>2.883658420617356e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.261991911742574e-05</v>
+        <v>3.261991911742575e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.727832784366297e-05</v>
+        <v>4.727832784366294e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.469022786788283e-05</v>
+        <v>6.469022786788279e-05</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.974658366118129e-05</v>
+        <v>9.974658366118135e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>4.755962396548615e-05</v>
+        <v>4.755962396548619e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.515381643637232e-05</v>
+        <v>4.515381643637233e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>4.492204264601727e-05</v>
+        <v>4.492204264601731e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>3.822127636641335e-05</v>
+        <v>3.822127636641337e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.640059525654401e-05</v>
+        <v>5.640059525654408e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>8.00392763891793e-05</v>
+        <v>8.00392763891794e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.756019965517581e-05</v>
+        <v>4.756019965517582e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.134542980482719e-05</v>
+        <v>5.134542980482718e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.617923530972316e-05</v>
+        <v>5.617923530972309e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>9.348736237809141e-05</v>
+        <v>9.348736237809149e-05</v>
       </c>
     </row>
     <row r="9">
@@ -795,34 +795,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001146871627170107</v>
+        <v>0.0001146871627170108</v>
       </c>
       <c r="C9" t="n">
-        <v>6.118866243901407e-05</v>
+        <v>6.118866243901405e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>5.678045674579618e-05</v>
+        <v>5.678045674579617e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>7.080047708800898e-05</v>
+        <v>7.080047708800903e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>6.118865305776814e-05</v>
+        <v>6.118865305776818e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>7.002689275195744e-05</v>
+        <v>7.002689275195743e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>9.366557388459236e-05</v>
+        <v>9.366557388459239e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>6.118649715058918e-05</v>
+        <v>6.118649715058919e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>6.496983206184136e-05</v>
+        <v>6.496983206184135e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.914017510820507e-05</v>
+        <v>6.914017510820504e-05</v>
       </c>
       <c r="L9" t="n">
         <v>9.704014081229836e-05</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.487495119932236e-06</v>
+        <v>4.487495119932083e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>5.475092828653056e-06</v>
+        <v>5.475092828653062e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.675065629318302e-06</v>
+        <v>4.675065629318079e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.743394794227629e-06</v>
+        <v>5.743394794227461e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.96343848720271e-06</v>
+        <v>4.96343848720258e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.692230649051629e-06</v>
+        <v>4.69223064905176e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.666141995128379e-06</v>
+        <v>4.666141995128376e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.619197886202236e-06</v>
+        <v>4.619197886202007e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.53615610539605e-06</v>
+        <v>6.536156105395981e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.26700704125067e-06</v>
+        <v>5.267007041250489e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.676611514640637e-06</v>
+        <v>4.676611514640578e-06</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.454665627844304e-06</v>
+        <v>4.454665627844288e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.810408816366463e-06</v>
+        <v>6.810408816366464e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.786915140363948e-06</v>
+        <v>5.786915140363942e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.248946349035013e-06</v>
+        <v>7.248946349034958e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.961259584040696e-06</v>
+        <v>5.96125958404065e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.910861591812218e-06</v>
+        <v>5.910861591812121e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.770860040762221e-06</v>
+        <v>5.770860040762225e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.391138411795318e-06</v>
+        <v>5.39113841179534e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.410138886467364e-06</v>
+        <v>8.410138886467269e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.90188230065384e-06</v>
+        <v>5.90188230065381e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.823339538619724e-06</v>
+        <v>5.823339538619699e-06</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.541596705601725e-06</v>
+        <v>4.541596705601699e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.908966911653507e-06</v>
+        <v>5.90896691165351e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>6.660291895814574e-06</v>
+        <v>6.660291895814554e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.919112804576522e-06</v>
+        <v>5.919112804576497e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.91911280457651e-06</v>
+        <v>5.919112804576497e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>6.838440443559697e-06</v>
+        <v>6.838440443559666e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>6.627971099327561e-06</v>
+        <v>6.627971099327542e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.927515155798222e-06</v>
+        <v>5.927515155798225e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>5.723999217719708e-06</v>
+        <v>5.723999217719681e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.871971789378706e-06</v>
+        <v>4.871971789378685e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>6.698447132357086e-06</v>
+        <v>6.698447132357077e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1034,34 +1034,34 @@
         <v>1.489831593826351e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.929641011172659e-05</v>
+        <v>3.929641011172655e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>4.90280951919375e-05</v>
+        <v>4.902809519193748e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.929641103054188e-05</v>
+        <v>3.929641103054185e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.929641103054188e-05</v>
+        <v>3.929641103054185e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.318721236610587e-05</v>
+        <v>5.318721236610574e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>5.38610506369444e-05</v>
+        <v>5.386105063694432e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.92960846924039e-05</v>
+        <v>3.929608469240404e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.553816424528007e-05</v>
+        <v>3.553816424527991e-05</v>
       </c>
       <c r="K5" t="n">
         <v>2.075275334241418e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>5.703478044387979e-05</v>
+        <v>5.70347804438797e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.041200565203788e-06</v>
+        <v>5.04120056520375e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.405576558661683e-06</v>
+        <v>6.40557655866165e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>9.037703690169969e-06</v>
+        <v>9.037703690169953e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>6.375770871451445e-06</v>
+        <v>6.375770871451388e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.433654035794393e-06</v>
+        <v>6.433654035794359e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>9.185241094022282e-06</v>
+        <v>9.185241094022196e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>9.093107774986437e-06</v>
+        <v>9.09310777498641e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.427119015400286e-06</v>
+        <v>6.427119015400245e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>6.278383484060813e-06</v>
+        <v>6.278383484060803e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>5.332885525542378e-06</v>
+        <v>5.332885525542368e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>7.209681478846184e-06</v>
+        <v>7.209681478846142e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.138822598198779e-06</v>
+        <v>7.138822598198761e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.525066467717932e-06</v>
+        <v>8.525066467717934e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>9.256089968410076e-06</v>
+        <v>9.256089968410059e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>8.528567012293231e-06</v>
+        <v>8.528567012293202e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.528567012293231e-06</v>
+        <v>8.528567012293202e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.435666336156743e-06</v>
+        <v>9.435666336156742e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>9.225196991924621e-06</v>
+        <v>9.225196991924608e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>8.524741048395291e-06</v>
+        <v>8.524741048395223e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>8.321225110316779e-06</v>
+        <v>8.321225110316764e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.469197681975762e-06</v>
+        <v>7.469197681975737e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>9.295673024954139e-06</v>
+        <v>9.295673024954118e-06</v>
       </c>
     </row>
     <row r="8">
@@ -1151,31 +1151,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.354662727343968e-05</v>
+        <v>1.354662727343966e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.097834774656322e-05</v>
+        <v>2.097834774656321e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.295671898517911e-05</v>
+        <v>2.29567189851791e-05</v>
       </c>
       <c r="E8" t="n">
         <v>1.932563680279354e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.512724297467464e-05</v>
+        <v>1.512724297467459e-05</v>
       </c>
       <c r="G8" t="n">
         <v>2.188261225476104e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.167214291052801e-05</v>
+        <v>2.167214291052802e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.097168696699955e-05</v>
+        <v>2.097168696699954e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.076935789329653e-05</v>
+        <v>2.076935789329648e-05</v>
       </c>
       <c r="K8" t="n">
         <v>1.376482220812986e-05</v>
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.575696014758203e-05</v>
+        <v>1.575696014758201e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.038303955041792e-05</v>
+        <v>2.038303955041788e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.111549182443731e-05</v>
+        <v>2.111549182443728e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.412174182456798e-05</v>
+        <v>2.412174182456796e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.038303965618844e-05</v>
+        <v>2.038303965618843e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.129363941885672e-05</v>
+        <v>2.129363941885674e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.108317007462463e-05</v>
+        <v>2.10831700746246e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.038271413109528e-05</v>
+        <v>2.038271413109531e-05</v>
       </c>
       <c r="J9" t="n">
         <v>2.01791981930168e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.744999773382702e-05</v>
+        <v>1.744999773382699e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.115364610765416e-05</v>
+        <v>2.115364610765415e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.027628087210144e-06</v>
+        <v>9.027628087210177e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.066127035980484e-05</v>
+        <v>1.066127035980483e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>8.399483756272279e-06</v>
+        <v>8.399483756272328e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>8.494999409607859e-06</v>
+        <v>8.494999409607921e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.495356414920502e-06</v>
+        <v>8.495356414920558e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>8.957470156388719e-06</v>
+        <v>8.957470156388741e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>9.768674193067619e-06</v>
+        <v>9.768674193067627e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>8.523046332347579e-06</v>
+        <v>8.523046332347577e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.009804034435718e-05</v>
+        <v>1.009804034435716e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>9.832448254289217e-06</v>
+        <v>9.832448254289146e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>8.62792018313862e-06</v>
+        <v>8.627920183138622e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.673046136046668e-05</v>
+        <v>1.673046136046675e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.641561563423438e-05</v>
+        <v>2.641561563423439e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.224774590663362e-05</v>
+        <v>1.224774590663354e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.308652264994524e-05</v>
+        <v>1.308652264994527e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.308687965525793e-05</v>
+        <v>1.308687965525776e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62349494185004e-05</v>
+        <v>1.623494941850043e-05</v>
       </c>
       <c r="H3" t="n">
         <v>2.211119454207998e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.313072330860035e-05</v>
+        <v>1.313072330860029e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.069492325128658e-05</v>
+        <v>2.069492325128662e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.847834220646533e-05</v>
+        <v>1.847834220646529e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.398755801447322e-05</v>
+        <v>1.39875580144732e-05</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.135691294441772e-05</v>
+        <v>2.135691294441774e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>3.593013772499263e-05</v>
+        <v>3.593013772499269e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.426173376580598e-05</v>
+        <v>1.426173376580597e-05</v>
       </c>
       <c r="E4" t="n">
+        <v>1.546535247348164e-05</v>
+      </c>
+      <c r="F4" t="n">
         <v>1.546535247348163e-05</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.546535247348164e-05</v>
       </c>
       <c r="G4" t="n">
         <v>2.054610246798493e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.975544556412704e-05</v>
+        <v>2.975544556412696e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.553828064644814e-05</v>
+        <v>1.553828064644812e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.584606957453024e-05</v>
+        <v>2.584606957453029e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.223711573221284e-05</v>
+        <v>2.223711573221282e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.695540201969002e-05</v>
+        <v>1.695540201968999e-05</v>
       </c>
     </row>
     <row r="5">
@@ -1433,28 +1433,28 @@
         <v>0.000547433223262884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001493508819976453</v>
+        <v>0.0001493508819976452</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001758216780741252</v>
+        <v>0.000175821678074125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001758216780741252</v>
+        <v>0.0001758216780741251</v>
       </c>
       <c r="G5" t="n">
         <v>0.0002693125739814497</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004794998444018606</v>
+        <v>0.000479499844401861</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001758204071767954</v>
+        <v>0.0001758204071767955</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003741677798901792</v>
+        <v>0.0003741677798901789</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0002931629152682987</v>
+        <v>0.0002931629152682993</v>
       </c>
       <c r="L5" t="n">
         <v>0.0002256804863092948</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.616202059433354e-05</v>
+        <v>2.616202059433357e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.79899320396378e-05</v>
+        <v>3.798993203963792e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.583346431987104e-05</v>
+        <v>1.583346431987103e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.701032304462921e-05</v>
+        <v>1.701032304462923e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.725401363931838e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.230611859151192e-05</v>
+        <v>2.230611859151196e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>3.493481777273825e-05</v>
+        <v>3.493481777273823e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.729829676997518e-05</v>
+        <v>1.729829676997519e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>3.079919230251036e-05</v>
+        <v>3.079919230251042e-05</v>
       </c>
       <c r="K6" t="n">
         <v>2.408230831328279e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>1.869247773524869e-05</v>
+        <v>1.869247773524868e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1516,25 +1516,25 @@
         <v>1.810564350789082e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.938230396897279e-05</v>
+        <v>1.938230396897281e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.938230396897279e-05</v>
+        <v>1.938230396897281e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>2.439154188164498e-05</v>
+        <v>2.4391541881645e-05</v>
       </c>
       <c r="H7" t="n">
         <v>3.360088497778703e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.938372006010818e-05</v>
+        <v>1.938372006010817e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.969150898819032e-05</v>
+        <v>2.969150898819029e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.608255514587289e-05</v>
+        <v>2.60825551458729e-05</v>
       </c>
       <c r="L7" t="n">
         <v>2.080084143335004e-05</v>
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.293638753760542e-05</v>
+        <v>3.293638753760541e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>5.521031162245093e-05</v>
+        <v>5.521031162245096e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.537978611178325e-05</v>
+        <v>3.537978611178326e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.285912541464621e-05</v>
+        <v>3.285912541464622e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.736876565375181e-05</v>
+        <v>2.736876565375182e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.002595912650084e-05</v>
+        <v>4.002595912650083e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>4.92353022226509e-05</v>
+        <v>4.923530222265091e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.501813730496408e-05</v>
+        <v>3.501813730496404e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.532747888445094e-05</v>
+        <v>4.5327478884451e-05</v>
       </c>
       <c r="K8" t="n">
         <v>3.366983667248121e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>4.468786836462032e-05</v>
+        <v>4.468786836462024e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.039800931688671e-05</v>
+        <v>4.039800931688667e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>6.02728433109272e-05</v>
+        <v>6.027284331092726e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.880504891966595e-05</v>
+        <v>3.880504891966603e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.643230178433643e-05</v>
+        <v>4.643230178433637e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.008285972070854e-05</v>
+        <v>4.008285972070852e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.508941830819567e-05</v>
+        <v>4.508941830819572e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>5.429876140433777e-05</v>
+        <v>5.429876140433781e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.008159648665889e-05</v>
+        <v>4.008159648665885e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.0389385414741e-05</v>
+        <v>5.038938541474106e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.359242371526062e-05</v>
+        <v>4.359242371526068e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.149871785990077e-05</v>
+        <v>4.149871785990074e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.889935748051137e-06</v>
+        <v>6.889935748051175e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>8.387063664722275e-06</v>
+        <v>8.387063664722245e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.871438646965099e-06</v>
+        <v>6.871438646965116e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.866586663872706e-06</v>
+        <v>6.86658666387273e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>6.86693880273574e-06</v>
+        <v>6.866938802735761e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>7.109939094335877e-06</v>
+        <v>7.109939094335916e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.484033898262197e-06</v>
+        <v>7.484033898262167e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>6.782656358938777e-06</v>
+        <v>6.782656358938791e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.20135948164701e-06</v>
+        <v>8.201359481647012e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>7.192982833866226e-06</v>
+        <v>7.192982833866184e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>6.664011024645704e-06</v>
+        <v>6.664011024645692e-06</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.755314899251208e-06</v>
+        <v>9.75531489925123e-06</v>
       </c>
       <c r="C3" t="n">
         <v>1.884384520882424e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>9.623680635195934e-06</v>
+        <v>9.623680635195944e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>9.13348157047952e-06</v>
+        <v>9.133481570479539e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>9.133833709342552e-06</v>
+        <v>9.133833709342579e-06</v>
       </c>
       <c r="G3" t="n">
         <v>1.132999403452754e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.406662499795157e-05</v>
+        <v>1.406662499795155e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>8.992846110359335e-06</v>
+        <v>8.992846110359325e-06</v>
       </c>
       <c r="J3" t="n">
         <v>1.473393054603943e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>9.861027997989072e-06</v>
+        <v>9.861027997989035e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>8.222653603642546e-06</v>
+        <v>8.222653603642521e-06</v>
       </c>
     </row>
     <row r="4">
@@ -1786,34 +1786,34 @@
         <v>1.121808055312192e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.495688669621403e-05</v>
+        <v>2.495688669621401e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.10091472872681e-05</v>
+        <v>1.100914728726809e-05</v>
       </c>
       <c r="E4" t="n">
         <v>9.872569470680638e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>9.872569470680643e-06</v>
+        <v>9.872569470680642e-06</v>
       </c>
       <c r="G4" t="n">
         <v>1.36856066155277e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79800751142203e-05</v>
+        <v>1.798007511422029e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.892692699958245e-06</v>
+        <v>9.892692699958248e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.698750868014104e-05</v>
+        <v>1.698750868014107e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.040203226064386e-05</v>
+        <v>1.040203226064387e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>8.776326053503353e-06</v>
+        <v>8.776326053503318e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001060867181777399</v>
+        <v>0.0001060867181777401</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0003462954245275841</v>
+        <v>0.0003462954245275846</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000102588556776294</v>
+        <v>0.0001025885567762943</v>
       </c>
       <c r="E5" t="n">
-        <v>8.619484198687585e-05</v>
+        <v>8.619484198687589e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.619484198687585e-05</v>
+        <v>8.619484198687589e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001523554524113883</v>
+        <v>0.0001523554524113889</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002481149793168142</v>
+        <v>0.0002481149793168141</v>
       </c>
       <c r="I5" t="n">
-        <v>8.619385578050582e-05</v>
+        <v>8.619385578050574e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002141279493554279</v>
+        <v>0.000214127949355428</v>
       </c>
       <c r="K5" t="n">
-        <v>9.260955422890903e-05</v>
+        <v>9.260955422890919e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>7.322204900949611e-05</v>
+        <v>7.322204900949626e-05</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.47247847587167e-05</v>
+        <v>1.472478475871668e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.632294132650081e-05</v>
+        <v>2.632294132650085e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.466685238338619e-05</v>
+        <v>1.466685238338617e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.084351872401108e-05</v>
+        <v>1.08435187240111e-05</v>
       </c>
       <c r="F6" t="n">
         <v>1.100776847726205e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.719231082112246e-05</v>
+        <v>1.71923108211225e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.188553606399277e-05</v>
+        <v>2.188553606399272e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.101985829507308e-05</v>
+        <v>1.101985829507307e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>1.82406158490836e-05</v>
+        <v>1.824061584908358e-05</v>
       </c>
       <c r="K6" t="n">
         <v>1.14713305932168e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>9.890876588528546e-06</v>
+        <v>9.890876588528544e-06</v>
       </c>
     </row>
     <row r="7">
@@ -1903,34 +1903,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.449219827784427e-05</v>
+        <v>1.449219827784426e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.810165457563417e-05</v>
+        <v>2.810165457563415e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.428182276381228e-05</v>
+        <v>1.428182276381226e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.317718866959416e-05</v>
+        <v>1.317718866959419e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.317718866959416e-05</v>
+        <v>1.317718866959419e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.695972434025008e-05</v>
+        <v>1.695972434025009e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.125419283894264e-05</v>
+        <v>2.125419283894261e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.316681042468061e-05</v>
+        <v>1.31668104246806e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.026162640486342e-05</v>
+        <v>2.02616264048634e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.367614998536623e-05</v>
+        <v>1.367614998536621e-05</v>
       </c>
       <c r="L7" t="n">
         <v>1.20504437782257e-05</v>
@@ -1943,34 +1943,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.153410710502148e-05</v>
+        <v>2.153410710502154e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>4.217083887970225e-05</v>
+        <v>4.217083887970223e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.979488337299979e-05</v>
+        <v>2.979488337299974e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.531672341081182e-05</v>
+        <v>2.531672341081183e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.043853602396983e-05</v>
+        <v>2.04385360239698e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.101671896260575e-05</v>
+        <v>3.101671896260571e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.531118746132102e-05</v>
+        <v>3.5311187461321e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.722380504703627e-05</v>
+        <v>2.722380504703625e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.431999969233277e-05</v>
+        <v>3.431999969233276e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.058774999236591e-05</v>
+        <v>2.058774999236589e-05</v>
       </c>
       <c r="L8" t="n">
         <v>3.343528210537359e-05</v>
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.545191041666235e-05</v>
+        <v>2.545191041666229e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.319819630533859e-05</v>
+        <v>4.319819630533862e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.93798065931529e-05</v>
+        <v>2.937980659315288e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.303814612895358e-05</v>
+        <v>3.303814612895359e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.826433377638185e-05</v>
+        <v>2.826433377638182e-05</v>
       </c>
       <c r="G9" t="n">
         <v>3.205626606995458e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.635073456864714e-05</v>
+        <v>3.635073456864711e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.826335215438513e-05</v>
+        <v>2.826335215438508e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.535816813456789e-05</v>
+        <v>3.53581681345679e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.637579634105743e-05</v>
+        <v>2.637579634105744e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.714698550793025e-05</v>
+        <v>2.714698550793022e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5142393396175e-06</v>
+        <v>5.514239339617524e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.575155863521789e-06</v>
+        <v>6.575155863521786e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.775705935770038e-06</v>
+        <v>5.775705935769967e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.599282425200429e-06</v>
+        <v>5.599282425200574e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.599631617965376e-06</v>
+        <v>5.599631617965295e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.820800624508694e-06</v>
+        <v>5.82080062450868e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.023847674140602e-06</v>
+        <v>6.023847674140624e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.504354245878432e-06</v>
+        <v>5.50435424587838e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5953639816135e-06</v>
+        <v>6.595363981613574e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.766752622809337e-06</v>
+        <v>5.766752622809346e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.531195216348877e-06</v>
+        <v>5.531195216348885e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.792890786685054e-06</v>
+        <v>5.79289078668512e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.250696428652983e-05</v>
+        <v>1.250696428652985e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>7.660092658400564e-06</v>
+        <v>7.660092658400602e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.886566341260092e-06</v>
+        <v>5.886566341260122e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.886915534025004e-06</v>
+        <v>5.886915534025136e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.985249964319912e-06</v>
+        <v>7.985249964320007e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>9.482832082908165e-06</v>
+        <v>9.482832082908192e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.727769605284946e-06</v>
+        <v>5.727769605285009e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.084964818193871e-06</v>
+        <v>9.084964818193991e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>6.116861563063651e-06</v>
+        <v>6.116861563063834e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.962372958006001e-06</v>
+        <v>5.962372958006012e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.525754584711373e-06</v>
+        <v>5.525754584711376e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>1.578962170627046e-05</v>
+        <v>1.578962170627048e-05</v>
       </c>
       <c r="D4" t="n">
         <v>8.479140068831199e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.28871262152835e-06</v>
+        <v>5.288712621528361e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.288712621528354e-06</v>
+        <v>5.288712621528363e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>8.97107294788217e-06</v>
+        <v>8.971072947882158e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.133313521458534e-05</v>
+        <v>1.133313521458537e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.300997209136078e-06</v>
+        <v>5.300997209136097e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.613947588761428e-06</v>
+        <v>8.613947588761449e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>5.323500383352269e-06</v>
+        <v>5.323500383352265e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.787398874052599e-06</v>
+        <v>5.787398874052612e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.867421993847418e-05</v>
+        <v>1.867421993847422e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001997348805056784</v>
+        <v>0.0001997348805056789</v>
       </c>
       <c r="D5" t="n">
-        <v>7.148066473663862e-05</v>
+        <v>7.148066473663835e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.940079907739867e-05</v>
+        <v>1.940079907739871e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.940079907739867e-05</v>
+        <v>1.940079907739871e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>8.218973096237569e-05</v>
+        <v>8.21897309623756e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0001343774882327255</v>
+        <v>0.0001343774882327259</v>
       </c>
       <c r="I5" t="n">
-        <v>1.939984518132729e-05</v>
+        <v>1.93998451813273e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>7.718084794436349e-05</v>
+        <v>7.718084794436345e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.788980520251235e-05</v>
+        <v>1.788980520251239e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.867566923848506e-05</v>
+        <v>2.867566923848508e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.241663403303065e-06</v>
+        <v>6.241663403303081e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.667351634887343e-05</v>
+        <v>1.667351634887346e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>9.22703718583698e-06</v>
+        <v>9.227037185836755e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.876225562885552e-06</v>
+        <v>5.876225562885575e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.011859400345178e-06</v>
+        <v>6.011859400345191e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.173807458397154e-05</v>
+        <v>1.173807458397155e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.44876635774755e-05</v>
+        <v>1.448766357747553e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.067998845225468e-06</v>
+        <v>8.067998845225471e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>1.152467561704948e-05</v>
+        <v>1.152467561704951e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.973623833631732e-06</v>
+        <v>5.973623833631508e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>6.504874791589047e-06</v>
+        <v>6.504874791589068e-06</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.511175643100449e-06</v>
+        <v>8.511175643100471e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>1.871069064122699e-05</v>
+        <v>1.871069064122701e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>1.146312450204682e-05</v>
+        <v>1.146312450204683e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>8.300089819275712e-06</v>
+        <v>8.300089819275734e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.300089819275712e-06</v>
+        <v>8.300089819275734e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.195649400627125e-05</v>
+        <v>1.195649400627126e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.431855627297443e-05</v>
+        <v>1.431855627297447e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.286418267525163e-06</v>
+        <v>8.28641826752518e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.159936864715054e-05</v>
+        <v>1.159936864715055e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>8.308921441741343e-06</v>
+        <v>8.308921441741368e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>8.772819932441687e-06</v>
+        <v>8.772819932441702e-06</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.534597596077473e-05</v>
+        <v>1.534597596077474e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.221535534137129e-05</v>
+        <v>3.221535534137131e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.633379921160682e-05</v>
+        <v>2.633379921160678e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.997004648494047e-05</v>
+        <v>1.997004648494053e-05</v>
       </c>
       <c r="F8" t="n">
         <v>1.534155577299326e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.544586376631359e-05</v>
+        <v>2.544586376631363e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.780792603304155e-05</v>
+        <v>2.780792603304159e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.177578802756756e-05</v>
+        <v>2.177578802756758e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.509004622043931e-05</v>
+        <v>2.509004622043935e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.502010971558701e-05</v>
+        <v>1.502010971558702e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.921344392081454e-05</v>
+        <v>2.921344392081457e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.728602668411993e-05</v>
+        <v>1.728602668411997e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>3.091849762045737e-05</v>
+        <v>3.091849762045744e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.367236806676761e-05</v>
+        <v>2.367236806676763e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.445673354570326e-05</v>
+        <v>2.445673354570329e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.049517600399529e-05</v>
+        <v>2.049517600399531e-05</v>
       </c>
       <c r="G9" t="n">
         <v>2.416430098550161e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.652636325220483e-05</v>
+        <v>2.652636325220487e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.049422524675555e-05</v>
+        <v>2.049422524675557e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.380717562638091e-05</v>
+        <v>2.380717562638098e-05</v>
       </c>
       <c r="K9" t="n">
         <v>1.844696124482633e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.098062691167205e-05</v>
+        <v>2.098062691167216e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.973400598749905e-06</v>
+        <v>5.973400598749909e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>5.488207879389741e-06</v>
+        <v>5.488207879389714e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.286804881601087e-06</v>
+        <v>6.28680488160108e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.813007481137756e-06</v>
+        <v>5.813007481137858e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.813359722367706e-06</v>
+        <v>5.813359722367736e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.659979123947451e-06</v>
+        <v>6.659979123947447e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.538023962432395e-06</v>
+        <v>7.538023962432423e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9900002151347e-06</v>
+        <v>5.99000021513477e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>8.49283222855971e-06</v>
+        <v>8.492832228559835e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>7.274555056898532e-06</v>
+        <v>7.274555056898689e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>6.804101006204491e-06</v>
+        <v>6.804101006204521e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.96133033141526e-06</v>
+        <v>5.961330331415414e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.186393188498719e-06</v>
+        <v>5.186393188498685e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>8.198963989044027e-06</v>
+        <v>8.198963989044082e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.795254856130014e-06</v>
+        <v>5.795254856129959e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.795607097359932e-06</v>
+        <v>5.795607097359847e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>1.086431413051454e-05</v>
+        <v>1.086431413051467e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.717730256669799e-05</v>
+        <v>1.717730256669804e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.085318646067926e-06</v>
+        <v>6.085318646068113e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.964469787249013e-05</v>
+        <v>1.964469787249024e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.228109015015391e-05</v>
+        <v>1.228109015015411e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.193856523415746e-05</v>
+        <v>1.193856523415748e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.015446312155355e-06</v>
+        <v>5.015446312155345e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.90293579834932e-06</v>
+        <v>4.902935798349314e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>8.555491860052232e-06</v>
+        <v>8.55549186005222e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.038262479989769e-06</v>
+        <v>5.038262479989784e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.038262479989769e-06</v>
+        <v>5.038262479989783e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.275076939927659e-05</v>
+        <v>1.27507693992766e-05</v>
       </c>
       <c r="H4" t="n">
         <v>2.267417333055969e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.073136401885929e-06</v>
+        <v>5.073136401885941e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>2.459907820745635e-05</v>
+        <v>2.459907820745637e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.361444957761971e-05</v>
+        <v>1.36144495776197e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.441266004516805e-05</v>
+        <v>1.441266004516803e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.118401610249012e-05</v>
+        <v>1.118401610249014e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.467621073962344e-05</v>
+        <v>1.467621073962348e-05</v>
       </c>
       <c r="D5" t="n">
         <v>7.755590275986221e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.756477847704997e-05</v>
+        <v>1.756477847705028e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.756477847704997e-05</v>
+        <v>1.756477847705028e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001570980955533706</v>
+        <v>0.000157098095553371</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0003711317921637804</v>
+        <v>0.0003711317921637803</v>
       </c>
       <c r="I5" t="n">
-        <v>1.756290498168549e-05</v>
+        <v>1.756290498168586e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0003826349685466547</v>
+        <v>0.0003826349685466551</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001687062069488872</v>
+        <v>0.0001687062069488871</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002084788651464974</v>
+        <v>0.0002084788651464977</v>
       </c>
     </row>
     <row r="6">
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.776075094980276e-06</v>
+        <v>5.776075094980304e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>5.557789632327526e-06</v>
+        <v>5.557789632326619e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>9.261229013348756e-06</v>
+        <v>9.261229013348766e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.587867044715167e-06</v>
+        <v>5.587867044715188e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.821644908700297e-06</v>
+        <v>5.821644908700323e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.351139818210151e-05</v>
+        <v>1.351139818210154e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.601499771080539e-05</v>
+        <v>2.601499771080546e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>8.095167753968058e-06</v>
+        <v>8.095167753968092e-06</v>
       </c>
       <c r="J6" t="n">
         <v>2.554552054856372e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.449327158381476e-05</v>
+        <v>1.449327158381478e-05</v>
       </c>
       <c r="L6" t="n">
         <v>1.522973563755199e-05</v>
@@ -2695,31 +2695,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.323519884778913e-06</v>
+        <v>8.323519884778917e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.323835322691981e-06</v>
+        <v>8.323835322691988e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.186206370619701e-05</v>
+        <v>1.1862063706197e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>8.399160478419965e-06</v>
+        <v>8.399160478419995e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.399160478419965e-06</v>
+        <v>8.399160478419995e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.605884297190017e-05</v>
+        <v>1.60588429719002e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.598224690318324e-05</v>
+        <v>2.598224690318329e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.38120997450949e-06</v>
+        <v>8.381209974509512e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.790715178007992e-05</v>
+        <v>2.790715178007993e-05</v>
       </c>
       <c r="K7" t="n">
         <v>1.692252315024327e-05</v>
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.563039259066027e-05</v>
+        <v>1.563039259066029e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.282828018777904e-05</v>
+        <v>2.282828018777907e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.783793316644856e-05</v>
+        <v>2.783793316644857e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.092178244299755e-05</v>
+        <v>2.092178244299758e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.592800287722741e-05</v>
+        <v>1.592800287722743e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.054461844969156e-05</v>
+        <v>3.054461844969158e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>4.046802238097703e-05</v>
+        <v>4.046802238097704e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.286698545230088e-05</v>
+        <v>2.28669854523009e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.239433811820222e-05</v>
+        <v>4.239433811820227e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>2.409604405147372e-05</v>
+        <v>2.409604405147374e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.970547333114446e-05</v>
+        <v>3.970547333114449e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.056570492565438e-05</v>
+        <v>2.056570492565444e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.505554844991797e-05</v>
+        <v>2.505554844991804e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.859527912381609e-05</v>
+        <v>2.859527912381617e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.029561127109093e-05</v>
+        <v>3.029561127109099e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.511479175384406e-05</v>
+        <v>2.511479175384415e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.279055609912616e-05</v>
+        <v>3.279055609912624e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>4.271396003040926e-05</v>
+        <v>4.271396003040932e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.51129231017355e-05</v>
+        <v>2.511292310173557e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.463886490730593e-05</v>
+        <v>4.463886490730601e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.105298630968693e-05</v>
+        <v>3.105298630968695e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.445244674501763e-05</v>
+        <v>3.445244674501768e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.748167455536049e-06</v>
+        <v>4.748167455536094e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.581983559856807e-06</v>
+        <v>4.581983559856804e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.767573928820927e-06</v>
+        <v>4.767573928820845e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.862879474520079e-06</v>
+        <v>4.862879474520138e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.863223871512612e-06</v>
+        <v>4.863223871512641e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.796892911694572e-06</v>
+        <v>4.796892911694597e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.827080842746126e-06</v>
+        <v>4.827080842746117e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.761052443242604e-06</v>
+        <v>4.761052443242646e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.919671797117856e-06</v>
+        <v>5.919671797117864e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.030574094212216e-06</v>
+        <v>5.030574094212286e-06</v>
       </c>
       <c r="L2" t="n">
         <v>4.844529416316124e-06</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.894551297143202e-06</v>
+        <v>4.894551297143161e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.65375454421624e-06</v>
+        <v>4.653754544216263e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.038136572305373e-06</v>
+        <v>5.03813657230541e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.162066438737476e-06</v>
+        <v>5.162066438737372e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.162410835729887e-06</v>
+        <v>5.162410835729848e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.247802439119195e-06</v>
+        <v>5.247802439119194e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.497232165826888e-06</v>
+        <v>5.497232165826893e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.991883921445059e-06</v>
+        <v>4.991883921445033e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>9.265368689186753e-06</v>
+        <v>9.265368689186765e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.371258620555473e-06</v>
+        <v>5.371258620555485e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.595376812739608e-06</v>
+        <v>5.595376812739609e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.409312690568304e-06</v>
+        <v>4.409312690568303e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.428230329654737e-06</v>
+        <v>4.428230329654743e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.628517733738446e-06</v>
+        <v>4.628517733738452e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.514965452299245e-06</v>
+        <v>4.514965452299244e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.514965452299246e-06</v>
+        <v>4.514965452299244e-06</v>
       </c>
       <c r="G4" t="n">
         <v>4.944106310186097e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.355022205945516e-06</v>
+        <v>5.355022205945514e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.454161548300335e-06</v>
+        <v>4.454161548300333e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>9.410840401118824e-06</v>
+        <v>9.410840401118814e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.419861652389838e-06</v>
+        <v>4.419861652389839e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>5.500715762168567e-06</v>
+        <v>5.50071576216857e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3011,28 +3011,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.040066268460121e-05</v>
+        <v>1.04006626846012e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.41807947570918e-05</v>
+        <v>1.418079475709181e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.691040650390261e-05</v>
+        <v>1.69104065039026e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.565815428817158e-05</v>
+        <v>1.56581542881716e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.565815428817158e-05</v>
+        <v>1.56581542881716e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.296710860734494e-05</v>
+        <v>2.296710860734505e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.22806044708174e-05</v>
+        <v>3.228060447081745e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.565792982686294e-05</v>
+        <v>1.565792982686293e-05</v>
       </c>
       <c r="J5" t="n">
         <v>0.000102862319609051</v>
@@ -3041,7 +3041,7 @@
         <v>1.339585257126785e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>3.565438401650682e-05</v>
+        <v>3.565438401650685e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8166004068509e-06</v>
+        <v>4.816600406850898e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.829534410832805e-06</v>
+        <v>4.829534410832801e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>6.7711041350415e-06</v>
+        <v>6.771104135041504e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.825026944922751e-06</v>
+        <v>4.825026944922755e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.866998137250748e-06</v>
+        <v>4.866998137250749e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>5.351394026468672e-06</v>
+        <v>5.35139402646868e-06</v>
       </c>
       <c r="H6" t="n">
         <v>7.652560812742188e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.481749925302544e-06</v>
+        <v>6.481749925302497e-06</v>
       </c>
       <c r="J6" t="n">
         <v>1.154455574040096e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>4.824280960104428e-06</v>
+        <v>4.8242809601044e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>5.91521575679455e-06</v>
+        <v>5.915215756794556e-06</v>
       </c>
     </row>
     <row r="7">
@@ -3094,34 +3094,34 @@
         <v>7.071838508102382e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.110352112715904e-06</v>
+        <v>7.110352112715892e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.289622570444782e-06</v>
+        <v>7.28962257044478e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.140554078533922e-06</v>
+        <v>7.140554078533918e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.140554078533922e-06</v>
+        <v>7.140554078533918e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.606632127720174e-06</v>
+        <v>7.60663212772016e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>8.017548023479583e-06</v>
+        <v>8.017548023479591e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.116687365834423e-06</v>
+        <v>7.11668736583442e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.20733662186529e-05</v>
+        <v>1.207336621865288e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>7.082387469923919e-06</v>
+        <v>7.08238746992392e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>8.163241579702645e-06</v>
+        <v>8.163241579702651e-06</v>
       </c>
     </row>
     <row r="8">
@@ -3134,34 +3134,34 @@
         <v>1.358339249299807e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.979893454249982e-05</v>
+        <v>1.979893454249983e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.122956182058882e-05</v>
+        <v>2.122956182058883e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.812003778286906e-05</v>
+        <v>1.812003778286911e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.383840795302141e-05</v>
+        <v>1.383840795302144e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.026961213786764e-05</v>
+        <v>2.026961213786763e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.068052803363667e-05</v>
+        <v>2.068052803363668e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.977966737598194e-05</v>
+        <v>1.977966737598191e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.473755516052035e-05</v>
+        <v>2.473755516052032e-05</v>
       </c>
       <c r="K8" t="n">
         <v>1.347967555823782e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.725190044735409e-05</v>
+        <v>2.725190044735406e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.562567152198068e-05</v>
+        <v>1.56256715219807e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.890641739290854e-05</v>
+        <v>1.890641739290856e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.908710925851919e-05</v>
+        <v>1.90871092585192e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.265444367646866e-05</v>
+        <v>2.26544436764687e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.891297622267212e-05</v>
+        <v>1.89129762226721e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.940269740791284e-05</v>
+        <v>1.940269740791282e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.981361330367224e-05</v>
+        <v>1.981361330367229e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.891275264602709e-05</v>
+        <v>1.891275264602708e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.386943149884553e-05</v>
+        <v>2.386943149884556e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.699989082140851e-05</v>
+        <v>1.699989082140852e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.995930685989529e-05</v>
+        <v>1.995930685989532e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.57865693995822e-06</v>
+        <v>4.578656939958168e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.500332479798862e-06</v>
+        <v>4.500332479798852e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.596533366822046e-06</v>
+        <v>4.596533366822018e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.761441061737567e-06</v>
+        <v>4.761441061737613e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.761785933769798e-06</v>
+        <v>4.761785933769783e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.59073369781178e-06</v>
+        <v>4.590733697811773e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.595043478092111e-06</v>
+        <v>4.595043478092102e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.587561504042281e-06</v>
+        <v>4.587561504042247e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.328008756495446e-06</v>
+        <v>5.32800875649541e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.921035311200113e-06</v>
+        <v>4.921035311200094e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.586824848236488e-06</v>
+        <v>4.58682484823648e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.690066215502148e-06</v>
+        <v>4.690066215502091e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.607817791005768e-06</v>
+        <v>4.607817791005762e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.822756397492864e-06</v>
+        <v>4.822756397492777e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.048159388627634e-06</v>
+        <v>5.048159388627601e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.048504260659872e-06</v>
+        <v>5.048504260659936e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.781911848814847e-06</v>
+        <v>4.781911848814841e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.844972882415391e-06</v>
+        <v>4.844972882415384e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.759035319496176e-06</v>
+        <v>4.759035319496152e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.041286380259014e-06</v>
+        <v>6.041286380258958e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.264794782640829e-06</v>
+        <v>5.264794782640912e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.761684704192599e-06</v>
+        <v>4.761684704192592e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.378783667459606e-06</v>
+        <v>4.378783667459584e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.434633609746361e-06</v>
+        <v>4.434633609746338e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.580706132449209e-06</v>
+        <v>4.58070613244919e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.429149276413981e-06</v>
+        <v>4.429149276413968e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.429149276413981e-06</v>
+        <v>4.42914927641397e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.499796050474566e-06</v>
+        <v>4.499796050474112e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.619128602706348e-06</v>
+        <v>4.619128602706355e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.37995480903783e-06</v>
+        <v>4.37995480903791e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.601307205829956e-06</v>
+        <v>4.601307205829926e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.387322357536467e-06</v>
+        <v>4.387322357536456e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.480892893116267e-06</v>
+        <v>4.48089289311627e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.023969193364609e-05</v>
+        <v>1.023969193364591e-05</v>
       </c>
       <c r="C5" t="n">
         <v>1.452632769681757e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.645668128389434e-05</v>
+        <v>1.645668128389433e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.472647836967428e-05</v>
+        <v>1.472647836967417e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.472647836967428e-05</v>
+        <v>1.472647836967416e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.556660574137129e-05</v>
+        <v>1.556660574137109e-05</v>
       </c>
       <c r="H5" t="n">
         <v>1.86031719040281e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.472633779113154e-05</v>
+        <v>1.472633779113143e-05</v>
       </c>
       <c r="J5" t="n">
         <v>1.738575696104838e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.320105662527945e-05</v>
+        <v>1.320105662527944e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.617725563957048e-05</v>
+        <v>1.617725563957045e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.37541427971545e-06</v>
+        <v>6.375414279715444e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.805259243399146e-06</v>
+        <v>4.805259243399138e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.961656492841274e-06</v>
+        <v>4.961656492841278e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7254441016986e-06</v>
+        <v>4.725444101698592e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.758941711265203e-06</v>
+        <v>4.758941711265189e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>6.496426662729925e-06</v>
+        <v>6.496426662729966e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.994218436558538e-06</v>
+        <v>4.994218436558528e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.376585421293773e-06</v>
+        <v>6.376585421293764e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.020042579765926e-06</v>
+        <v>5.020042579765918e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.76681008193238e-06</v>
+        <v>4.766810081932379e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.856306661356683e-06</v>
+        <v>4.856306661356687e-06</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.970839918840498e-06</v>
+        <v>6.97083991884049e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.038495642329374e-06</v>
+        <v>7.038495642329362e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.171341241647971e-06</v>
+        <v>7.17134124164796e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.992403137571281e-06</v>
+        <v>6.99240313757127e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.992403137571281e-06</v>
+        <v>6.992403137571269e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.091852301855013e-06</v>
+        <v>7.091852301854981e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.211184854087259e-06</v>
+        <v>7.211184854087256e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.972011060418834e-06</v>
+        <v>6.972011060418823e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.193363457210845e-06</v>
+        <v>7.193363457210834e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>6.979378608917361e-06</v>
+        <v>6.979378608917366e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.072949144497159e-06</v>
+        <v>7.072949144497174e-06</v>
       </c>
     </row>
     <row r="8">
@@ -3530,31 +3530,31 @@
         <v>1.344471857654826e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9614077340822e-05</v>
+        <v>1.961407734082198e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.098658305191811e-05</v>
+        <v>2.098658305191812e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.788232702221577e-05</v>
+        <v>1.788232702221574e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.36516650652825e-05</v>
+        <v>1.365166506528249e-05</v>
       </c>
       <c r="G8" t="n">
         <v>1.964508028419938e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.976441283644469e-05</v>
+        <v>1.976441283644467e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.952523904276321e-05</v>
+        <v>1.952523904276318e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.97477862059378e-05</v>
+        <v>1.974778620593778e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.334033023177332e-05</v>
+        <v>1.334033023177331e-05</v>
       </c>
       <c r="L8" t="n">
         <v>2.597656584342674e-05</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.475767879745494e-05</v>
+        <v>1.475767879745495e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.783449837978538e-05</v>
+        <v>1.783449837978537e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.796876549653563e-05</v>
+        <v>1.796876549653565e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.124066510343986e-05</v>
+        <v>2.124066510343987e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.776815365582956e-05</v>
+        <v>1.776815365582957e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.788785503931101e-05</v>
+        <v>1.788785503931102e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80071875915433e-05</v>
+        <v>1.800718759154327e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.776801379787484e-05</v>
+        <v>1.776801379787483e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.798936619466684e-05</v>
+        <v>1.798936619466685e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.603186014649654e-05</v>
+        <v>1.603186014649653e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.78689518819532e-05</v>
+        <v>1.786895188195318e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.009074305657922e-06</v>
+        <v>5.00907430565818e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.792515402381494e-06</v>
+        <v>4.792515402381684e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>5.066265540089394e-06</v>
+        <v>5.066265540089257e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.077415781308588e-06</v>
+        <v>5.077415781308961e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.077761885865493e-06</v>
+        <v>5.077761885865768e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.212369576321169e-06</v>
+        <v>5.21236957632102e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.298755686008157e-06</v>
+        <v>6.29875568600835e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.025266773914852e-06</v>
+        <v>5.025266773914784e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.670168291369107e-06</v>
+        <v>5.670168291369204e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.25092685886346e-06</v>
+        <v>5.250926858863553e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.675695052639393e-06</v>
+        <v>5.675695052639215e-06</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.09818757557404e-06</v>
+        <v>5.098187575574163e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.765815291641474e-06</v>
+        <v>4.765815291641478e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.510922839182705e-06</v>
+        <v>5.510922839182638e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.30730433669428e-06</v>
+        <v>5.307304336694114e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.307650441251195e-06</v>
+        <v>5.307650441251023e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.553945125096924e-06</v>
+        <v>6.553945125097085e-06</v>
       </c>
       <c r="H3" t="n">
         <v>1.43117980915748e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>5.21912571404539e-06</v>
+        <v>5.21912571404556e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>6.251259356304667e-06</v>
+        <v>6.25125935630452e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.516200396033495e-06</v>
+        <v>5.516200396033628e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>9.858418283992393e-06</v>
+        <v>9.858418283992368e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.528454486587206e-06</v>
+        <v>4.528454486587272e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.49821856317735e-06</v>
+        <v>4.498218563177343e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.174455788754736e-06</v>
+        <v>5.174455788754643e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.640682923515105e-06</v>
+        <v>4.640682923515106e-06</v>
       </c>
       <c r="F4" t="n">
         <v>4.640682923515106e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>6.808101467878121e-06</v>
+        <v>6.808101467878148e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90245880089766e-05</v>
+        <v>1.902458800897662e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>4.603333319552845e-06</v>
+        <v>4.603333319552842e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.64300587717578e-06</v>
+        <v>4.643005877175777e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.555937952539917e-06</v>
+        <v>4.555937952539919e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>1.200065891912655e-05</v>
+        <v>1.200065891912637e-05</v>
       </c>
     </row>
     <row r="5">
@@ -3803,31 +3803,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.039050949052765e-05</v>
+        <v>1.039050949052759e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.400936026755616e-05</v>
+        <v>1.400936026755617e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.49113900058724e-05</v>
+        <v>2.491139000587249e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.662721328268917e-05</v>
+        <v>1.662721328268911e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.662721328268917e-05</v>
+        <v>1.662721328268911e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.576699744594999e-05</v>
+        <v>5.57669974459503e-05</v>
       </c>
       <c r="H5" t="n">
         <v>0.0003064700876991528</v>
       </c>
       <c r="I5" t="n">
-        <v>1.662659472155926e-05</v>
+        <v>1.662659472155925e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.590212340179275e-05</v>
+        <v>1.590212340179264e-05</v>
       </c>
       <c r="K5" t="n">
         <v>1.387952022919668e-05</v>
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.964618344059976e-06</v>
+        <v>4.964618344060018e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.90983502810932e-06</v>
+        <v>4.90983502810931e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.588658983487557e-06</v>
+        <v>5.588658983487683e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.962622710819698e-06</v>
+        <v>4.962622710819693e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.040930871155282e-06</v>
+        <v>5.040930871155275e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.244265325350946e-06</v>
+        <v>7.244265325350899e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>2.168204215056375e-05</v>
+        <v>2.168204215056361e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>5.039497177025593e-06</v>
+        <v>5.039497177025591e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.129775247840603e-06</v>
+        <v>5.129775247840535e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.952453689347819e-06</v>
+        <v>4.95245368934793e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.248188473745302e-05</v>
+        <v>1.248188473745288e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3883,34 +3883,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.439848895178857e-06</v>
+        <v>7.439848895178768e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.455645065188215e-06</v>
+        <v>7.455645065188221e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>8.08435037420789e-06</v>
+        <v>8.084350374207816e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.536806410459905e-06</v>
+        <v>7.536806410459914e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.536806410459901e-06</v>
+        <v>7.536806410459914e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>9.719495876469621e-06</v>
+        <v>9.719495876469641e-06</v>
       </c>
       <c r="H7" t="n">
         <v>2.193598241756811e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>7.514727728144326e-06</v>
+        <v>7.514727728144334e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.554400285767335e-06</v>
+        <v>7.554400285767279e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.467332361131474e-06</v>
+        <v>7.467332361131413e-06</v>
       </c>
       <c r="L7" t="n">
         <v>1.491205332771786e-05</v>
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.442294485237325e-05</v>
+        <v>1.442294485237315e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.110797254009026e-05</v>
+        <v>2.110797254009028e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.309246191489822e-05</v>
+        <v>2.309246191489826e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.934726936573578e-05</v>
+        <v>1.93472693657358e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.472279179248017e-05</v>
+        <v>1.47227917924802e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.334811506120581e-05</v>
+        <v>2.334811506120578e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>3.556460160230588e-05</v>
+        <v>3.556460160230583e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.114334691288044e-05</v>
+        <v>2.114334691288047e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.118432550654066e-05</v>
+        <v>2.118432550654087e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.432698431254161e-05</v>
+        <v>1.432698431254163e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>3.548247721351635e-05</v>
+        <v>3.548247721351643e-05</v>
       </c>
     </row>
     <row r="9">
@@ -3966,34 +3966,34 @@
         <v>1.792062321657957e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.179620972743435e-05</v>
+        <v>2.179620972743437e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.242641285186715e-05</v>
+        <v>2.242641285186724e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.631001991955068e-05</v>
+        <v>2.631001991955071e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>2.185590660783494e-05</v>
+        <v>2.185590660783495e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.406006053871572e-05</v>
+        <v>2.406006053871575e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.627654707981416e-05</v>
+        <v>3.627654707981425e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.185529239039047e-05</v>
+        <v>2.185529239039049e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.189496494801338e-05</v>
+        <v>2.18949649480134e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.957151849689032e-05</v>
+        <v>1.957151849689033e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.925261798996396e-05</v>
+        <v>2.925261798996402e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.561324630416131e-06</v>
+        <v>4.561324630415809e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.519901793216451e-06</v>
+        <v>4.519901793215618e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.578696848157356e-06</v>
+        <v>4.578696848157017e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.783284544023614e-06</v>
+        <v>4.783284544023444e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.78362886439264e-06</v>
+        <v>4.783628864392534e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.572739302065797e-06</v>
+        <v>4.572739302065475e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.578387894140945e-06</v>
+        <v>4.578387894140949e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.57506695544115e-06</v>
+        <v>4.575066955440829e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.305432535804088e-06</v>
+        <v>5.305432535803926e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.960783059552466e-06</v>
+        <v>4.960783059552301e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.566798855351552e-06</v>
+        <v>4.566798855351556e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.645685745349148e-06</v>
+        <v>4.64568574534905e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.614159502088721e-06</v>
+        <v>4.614159502089081e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.774759934749387e-06</v>
+        <v>4.774759934749285e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.094901754231996e-06</v>
+        <v>5.094901754232028e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.095246074601e-06</v>
+        <v>5.095246074601068e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.732795697794227e-06</v>
+        <v>4.732795697794153e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.804978917329391e-06</v>
+        <v>4.804978917329394e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.749105596118445e-06</v>
+        <v>4.749105596118399e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9894465905362e-06</v>
+        <v>5.98944659053615e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.322334093535797e-06</v>
+        <v>5.322334093535788e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.698277615342986e-06</v>
+        <v>4.698277615342988e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.353951532090063e-06</v>
+        <v>4.353951532090454e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.387696582667433e-06</v>
+        <v>4.387696582667643e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.550178723092333e-06</v>
+        <v>4.550178723092654e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.496482891364577e-06</v>
+        <v>4.496482891364702e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.496482891364576e-06</v>
+        <v>4.4964828913647e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.467594671118788e-06</v>
+        <v>4.467594671118859e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.601047190601625e-06</v>
+        <v>4.601047190601752e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.410434735687232e-06</v>
+        <v>4.410434735687576e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.578949349521645e-06</v>
+        <v>4.578949349521751e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.378428176836254e-06</v>
+        <v>4.378428176836567e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.426135325723311e-06</v>
+        <v>4.426135325723599e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.043213416865467e-05</v>
+        <v>1.043213416865503e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.436225305327035e-05</v>
+        <v>1.436225305327044e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.653936212663222e-05</v>
+        <v>1.653936212663232e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.584636268143158e-05</v>
+        <v>1.584636268143201e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.584636268143158e-05</v>
+        <v>1.584636268143201e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.562152875041972e-05</v>
+        <v>1.562152875041978e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.893676492518824e-05</v>
+        <v>1.893676492518857e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.584623664596091e-05</v>
+        <v>1.584623664596104e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.761932987317168e-05</v>
+        <v>1.761932987317195e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.365331301674507e-05</v>
+        <v>1.365331301674511e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.580214723283066e-05</v>
+        <v>1.580214723283071e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.33950892309534e-06</v>
+        <v>6.339508923095647e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.766203847123241e-06</v>
+        <v>4.766203847123411e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.937967332710172e-06</v>
+        <v>4.937967332710537e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.770702341248196e-06</v>
+        <v>4.770702341248365e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.798987813939503e-06</v>
+        <v>4.79898781393989e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>4.848320974042119e-06</v>
+        <v>4.848320974042247e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.842875263467305e-06</v>
+        <v>6.84287526346772e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.395992126692516e-06</v>
+        <v>6.395992126692639e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.003574897648381e-06</v>
+        <v>5.003574897648637e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.766090578696453e-06</v>
+        <v>4.766090578696744e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.808234783625492e-06</v>
+        <v>4.808234783625943e-06</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.903082860734595e-06</v>
+        <v>6.903082860735173e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>6.950281718466548e-06</v>
+        <v>6.950281718466695e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.097889613000544e-06</v>
+        <v>7.09788961300085e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.989384342455557e-06</v>
+        <v>6.989384342455721e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.989384342455557e-06</v>
+        <v>6.989384342455721e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.01672599976332e-06</v>
+        <v>7.016725999763643e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.150178519246149e-06</v>
+        <v>7.15017851924636e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.959566064331763e-06</v>
+        <v>6.959566064332173e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.128080678166177e-06</v>
+        <v>7.128080678166373e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>6.927559505480775e-06</v>
+        <v>6.927559505481184e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>6.975266654367837e-06</v>
+        <v>6.975266654368064e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.331482740771065e-05</v>
+        <v>1.331482740771078e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.93929701797449e-05</v>
+        <v>1.939297017974518e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.07546975993746e-05</v>
+        <v>2.075469759937489e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.775784194305316e-05</v>
+        <v>1.775784194305335e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.358017458225934e-05</v>
+        <v>1.358017458225949e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.942805966088333e-05</v>
+        <v>1.942805966088351e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.956151218037301e-05</v>
+        <v>1.956151218037337e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.937089972545177e-05</v>
+        <v>1.937089972545192e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.954059343059658e-05</v>
+        <v>1.954059343059686e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.322785860446238e-05</v>
+        <v>1.322785860446267e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.565367282283902e-05</v>
+        <v>2.56536728228392e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.536370376410649e-05</v>
+        <v>1.536370376410677e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.858887193537496e-05</v>
+        <v>1.858887193537497e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87379006171699e-05</v>
+        <v>1.87379006171702e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.226559099450991e-05</v>
+        <v>2.226559099451007e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.859828164369997e-05</v>
+        <v>1.859828164370037e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.865531621667173e-05</v>
+        <v>1.865531621667194e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.878876873615456e-05</v>
+        <v>1.878876873615469e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.859815628124016e-05</v>
+        <v>1.859815628124052e-05</v>
       </c>
       <c r="J9" t="n">
         <v>1.876667089507457e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.456451900080778e-05</v>
+        <v>1.456451900080807e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.861385687127625e-05</v>
+        <v>1.861385687127658e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.598385347472674e-06</v>
+        <v>4.598385347472536e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.548509349156774e-06</v>
+        <v>4.548509349156786e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.61472032929632e-06</v>
+        <v>4.614720329296176e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>4.77928698910926e-06</v>
+        <v>4.7792869891095e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.779632344597319e-06</v>
+        <v>4.779632344597549e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.610184903510134e-06</v>
+        <v>4.610184903509958e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.615486132397775e-06</v>
+        <v>4.615486132397791e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.608492041143502e-06</v>
+        <v>4.608492041143358e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.310970490043709e-06</v>
+        <v>5.31097049004366e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.945590454411099e-06</v>
+        <v>4.945590454411343e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.605841999337523e-06</v>
+        <v>4.605841999337536e-06</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.640185780076052e-06</v>
+        <v>4.640185780076062e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>4.60347750522029e-06</v>
+        <v>4.603477505220293e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.761906044851698e-06</v>
+        <v>4.761906044851693e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>5.001758900049501e-06</v>
+        <v>5.001758900049348e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.002104255537452e-06</v>
+        <v>5.002104255537241e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.730058728297885e-06</v>
+        <v>4.730058728298114e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.799491610679038e-06</v>
+        <v>4.799491610679057e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.717727635552563e-06</v>
+        <v>4.717727635552387e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.942430141788768e-06</v>
+        <v>5.942430141788902e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.229718360476071e-06</v>
+        <v>5.22971836047608e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>4.706925693901528e-06</v>
+        <v>4.706925693901547e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.35709547342855e-06</v>
+        <v>4.357095473428549e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.417126887538953e-06</v>
+        <v>4.417126887538961e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.54160660758949e-06</v>
+        <v>4.541606607589488e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.43327302312448e-06</v>
+        <v>4.433273023124494e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.433273023124479e-06</v>
+        <v>4.433273023124494e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.474974479376056e-06</v>
+        <v>4.47497447937606e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>4.604207716630637e-06</v>
+        <v>4.60420771663064e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.371827296051742e-06</v>
+        <v>4.37182729605175e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.603719619132179e-06</v>
+        <v>4.603719619132173e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.379728465704764e-06</v>
+        <v>4.37972846570476e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>4.451609927664493e-06</v>
+        <v>4.45160992766449e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.014735942906432e-05</v>
+        <v>1.014735942906434e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>1.440878199457968e-05</v>
+        <v>1.440878199457969e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.607270032164918e-05</v>
+        <v>1.607270032164923e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.487070545295134e-05</v>
+        <v>1.487070545295135e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.487070545295134e-05</v>
+        <v>1.487070545295135e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.542185517789874e-05</v>
+        <v>1.54218551778993e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.863472949572999e-05</v>
+        <v>1.863472949573001e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.487056788978401e-05</v>
+        <v>1.4870567889784e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>1.772399141681571e-05</v>
+        <v>1.772399141681574e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.335323632226556e-05</v>
+        <v>1.335323632226557e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.592938774115028e-05</v>
+        <v>1.592938774115025e-05</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.368118009849542e-06</v>
+        <v>6.368118009849559e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>4.798338363159828e-06</v>
+        <v>4.798338363159833e-06</v>
       </c>
       <c r="D6" t="n">
         <v>4.938345431729957e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>4.734835599391239e-06</v>
+        <v>4.734835599391255e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>4.767638442444629e-06</v>
+        <v>4.767638442444643e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>4.864567664702426e-06</v>
+        <v>4.864567664702429e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>6.896333026970516e-06</v>
+        <v>6.896333026970521e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>4.761420481378105e-06</v>
+        <v>4.761420481378114e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>6.72308664759501e-06</v>
+        <v>6.723086647594968e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>4.77645727080007e-06</v>
+        <v>4.776457270800064e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>4.843022306898104e-06</v>
+        <v>4.843022306898114e-06</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.867783553898974e-06</v>
+        <v>6.867783553898975e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>6.933158829303943e-06</v>
+        <v>6.933158829303976e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.050873671829236e-06</v>
+        <v>7.050873671829237e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>6.906503202571917e-06</v>
+        <v>6.906503202571938e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>6.906503202571917e-06</v>
+        <v>6.906503202571938e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.985662559846481e-06</v>
+        <v>6.985662559846485e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.114895797101059e-06</v>
+        <v>7.114895797101063e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.882515376522159e-06</v>
+        <v>6.882515376522179e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.114407699602595e-06</v>
+        <v>7.114407699602601e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>6.890416546175185e-06</v>
+        <v>6.890416546175186e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>6.962298008134913e-06</v>
+        <v>6.962298008134914e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.325270784116399e-05</v>
+        <v>1.3252707841164e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.930542141258137e-05</v>
+        <v>1.930542141258141e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.063495536822514e-05</v>
+        <v>2.06349553682252e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.762135912300599e-05</v>
+        <v>1.762135912300602e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.347162523077886e-05</v>
+        <v>1.347162523077888e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.933215354849e-05</v>
+        <v>1.933215354849003e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.946138678575644e-05</v>
+        <v>1.946138678575645e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.922900636516569e-05</v>
+        <v>1.922900636516571e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.946207030685744e-05</v>
+        <v>1.946207030685745e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.316460167129631e-05</v>
+        <v>1.31646016712963e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.553614391444179e-05</v>
+        <v>2.553614391444182e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.466223112389821e-05</v>
+        <v>1.466223112389824e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.771220998562523e-05</v>
+        <v>1.771220998562527e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.783134619135223e-05</v>
+        <v>1.783134619135229e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.110587284464979e-05</v>
+        <v>2.110587284464986e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.766170344014721e-05</v>
+        <v>1.766170344014727e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.776471371616775e-05</v>
+        <v>1.776471371616779e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.789394695342234e-05</v>
+        <v>1.789394695342238e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.766156653284342e-05</v>
+        <v>1.766156653284347e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.789345885592386e-05</v>
+        <v>1.789345885592391e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.587001727902932e-05</v>
+        <v>1.587001727902936e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.774134916445617e-05</v>
+        <v>1.774134916445622e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4874,34 +4874,34 @@
         <v>1.426200401018757e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.018820959862699e-05</v>
+        <v>1.0188209598627e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>9.461150420693664e-06</v>
+        <v>9.461150420693669e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.058383590819806e-05</v>
+        <v>1.058383590819808e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>9.497603908501801e-06</v>
+        <v>9.497603908501818e-06</v>
       </c>
       <c r="G2" t="n">
         <v>1.06574365059836e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.250535423289187e-05</v>
+        <v>1.250535423289189e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>9.290617196458022e-06</v>
+        <v>9.290617196458023e-06</v>
       </c>
       <c r="J2" t="n">
         <v>1.204383798109377e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.299510283860444e-05</v>
+        <v>1.299510283860443e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.293496924688113e-05</v>
+        <v>1.293496924688114e-05</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.880828125721692e-05</v>
+        <v>4.880828125721681e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.498828054781519e-05</v>
+        <v>1.498828054781524e-05</v>
       </c>
       <c r="D3" t="n">
         <v>1.470213054652823e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.561423891305974e-05</v>
+        <v>1.561423891305976e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.38209732165802e-05</v>
+        <v>1.382097321658022e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.323326762036771e-05</v>
+        <v>2.32332676203677e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.652745788633553e-05</v>
+        <v>3.652745788633558e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.347744930638327e-05</v>
+        <v>1.347744930638329e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.994377180110075e-05</v>
+        <v>1.994377180110073e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.873685059494035e-05</v>
+        <v>2.873685059494033e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>3.955506151300247e-05</v>
+        <v>3.955506151300246e-05</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.284774864676768e-05</v>
+        <v>7.284774864676755e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.629673419349562e-05</v>
+        <v>1.629673419349567e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.861989885167094e-05</v>
+        <v>1.861989885167095e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.633097382815276e-05</v>
+        <v>1.633097382815281e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.633097382815276e-05</v>
+        <v>1.633097382815281e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.210743093715314e-05</v>
+        <v>3.210743093715311e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>5.296212066066826e-05</v>
+        <v>5.296212066066834e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.652913636662361e-05</v>
+        <v>1.652913636662364e-05</v>
       </c>
       <c r="J4" t="n">
         <v>2.05855420361276e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.556840968821964e-05</v>
+        <v>3.556840968821971e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.759471955000446e-05</v>
+        <v>5.759471955000449e-05</v>
       </c>
     </row>
     <row r="5">
@@ -4994,34 +4994,34 @@
         <v>0.001160322299038592</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001819411642815725</v>
+        <v>0.000181941164281573</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002227373792459577</v>
+        <v>0.0002227373792459582</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001819411676434765</v>
+        <v>0.000181941167643477</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001819411676434765</v>
+        <v>0.000181941167643477</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000474416360687204</v>
+        <v>0.0004744163606872044</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009400975962129091</v>
+        <v>0.0009400975962129096</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001819374630861064</v>
+        <v>0.0001819374630861068</v>
       </c>
       <c r="J5" t="n">
         <v>0.0002730852509264685</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0005260409395401833</v>
+        <v>0.000526040939540183</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002354731552780863</v>
+        <v>0.0002354731552780862</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.454593621131129e-05</v>
+        <v>7.454593621131108e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.775399006251556e-05</v>
+        <v>1.775399006251562e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.998899680422175e-05</v>
+        <v>1.998899680422177e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.767676661806674e-05</v>
+        <v>1.767676661806678e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>1.815014625929319e-05</v>
+        <v>1.815014625929323e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.380561850169649e-05</v>
+        <v>3.380561850169654e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.913717348770766e-05</v>
+        <v>5.913717348770774e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.244844912513775e-05</v>
+        <v>2.244844912513777e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.240067767506775e-05</v>
+        <v>2.240067767506776e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.750831728665335e-05</v>
+        <v>3.750831728665356e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.949828055584465e-05</v>
+        <v>5.949828055584472e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.733465926984793e-05</v>
+        <v>7.733465926984777e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>2.101974818516967e-05</v>
+        <v>2.101974818516972e-05</v>
       </c>
       <c r="D7" t="n">
         <v>2.310526584795919e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.100898667928619e-05</v>
+        <v>2.100898667928624e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.100898667928619e-05</v>
+        <v>2.100898667928623e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.659434156023322e-05</v>
+        <v>3.65943415602332e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.744903128374839e-05</v>
+        <v>5.744903128374845e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.101604698970371e-05</v>
+        <v>2.101604698970374e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.507245265920769e-05</v>
+        <v>2.507245265920773e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.005532031129977e-05</v>
+        <v>4.005532031129981e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.208163017308451e-05</v>
+        <v>6.208163017308463e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.578617018041003e-05</v>
+        <v>8.578617018040987e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.834665440945888e-05</v>
+        <v>3.834665440945896e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.228206227426125e-05</v>
+        <v>4.228206227426124e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.591779664396705e-05</v>
+        <v>3.591779664396707e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.974730726014499e-05</v>
+        <v>2.974730726014502e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.39278535708168e-05</v>
+        <v>5.392785357081674e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.478254329433151e-05</v>
+        <v>7.478254329433159e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.834955900028728e-05</v>
+        <v>3.834955900028732e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.240771023720442e-05</v>
+        <v>4.240771023720443e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.834184349144892e-05</v>
+        <v>4.834184349144888e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.869313503317479e-05</v>
+        <v>8.869313503317507e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5151,25 +5151,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.654455195148192e-05</v>
+        <v>9.654455195148188e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.70708463794007e-05</v>
+        <v>4.707084637940077e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.915790982693756e-05</v>
+        <v>4.91579098269376e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.496544392140999e-05</v>
+        <v>5.496544392141003e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.707083864113789e-05</v>
+        <v>4.707083864113792e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>6.264543975446428e-05</v>
+        <v>6.264543975446427e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>8.350012947797958e-05</v>
+        <v>8.350012947797955e-05</v>
       </c>
       <c r="I9" t="n">
         <v>4.706714518393475e-05</v>
@@ -5178,10 +5178,10 @@
         <v>5.11235508534388e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.214259807167912e-05</v>
+        <v>6.214259807167907e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.813272836731563e-05</v>
+        <v>8.813272836731571e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.345048840330389e-05</v>
+        <v>1.345048840330391e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.121600613056201e-05</v>
+        <v>1.121600613056202e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>9.729797675403951e-06</v>
+        <v>9.729797675403973e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.159983150235722e-05</v>
+        <v>1.159983150235725e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.054399646058545e-05</v>
+        <v>1.054399646058548e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.095016703907456e-05</v>
+        <v>1.095016703907455e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.238339335644911e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.007964889452381e-05</v>
+        <v>1.007964889452383e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.230901747845895e-05</v>
+        <v>1.230901747845898e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.347246569537302e-05</v>
+        <v>1.347246569537304e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.300439647980043e-05</v>
+        <v>1.300439647980045e-05</v>
       </c>
     </row>
     <row r="3">
@@ -5307,34 +5307,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1390536801927e-05</v>
+        <v>4.139053680192699e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.92963887722398e-05</v>
+        <v>1.929638877223982e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.492587771091564e-05</v>
+        <v>1.492587771091568e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.990514636597635e-05</v>
+        <v>1.990514636597639e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.816205696584126e-05</v>
+        <v>1.81620569658413e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.36232975598465e-05</v>
+        <v>2.362329755984652e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.399080262789787e-05</v>
+        <v>3.399080262789795e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.739372327967024e-05</v>
+        <v>1.739372327967026e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.956458680594799e-05</v>
+        <v>1.956458680594801e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.96522644530377e-05</v>
+        <v>2.965226445303772e-05</v>
       </c>
       <c r="L3" t="n">
         <v>3.838078213677709e-05</v>
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.109965944847599e-05</v>
+        <v>6.109965944847602e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>2.275020300609105e-05</v>
+        <v>2.275020300609103e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.907274607454893e-05</v>
+        <v>1.907274607454899e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>2.278100277345758e-05</v>
+        <v>2.278100277345759e-05</v>
       </c>
       <c r="F4" t="n">
         <v>2.278100277345758e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.283568402632567e-05</v>
+        <v>3.283568402632565e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.905689118776218e-05</v>
+        <v>4.905689118776223e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.288281080573286e-05</v>
+        <v>2.288281080573285e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>1.979891005891073e-05</v>
+        <v>1.979891005891079e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.684384832106126e-05</v>
+        <v>3.684384832106133e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.583468371960315e-05</v>
+        <v>5.583468371960308e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009026103989706341</v>
+        <v>0.0009026103989706349</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002606791241651138</v>
+        <v>0.0002606791241651146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002059851176449837</v>
+        <v>0.0002059851176449849</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002606791265526759</v>
+        <v>0.0002606791265526765</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000260679126552676</v>
+        <v>0.0002606791265526765</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004433325426358731</v>
+        <v>0.0004433325426358735</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0007986684751129859</v>
+        <v>0.0007986684751129878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002606767050077497</v>
+        <v>0.0002606767050077505</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002336116001288675</v>
+        <v>0.000233611600128868</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000477153666751292</v>
+        <v>0.0004771536667512904</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002878720345354421</v>
+        <v>0.0002878720345354417</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.284900617371462e-05</v>
+        <v>6.284900617371456e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>2.438025013868719e-05</v>
+        <v>2.43802501386872e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>2.049879941156239e-05</v>
+        <v>2.049879941156241e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>2.429457986998726e-05</v>
+        <v>2.429457986998727e-05</v>
       </c>
       <c r="F6" t="n">
         <v>2.462476263207604e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.458503075156423e-05</v>
+        <v>3.458503075156421e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.503697602663635e-05</v>
+        <v>5.50369760266365e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.863090957841952e-05</v>
+        <v>2.863090957841955e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.167911432434589e-05</v>
+        <v>2.167911432434594e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.882760514439062e-05</v>
+        <v>3.882760514439069e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.778091761091855e-05</v>
+        <v>5.778091761091833e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5473,31 +5473,31 @@
         <v>2.71249057803058e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.331097007930864e-05</v>
+        <v>2.331097007930866e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>2.712225822901705e-05</v>
+        <v>2.712225822901707e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>2.712225822901706e-05</v>
+        <v>2.712225822901708e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.707535984353501e-05</v>
+        <v>3.707535984353504e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.32965670049715e-05</v>
+        <v>5.329656700497159e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.71224866229422e-05</v>
+        <v>2.712248662294221e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.403858587612011e-05</v>
+        <v>2.40385858761201e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.108352413827066e-05</v>
+        <v>4.108352413827064e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.007435953681259e-05</v>
+        <v>6.007435953681249e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.319554039566986e-05</v>
+        <v>7.319554039566992e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>4.330314232678671e-05</v>
+        <v>4.330314232678666e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.121516409744244e-05</v>
+        <v>4.121516409744247e-05</v>
       </c>
       <c r="E8" t="n">
         <v>4.102690874720782e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>3.524416465215699e-05</v>
+        <v>3.5244164652157e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.325266727923513e-05</v>
+        <v>5.325266727923515e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>6.947387444067081e-05</v>
+        <v>6.947387444067085e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.329979405864235e-05</v>
+        <v>4.329979405864238e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.021752864619367e-05</v>
+        <v>4.021752864619369e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.878516052093324e-05</v>
+        <v>4.87851605209333e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.494375412945756e-05</v>
+        <v>8.494375412945741e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.190548879903419e-05</v>
+        <v>8.190548879903427e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.972162660125315e-05</v>
+        <v>4.972162660125314e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.590914525297361e-05</v>
+        <v>4.590914525297375e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>5.668076716984342e-05</v>
+        <v>5.668076716984345e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.972162027157876e-05</v>
+        <v>4.972162027157882e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.96720806644824e-05</v>
+        <v>5.967208066448244e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>7.5893287825919e-05</v>
+        <v>7.589328782591902e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.971920744388958e-05</v>
+        <v>4.971920744388964e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.663530669706747e-05</v>
+        <v>4.663530669706756e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>6.018611165735115e-05</v>
+        <v>6.01861116573512e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.267108035775992e-05</v>
+        <v>8.267108035775983e-05</v>
       </c>
     </row>
   </sheetData>
@@ -5663,34 +5663,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.303476151884155e-05</v>
+        <v>1.303476151884156e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.324793014651292e-05</v>
+        <v>1.324793014651291e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>9.979193314249374e-06</v>
+        <v>9.979193314249429e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.360949343395519e-05</v>
+        <v>1.360949343395522e-05</v>
       </c>
       <c r="F2" t="n">
         <v>1.26088184042447e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.109465120039501e-05</v>
+        <v>1.109465120039506e-05</v>
       </c>
       <c r="H2" t="n">
         <v>1.222271642245763e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.151362559142755e-05</v>
+        <v>1.15136255914276e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>1.308141803743823e-05</v>
+        <v>1.308141803743821e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.389205355541622e-05</v>
+        <v>1.389205355541619e-05</v>
       </c>
       <c r="L2" t="n">
         <v>1.305762119976556e-05</v>
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.662682994379204e-05</v>
+        <v>3.662682994379201e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.868391125146181e-05</v>
+        <v>2.868391125146182e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.492913785000422e-05</v>
+        <v>1.492913785000424e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>2.92630325666843e-05</v>
+        <v>2.926303256668429e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>2.761099862807209e-05</v>
+        <v>2.761099862807207e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>2.287126423352183e-05</v>
+        <v>2.287126423352186e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.102724969878666e-05</v>
+        <v>3.102724969878667e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.580135606488941e-05</v>
+        <v>2.580135606488935e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.137334054240586e-05</v>
+        <v>2.137334054240578e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.972636264605146e-05</v>
+        <v>2.972636264605152e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6962907530611e-05</v>
+        <v>3.696290753061097e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.413697017329898e-05</v>
+        <v>5.413697017329902e-05</v>
       </c>
       <c r="C4" t="n">
         <v>3.696278218980337e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.962292167161053e-05</v>
+        <v>1.962292167161057e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.698481970963906e-05</v>
+        <v>3.698481970963902e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>3.698481970963904e-05</v>
+        <v>3.698481970963902e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.220954633904538e-05</v>
+        <v>3.22095463390454e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.500536265968994e-05</v>
+        <v>4.500536265968997e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.687231036809418e-05</v>
+        <v>3.687231036809415e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.226952289442276e-05</v>
+        <v>2.226952289442281e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.703004807083531e-05</v>
+        <v>3.703004807083538e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.417825488904219e-05</v>
+        <v>5.417825488904223e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000747058479167152</v>
+        <v>0.000747058479167151</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004591226193033833</v>
+        <v>0.0004591226193033832</v>
       </c>
       <c r="D5" t="n">
         <v>0.0001936514680174013</v>
@@ -5798,22 +5798,22 @@
         <v>0.0004591226189657529</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0004066619000692817</v>
+        <v>0.0004066619000692821</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0006756444268953889</v>
+        <v>0.0006756444268953888</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0004591235340230474</v>
+        <v>0.0004591235340230471</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000260112434042258</v>
+        <v>0.0002601124340422584</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004411219528848326</v>
+        <v>0.0004411219528848328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002590622450451358</v>
+        <v>0.0002590622450451367</v>
       </c>
     </row>
     <row r="6">
@@ -5823,25 +5823,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.622400803289777e-05</v>
+        <v>5.622400803289772e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.915792458722095e-05</v>
+        <v>3.915792458722097e-05</v>
       </c>
       <c r="D6" t="n">
         <v>2.136279440772934e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>3.904287643496779e-05</v>
+        <v>3.904287643496781e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.907678189895416e-05</v>
+        <v>3.907678189895418e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.823938229598209e-05</v>
+        <v>3.823938229598225e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.125456745395325e-05</v>
+        <v>5.125456745395323e-05</v>
       </c>
       <c r="I6" t="n">
         <v>3.895934822769298e-05</v>
@@ -5850,10 +5850,10 @@
         <v>2.83452113168793e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.931666530498287e-05</v>
+        <v>3.93166653049829e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.646564793640448e-05</v>
+        <v>5.646564793640453e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.847830100615526e-05</v>
+        <v>5.847830100615521e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>4.121272648128595e-05</v>
+        <v>4.121272648128597e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.396277115115243e-05</v>
+        <v>2.396277115115248e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>4.122973443332673e-05</v>
+        <v>4.122973443332672e-05</v>
       </c>
       <c r="F7" t="n">
         <v>4.122973443332672e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.655087717190161e-05</v>
+        <v>3.655087717190173e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.934669349254625e-05</v>
+        <v>4.934669349254622e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>4.121364120095041e-05</v>
+        <v>4.121364120095043e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6610853727279e-05</v>
+        <v>2.661085372727901e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.137137890369152e-05</v>
+        <v>4.137137890369158e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.851958572189838e-05</v>
+        <v>5.851958572189841e-05</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.62252585187201e-05</v>
+        <v>6.622525851872007e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>5.730421186060645e-05</v>
+        <v>5.73042118606065e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>4.176216546541571e-05</v>
+        <v>4.176216546541573e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>5.502496705776199e-05</v>
+        <v>5.502496705776202e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>4.923459572260857e-05</v>
+        <v>4.923459572260853e-05</v>
       </c>
       <c r="G8" t="n">
         <v>5.262259653287275e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>6.541841285351716e-05</v>
+        <v>6.54184128535172e-05</v>
       </c>
       <c r="I8" t="n">
         <v>5.728536056192156e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>4.268420914154345e-05</v>
+        <v>4.26842091415435e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>4.896369969107422e-05</v>
+        <v>4.896369969107423e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>8.328721493789652e-05</v>
+        <v>8.328721493789659e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.404899144018273e-05</v>
+        <v>7.404899144018278e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>6.257049079635094e-05</v>
+        <v>6.257049079635098e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.532201820471847e-05</v>
+        <v>4.53220182047185e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>6.924864428592038e-05</v>
+        <v>6.924864428592046e-05</v>
       </c>
       <c r="F9" t="n">
         <v>6.257048407637843e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.790864148696658e-05</v>
+        <v>5.790864148696667e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>7.070445780761114e-05</v>
+        <v>7.07044578076112e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>6.257140551601539e-05</v>
+        <v>6.257140551601541e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.796861804234397e-05</v>
+        <v>4.796861804234403e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>5.937609046710083e-05</v>
+        <v>5.937609046710092e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>7.98773500369634e-05</v>
+        <v>7.987735003696345e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.611574896293885e-06</v>
+        <v>5.611574896293879e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.054714258577602e-06</v>
+        <v>6.054714258577601e-06</v>
       </c>
       <c r="D2" t="n">
         <v>5.440575376265112e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.348255342573665e-06</v>
+        <v>6.348255342573657e-06</v>
       </c>
       <c r="F2" t="n">
         <v>5.512255541763187e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>5.663592678995471e-06</v>
+        <v>5.663592678995457e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.341945756421682e-06</v>
+        <v>6.34194575642168e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.256742403221318e-06</v>
+        <v>5.256742403221315e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.744936898830573e-06</v>
+        <v>7.744936898830609e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.43379165208948e-06</v>
+        <v>6.433791652089485e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>6.505062065789903e-06</v>
+        <v>6.505062065789905e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6099,31 +6099,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.567364258039663e-06</v>
+        <v>8.567364258039641e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>7.376884301853954e-06</v>
+        <v>7.376884301853959e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>7.349832936311985e-06</v>
+        <v>7.349832936311993e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>7.852538886136056e-06</v>
+        <v>7.852538886136071e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.472339505623507e-06</v>
+        <v>6.472339505623488e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>8.938623466247355e-06</v>
+        <v>8.938623466247343e-06</v>
       </c>
       <c r="H3" t="n">
         <v>1.37834953571724e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.048683277881515e-06</v>
+        <v>6.048683277881502e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.27985742075003e-05</v>
+        <v>1.279857420750034e-05</v>
       </c>
       <c r="K3" t="n">
         <v>9.480098464274932e-06</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.067830678977612e-05</v>
+        <v>1.067830678977609e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>6.481971657560936e-06</v>
+        <v>6.481971657560931e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>8.746788547385513e-06</v>
+        <v>8.746788547385519e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>6.495843973165334e-06</v>
+        <v>6.495843973165331e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>6.495843973165334e-06</v>
+        <v>6.49584397316533e-06</v>
       </c>
       <c r="G4" t="n">
         <v>1.124779754188914e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.892913464936902e-05</v>
+        <v>1.8929134649369e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>6.552817569568544e-06</v>
+        <v>6.552817569568534e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>1.210203028445493e-05</v>
+        <v>1.210203028445492e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>9.763460869154557e-06</v>
+        <v>9.763460869154545e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>2.066832503904278e-05</v>
+        <v>2.066832503904275e-05</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001156659386869449</v>
+        <v>0.0001156659386869445</v>
       </c>
       <c r="C5" t="n">
-        <v>4.742850083979159e-05</v>
+        <v>4.74285008397916e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>8.075825007763938e-05</v>
+        <v>8.075825007763924e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.742850227463945e-05</v>
+        <v>4.742850227463939e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.742850227463946e-05</v>
+        <v>4.742850227463939e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001267606535000878</v>
+        <v>0.0001267606535000879</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002732958085982468</v>
+        <v>0.0002732958085982465</v>
       </c>
       <c r="I5" t="n">
-        <v>4.742730687254401e-05</v>
+        <v>4.742730687254403e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001526978094722707</v>
+        <v>0.0001526978094722706</v>
       </c>
       <c r="K5" t="n">
-        <v>9.829509644418346e-05</v>
+        <v>9.829509644418324e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003337766901353726</v>
+        <v>0.0003337766901353722</v>
       </c>
     </row>
     <row r="6">
@@ -6219,28 +6219,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.377429231307329e-05</v>
+        <v>1.377429231307316e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>7.162527431079366e-06</v>
+        <v>7.162527431079372e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.186960005175787e-05</v>
+        <v>1.186960005175786e-05</v>
       </c>
       <c r="E6" t="n">
         <v>7.122863092090753e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>7.284532498031554e-06</v>
+        <v>7.28453249803155e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.434378306518631e-05</v>
+        <v>1.434378306518625e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.974452025901032e-05</v>
+        <v>1.974452025901029e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.648803092865707e-06</v>
+        <v>9.64880309286557e-06</v>
       </c>
       <c r="J6" t="n">
         <v>1.522105275266357e-05</v>
@@ -6249,7 +6249,7 @@
         <v>1.051165407579541e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.149449595984497e-05</v>
+        <v>2.149449595984495e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.369460813795961e-05</v>
+        <v>1.36946081379596e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>9.570312884999647e-06</v>
+        <v>9.570312884999642e-06</v>
       </c>
       <c r="D7" t="n">
         <v>1.176155724346962e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>9.570842859555259e-06</v>
+        <v>9.570842859555253e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.570842859555262e-06</v>
+        <v>9.570842859555252e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.426409889007266e-05</v>
+        <v>1.426409889007265e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.194543599755255e-05</v>
+        <v>2.194543599755254e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>9.569118917752062e-06</v>
+        <v>9.569118917752055e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.511833163263843e-05</v>
+        <v>1.511833163263845e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.277976221733805e-05</v>
+        <v>1.277976221733806e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.368462638722631e-05</v>
+        <v>2.368462638722629e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.081302131104497e-05</v>
+        <v>2.081302131104495e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.350627204828414e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.710815082778556e-05</v>
+        <v>2.710815082778558e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.164195216229738e-05</v>
+        <v>2.164195216229736e-05</v>
       </c>
       <c r="F8" t="n">
         <v>1.690594303341486e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>2.819628054085306e-05</v>
+        <v>2.819628054085304e-05</v>
       </c>
       <c r="H8" t="n">
         <v>3.587761764833282e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.350130056853248e-05</v>
+        <v>2.350130056853245e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.905185238430948e-05</v>
+        <v>2.905185238430952e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.97716061427635e-05</v>
+        <v>1.977160614276346e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>4.473435897111545e-05</v>
+        <v>4.47343589711155e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6342,34 +6342,34 @@
         <v>2.603203684914395e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>2.631680361261218e-05</v>
+        <v>2.631680361261217e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>2.850958081766432e-05</v>
+        <v>2.850958081766431e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>3.140476432587249e-05</v>
+        <v>3.140476432587243e-05</v>
       </c>
       <c r="F9" t="n">
         <v>2.631680106573512e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.101058961768515e-05</v>
+        <v>3.101058961768514e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.869192672516507e-05</v>
+        <v>3.869192672516504e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.631560964536457e-05</v>
+        <v>2.631560964536454e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.186482236025097e-05</v>
+        <v>3.186482236025092e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.697162517871444e-05</v>
+        <v>2.697162517871442e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>4.043111711483881e-05</v>
+        <v>4.043111711483879e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.25153122165063e-06</v>
+        <v>4.251531221650627e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>5.108450981399838e-06</v>
+        <v>5.108450981399832e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.311695481588892e-06</v>
+        <v>4.311695481588885e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.359698161806719e-06</v>
+        <v>5.359698161806713e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.628542463947673e-06</v>
+        <v>4.628542463947664e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.343052337987406e-06</v>
+        <v>4.343052337987403e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.313130891597899e-06</v>
+        <v>4.313130891597897e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.309006465116446e-06</v>
+        <v>4.309006465116438e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.251153581677886e-06</v>
+        <v>6.251153581677878e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.015431695117575e-06</v>
+        <v>5.015431695117572e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.298907799266124e-06</v>
+        <v>4.29890779926612e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6495,34 +6495,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.318763352898118e-06</v>
+        <v>4.318763352898113e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.054380024414111e-06</v>
+        <v>6.054380024414103e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.749220623234083e-06</v>
+        <v>4.749220623234079e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.46590962605693e-06</v>
+        <v>6.465909626056932e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.258777681013128e-06</v>
+        <v>5.258777681013124e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.971012878658787e-06</v>
+        <v>4.971012878658785e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.798016963950279e-06</v>
+        <v>4.798016963950276e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.729432694315135e-06</v>
+        <v>4.729432694315136e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>8.530834715075564e-06</v>
+        <v>8.530834715075534e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.786750232674453e-06</v>
+        <v>5.786750232674447e-06</v>
       </c>
       <c r="L3" t="n">
         <v>4.672798442254763e-06</v>
@@ -6535,34 +6535,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.444834969288316e-06</v>
+        <v>4.444834969288321e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.97931139952497e-06</v>
+        <v>4.979311399524967e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>5.124417962217917e-06</v>
+        <v>5.124417962217923e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.98806602039235e-06</v>
+        <v>4.988066020392344e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>4.988066020392353e-06</v>
+        <v>4.988066020392344e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.463110398292054e-06</v>
+        <v>5.463110398292043e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.202556693160536e-06</v>
+        <v>5.202556693160537e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>4.993933316308542e-06</v>
+        <v>4.993933316308538e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>6.323379553336012e-06</v>
+        <v>6.323379553336018e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.871856430323619e-06</v>
+        <v>4.871856430323631e-06</v>
       </c>
       <c r="L4" t="n">
         <v>5.000991992442212e-06</v>
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.626173964425029e-05</v>
+        <v>1.626173964425031e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>2.788550829439569e-05</v>
+        <v>2.788550829439567e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>2.883161385769564e-05</v>
+        <v>2.883161385769563e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>2.788550920274892e-05</v>
+        <v>2.788550920274889e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>2.788550920274892e-05</v>
+        <v>2.788550920274889e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>3.404244939761019e-05</v>
+        <v>3.404244939761003e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.275634324331236e-05</v>
+        <v>3.275634324331235e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.788528503720204e-05</v>
+        <v>2.788528503720205e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.891300007973684e-05</v>
+        <v>4.891300007973679e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.361680203725142e-05</v>
+        <v>2.361680203725144e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.567021932401809e-05</v>
+        <v>1.56702193240181e-05</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.638758275358278e-06</v>
+        <v>6.638758275358287e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>5.447490484941444e-06</v>
+        <v>5.44749048494142e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.599508743383474e-06</v>
+        <v>5.599508743383469e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.419507701071471e-06</v>
+        <v>5.419507701071467e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>5.468682728105321e-06</v>
+        <v>5.468682728105314e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>7.657033704361992e-06</v>
+        <v>7.657033704362001e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>7.495992786315948e-06</v>
+        <v>7.495992786315957e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>7.187856622378507e-06</v>
+        <v>7.187856622378497e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>6.84979234252379e-06</v>
+        <v>6.849792342523793e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>5.338028069717551e-06</v>
+        <v>5.338028069717557e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>5.475767334804357e-06</v>
+        <v>5.475767334804356e-06</v>
       </c>
     </row>
     <row r="7">
@@ -6658,34 +6658,34 @@
         <v>6.877067053392156e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.426388657606002e-06</v>
+        <v>7.426388657605998e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>7.555224689249154e-06</v>
+        <v>7.555224689249157e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.429539627937818e-06</v>
+        <v>7.42953962793781e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.429539627937818e-06</v>
+        <v>7.42953962793781e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.895342482395886e-06</v>
+        <v>7.895342482395869e-06</v>
       </c>
       <c r="H7" t="n">
         <v>7.634788777264364e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.426165400412367e-06</v>
+        <v>7.42616540041236e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>8.755611637439837e-06</v>
+        <v>8.75561163743984e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.304088514427457e-06</v>
+        <v>7.30408851442747e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>7.433224076546041e-06</v>
+        <v>7.433224076546044e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.315077546971371e-05</v>
+        <v>1.31507754697137e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9520746142323e-05</v>
+        <v>1.952074614232302e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08507685578821e-05</v>
+        <v>2.085076855788211e-05</v>
       </c>
       <c r="E8" t="n">
         <v>1.79294602438419e-05</v>
@@ -6710,22 +6710,22 @@
         <v>1.388714430024885e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.998374607080059e-05</v>
+        <v>1.99837460708006e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.972319236566914e-05</v>
+        <v>1.972319236566915e-05</v>
       </c>
       <c r="I8" t="n">
         <v>1.951456898881706e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.084515798017138e-05</v>
+        <v>2.084515798017139e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.346978598266405e-05</v>
+        <v>1.346978598266406e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>2.559556298917227e-05</v>
+        <v>2.559556298917228e-05</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.581479997630888e-05</v>
+        <v>1.581479997630886e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.963173717600837e-05</v>
+        <v>1.963173717600834e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>1.976199922916423e-05</v>
+        <v>1.976199922916418e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.340249705744173e-05</v>
+        <v>2.340249705744172e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.963173749226208e-05</v>
+        <v>1.963173749226206e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.010069100079823e-05</v>
+        <v>2.010069100079819e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.984013729566673e-05</v>
+        <v>1.98401372956667e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.963151391881473e-05</v>
+        <v>1.963151391881471e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.096096015584221e-05</v>
+        <v>2.096096015584218e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.761616800335551e-05</v>
+        <v>1.761616800335548e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.963857259494843e-05</v>
+        <v>1.963857259494841e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.249827610241904e-06</v>
+        <v>4.249827610241932e-06</v>
       </c>
       <c r="C2" t="n">
         <v>5.158855744710395e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2438159846492e-06</v>
+        <v>4.243815984649232e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.403598843233459e-06</v>
+        <v>5.40359884323348e-06</v>
       </c>
       <c r="F2" t="n">
         <v>4.68814855380179e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>4.300477374293239e-06</v>
+        <v>4.300477374293248e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.294404122884953e-06</v>
+        <v>4.294404122884948e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.338389502284985e-06</v>
+        <v>4.338389502285004e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.077778498459387e-06</v>
+        <v>6.077778498459395e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>4.975552352929829e-06</v>
+        <v>4.975552352929863e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>4.412046953473473e-06</v>
+        <v>4.412046953473471e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.415751616498853e-06</v>
+        <v>4.415751616498862e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.404980595592875e-06</v>
+        <v>6.40498059559288e-06</v>
       </c>
       <c r="D3" t="n">
         <v>4.37548228779893e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8065061555392e-06</v>
+        <v>6.806506155539205e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>5.625299005127015e-06</v>
+        <v>5.625299005127034e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>4.777375847947076e-06</v>
+        <v>4.777375847947078e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.769668723568191e-06</v>
+        <v>4.769668723568197e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.046065899386197e-06</v>
+        <v>5.046065899386225e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>7.513839634675274e-06</v>
+        <v>7.513839634675282e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.607644255148303e-06</v>
+        <v>5.607644255148321e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.578614740413729e-06</v>
+        <v>5.578614740413731e-06</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.649856817730433e-06</v>
+        <v>4.649856817730421e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.548588541276161e-06</v>
+        <v>5.548588541276162e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>4.58195274117639e-06</v>
+        <v>4.581952741176381e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>5.557484376912347e-06</v>
+        <v>5.557484376912342e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.557484376912347e-06</v>
+        <v>5.557484376912342e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>5.206947511123564e-06</v>
+        <v>5.206947511123559e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.209919240049616e-06</v>
+        <v>5.209919240049608e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.553318163289356e-06</v>
+        <v>5.553318163289354e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>4.812796096621974e-06</v>
+        <v>4.812796096621964e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.634706378879814e-06</v>
+        <v>4.634706378879801e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>6.47742452068416e-06</v>
+        <v>6.477424520684155e-06</v>
       </c>
     </row>
     <row r="5">
@@ -6974,34 +6974,34 @@
         <v>1.910166202739161e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.578741894557012e-05</v>
+        <v>3.578741894557016e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9266677015571e-05</v>
+        <v>1.926667701557095e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>3.578741977318635e-05</v>
+        <v>3.57874197731864e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.578741977318635e-05</v>
+        <v>3.57874197731864e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.927501044767068e-05</v>
+        <v>2.927501044767096e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>3.162300522320353e-05</v>
+        <v>3.162300522320351e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>3.578738214655375e-05</v>
+        <v>3.578738214655381e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.280152541297377e-05</v>
+        <v>2.280152541297381e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.95125124360173e-05</v>
+        <v>1.951251243601732e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.837993264535931e-05</v>
+        <v>2.837993264535927e-05</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.116636642490041e-06</v>
+        <v>5.116636642490029e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.024432365160348e-06</v>
+        <v>6.024432365160358e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.036887265552839e-06</v>
+        <v>5.036887265552822e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>5.996313225418413e-06</v>
+        <v>5.996313225418411e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.028604407445236e-06</v>
+        <v>6.028604407445235e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>5.673727335883191e-06</v>
+        <v>5.67372733588317e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>7.510493467036001e-06</v>
+        <v>7.510493467035992e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>6.020097988048965e-06</v>
+        <v>6.020097988048957e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.326380460579607e-06</v>
+        <v>5.326380460579594e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>5.090739985606881e-06</v>
+        <v>5.090739985606859e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>6.955882673178644e-06</v>
+        <v>6.955882673178632e-06</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.06724024228069e-06</v>
+        <v>7.067240242280673e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>7.97073838685599e-06</v>
+        <v>7.970738386855987e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>6.997910226264499e-06</v>
+        <v>6.997910226264489e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.974552918697369e-06</v>
+        <v>7.974552918697356e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.974552918697369e-06</v>
+        <v>7.974552918697356e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>7.624330935673844e-06</v>
+        <v>7.624330935673834e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>7.627302664599884e-06</v>
+        <v>7.627302664599871e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>7.970701587839614e-06</v>
+        <v>7.970701587839611e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>7.230179521172228e-06</v>
+        <v>7.230179521172218e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>7.052089803430068e-06</v>
+        <v>7.052089803430071e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>8.894807945234428e-06</v>
+        <v>8.894807945234411e-06</v>
       </c>
     </row>
     <row r="8">
@@ -7091,31 +7091,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.330967481031293e-05</v>
+        <v>1.330967481031294e-05</v>
       </c>
       <c r="C8" t="n">
         <v>2.000776911199038e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>2.022996470584046e-05</v>
+        <v>2.022996470584043e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>1.842371353502719e-05</v>
+        <v>1.842371353502718e-05</v>
       </c>
       <c r="F8" t="n">
         <v>1.439977052683626e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>1.965477748588925e-05</v>
+        <v>1.965477748588923e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.965774921481613e-05</v>
+        <v>1.96577492148161e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.000114813805506e-05</v>
+        <v>2.000114813805499e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.926176358162427e-05</v>
+        <v>1.926176358162429e-05</v>
       </c>
       <c r="K8" t="n">
         <v>1.318700907733521e-05</v>
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.532384527206634e-05</v>
+        <v>1.532384527206633e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>1.930362488173623e-05</v>
+        <v>1.930362488173624e-05</v>
       </c>
       <c r="D9" t="n">
         <v>1.833222306687836e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>2.28535889845564e-05</v>
+        <v>2.285358898455639e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.930362516928095e-05</v>
+        <v>1.930362516928094e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.895721743055407e-05</v>
+        <v>1.895721743055409e-05</v>
       </c>
       <c r="H9" t="n">
         <v>1.896018915948013e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>1.930358808271988e-05</v>
+        <v>1.930358808271989e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>1.856306601605246e-05</v>
+        <v>1.856306601605247e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>1.653025228980591e-05</v>
+        <v>1.653025228980592e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>2.022769444011465e-05</v>
+        <v>2.022769444011467e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.05039691345961e-05</v>
+        <v>1.050396913459613e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>8.848905555385009e-06</v>
+        <v>8.848905555385002e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>8.412660849325788e-06</v>
+        <v>8.412660849325807e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>9.208801128604186e-06</v>
+        <v>9.208801128604118e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>8.217240628322382e-06</v>
+        <v>8.217240628322341e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>9.246592706325652e-06</v>
+        <v>9.246592706325662e-06</v>
       </c>
       <c r="H2" t="n">
         <v>1.131469362059884e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>8.0516291754714e-06</v>
+        <v>8.051629175471435e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.072341674081306e-05</v>
+        <v>1.072341674081298e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>1.066027224871073e-05</v>
+        <v>1.066027224871079e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>1.133191194273542e-05</v>
+        <v>1.133191194273543e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.841639637059071e-05</v>
+        <v>2.841639637059073e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.233514548284616e-05</v>
+        <v>1.233514548284624e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>1.355838925303969e-05</v>
+        <v>1.355838925303975e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>1.290672149046735e-05</v>
+        <v>1.290672149046731e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.126973163167851e-05</v>
+        <v>1.126973163167862e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.950216249790586e-05</v>
+        <v>1.950216249790594e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>3.422210889633797e-05</v>
+        <v>3.422210889633799e-05</v>
       </c>
       <c r="I3" t="n">
         <v>1.099449660240173e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.801123091958512e-05</v>
+        <v>1.801123091958502e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.126147577012818e-05</v>
+        <v>2.126147577012805e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>3.444107192985705e-05</v>
+        <v>3.444107192985716e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.090102365833258e-05</v>
+        <v>4.090102365833257e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.284886737985334e-05</v>
+        <v>1.284886737985338e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>1.727873452686262e-05</v>
+        <v>1.727873452686261e-05</v>
       </c>
       <c r="E4" t="n">
         <v>1.287751879936092e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.287751879936091e-05</v>
+        <v>1.287751879936092e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.667463922394788e-05</v>
+        <v>2.667463922394793e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>4.995859278397646e-05</v>
+        <v>4.995859278397657e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.304509929763331e-05</v>
+        <v>1.30450992976333e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.852140037155825e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.553412558753704e-05</v>
+        <v>2.553412558753707e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>5.000250270005002e-05</v>
+        <v>5.000250270004996e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7370,34 +7370,34 @@
         <v>0.0006123996312805864</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001333032165820013</v>
+        <v>0.000133303216582001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0002034389512479537</v>
+        <v>0.0002034389512479543</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001333032194023081</v>
+        <v>0.0001333032194023079</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001333032194023081</v>
+        <v>0.0001333032194023079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003770494808575419</v>
+        <v>0.0003770494808575422</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000824719543356011</v>
+        <v>0.0008247195433560111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001332999667336188</v>
+        <v>0.0001332999667336186</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0002463645770071681</v>
+        <v>0.0002463645770071679</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003502048160412139</v>
+        <v>0.0003502048160412143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001232049292870906</v>
+        <v>0.0001232049292870928</v>
       </c>
     </row>
     <row r="6">
@@ -7407,13 +7407,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.232624008521557e-05</v>
+        <v>4.232624008521559e-05</v>
       </c>
       <c r="C6" t="n">
-        <v>1.40733862146211e-05</v>
+        <v>1.407338621462113e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.851568507032096e-05</v>
+        <v>1.851568507032104e-05</v>
       </c>
       <c r="E6" t="n">
         <v>1.400783632274916e-05</v>
@@ -7422,22 +7422,22 @@
         <v>1.441161150061186e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.181053487806575e-05</v>
+        <v>3.181053487806579e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>5.538050660050291e-05</v>
+        <v>5.538050660050297e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>1.818099495175113e-05</v>
+        <v>1.818099495175117e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.373148827105778e-05</v>
+        <v>2.373148827105776e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>2.704586706474213e-05</v>
+        <v>2.704586706474237e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>5.162161048514942e-05</v>
+        <v>5.162161048514949e-05</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.490175659976368e-05</v>
+        <v>4.490175659976374e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>1.704908208744721e-05</v>
+        <v>1.704908208744722e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.127792788289483e-05</v>
+        <v>2.127792788289489e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.704221551662128e-05</v>
+        <v>1.70422155166213e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.704221551662128e-05</v>
+        <v>1.70422155166213e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.067537216537907e-05</v>
+        <v>3.067537216537913e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>5.395932572540772e-05</v>
+        <v>5.395932572540777e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.704583223906447e-05</v>
+        <v>1.704583223906449e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.252213331298942e-05</v>
+        <v>2.252213331298945e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.953485852896822e-05</v>
+        <v>2.953485852896824e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>5.400323564148108e-05</v>
+        <v>5.400323564148123e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.293028001196972e-05</v>
+        <v>5.293028001196982e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>3.328712965768518e-05</v>
+        <v>3.328712965768519e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.922345473469608e-05</v>
+        <v>3.922345473469609e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>3.104098163338429e-05</v>
+        <v>3.104098163338437e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.533475367413997e-05</v>
+        <v>2.533475367414001e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>4.691643573121331e-05</v>
+        <v>4.691643573121341e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>7.020038929124311e-05</v>
+        <v>7.020038929124324e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.328689580489868e-05</v>
+        <v>3.328689580489872e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.876481087809047e-05</v>
+        <v>3.876481087809049e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>3.741082979153419e-05</v>
+        <v>3.741082979153427e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>7.882298411900466e-05</v>
+        <v>7.882298411900478e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.230584232267151e-05</v>
+        <v>6.230584232267161e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>4.062056429405404e-05</v>
+        <v>4.062056429405418e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>4.485094986143559e-05</v>
+        <v>4.485094986143569e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>4.773759849690918e-05</v>
+        <v>4.773759849690909e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>4.062055626767788e-05</v>
+        <v>4.062055626767768e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>5.424685437198585e-05</v>
+        <v>5.424685437198604e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>7.753080793201458e-05</v>
+        <v>7.753080793201464e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>4.061731444567132e-05</v>
+        <v>4.061731444567137e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>4.609361551959621e-05</v>
+        <v>4.609361551959637e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.953292707014727e-05</v>
+        <v>4.953292707014737e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>7.757471784808786e-05</v>
+        <v>7.757471784808805e-05</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.549673665586068e-06</v>
+        <v>5.549673665586058e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>6.307625939525108e-06</v>
+        <v>6.307625939525111e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>6.244421380765071e-06</v>
+        <v>6.244421380765072e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.611823520942342e-06</v>
+        <v>6.611823520942352e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7517794933751e-06</v>
+        <v>5.751779493375098e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.430715717131272e-06</v>
+        <v>6.430715717131267e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.036174160469625e-06</v>
+        <v>6.036174160469616e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.620743775885512e-06</v>
+        <v>5.620743775885509e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.729334844686709e-06</v>
+        <v>7.729334844686715e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>6.417634881535111e-06</v>
+        <v>6.417634881535112e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>7.982016555616028e-06</v>
+        <v>7.982016555616023e-06</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.336902618776092e-06</v>
+        <v>5.336902618776091e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.993604551244154e-06</v>
+        <v>6.993604551244165e-06</v>
       </c>
       <c r="D3" t="n">
         <v>1.026302659544318e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>7.482536331542228e-06</v>
+        <v>7.482536331542231e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>6.062644718315214e-06</v>
+        <v>6.062644718315217e-06</v>
       </c>
       <c r="G3" t="n">
         <v>1.15965387243569e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>8.893264464078428e-06</v>
+        <v>8.89326446407843e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>5.844466040224502e-06</v>
+        <v>5.844466040224503e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.038040722049303e-05</v>
+        <v>1.038040722049306e-05</v>
       </c>
       <c r="K3" t="n">
         <v>7.751481072540826e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>2.265811039632743e-05</v>
+        <v>2.265811039632742e-05</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.10743383202309e-06</v>
+        <v>5.107433832023099e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>5.649482365417139e-06</v>
+        <v>5.649482365417145e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>1.295492887470901e-05</v>
+        <v>1.2954928874709e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>5.668173065810081e-06</v>
+        <v>5.668173065810088e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>5.668173065810077e-06</v>
+        <v>5.668173065810085e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>1.503849381759411e-05</v>
+        <v>1.50384938175941e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.076044404002819e-05</v>
+        <v>1.076044404002822e-05</v>
       </c>
       <c r="I4" t="n">
         <v>5.774860856089209e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>8.083105391013571e-06</v>
+        <v>8.083105391013584e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>7.142750958654692e-06</v>
+        <v>7.142750958654709e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>3.237892307097633e-05</v>
+        <v>3.237892307097634e-05</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.59874877526823e-05</v>
+        <v>1.598748775268227e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>3.022500012367991e-05</v>
+        <v>3.022500012367995e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0001380317218691262</v>
+        <v>0.0001380317218691261</v>
       </c>
       <c r="E5" t="n">
-        <v>3.022500210179997e-05</v>
+        <v>3.022500210180001e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>3.022500210179997e-05</v>
+        <v>3.022500210180001e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001772602000440797</v>
+        <v>0.0001772602000440792</v>
       </c>
       <c r="H5" t="n">
         <v>0.0001151761676478015</v>
       </c>
       <c r="I5" t="n">
-        <v>3.022276044167293e-05</v>
+        <v>3.022276044167295e-05</v>
       </c>
       <c r="J5" t="n">
         <v>6.874591871651929e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8496159376668e-05</v>
+        <v>4.849615937666803e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005354948745797985</v>
+        <v>0.0005354948745797972</v>
       </c>
     </row>
     <row r="6">
@@ -7803,34 +7803,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.379151540387234e-06</v>
+        <v>8.379151540387251e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>6.259875739549043e-06</v>
+        <v>6.259875739549041e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3712174841453e-05</v>
+        <v>1.371217484145298e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>6.225558515833173e-06</v>
+        <v>6.22555851583318e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>6.461995810039411e-06</v>
+        <v>6.461995810039417e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.831021152595829e-05</v>
+        <v>1.831021152595825e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.417428135352836e-05</v>
+        <v>1.417428135352838e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>9.046578564453372e-06</v>
+        <v>9.04657856445337e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>8.868283483858455e-06</v>
+        <v>8.868283483858457e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>7.710142856138545e-06</v>
+        <v>7.710142856138539e-06</v>
       </c>
       <c r="L6" t="n">
         <v>3.323306831843621e-05</v>
@@ -7846,34 +7846,34 @@
         <v>8.101772817037445e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>8.771439523110532e-06</v>
+        <v>8.771439523110539e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>1.594784195894682e-05</v>
+        <v>1.594784195894683e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>8.769017478209161e-06</v>
+        <v>8.769017478209178e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.769017478209161e-06</v>
+        <v>8.769017478209178e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.803283280260846e-05</v>
+        <v>1.803283280260842e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.375478302504256e-05</v>
+        <v>1.375478302504257e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.769199841103559e-06</v>
+        <v>8.769199841103571e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>1.107744437602791e-05</v>
+        <v>1.107744437602793e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.013708994366905e-05</v>
+        <v>1.013708994366904e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.537326205599075e-05</v>
+        <v>3.53732620559907e-05</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.494977926797016e-05</v>
+        <v>1.49497792679702e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>2.227429492397311e-05</v>
+        <v>2.227429492397319e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>3.083109798067205e-05</v>
+        <v>3.083109798067213e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>2.045400044383294e-05</v>
+        <v>2.045400044383299e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.582977597706682e-05</v>
+        <v>1.582977597706688e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.153490006676248e-05</v>
+        <v>3.153490006676254e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.725685028919525e-05</v>
+        <v>2.725685028919532e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>2.227126710525754e-05</v>
+        <v>2.227126710525762e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.458081935375388e-05</v>
+        <v>2.458081935375394e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.686149379881805e-05</v>
+        <v>1.68614937988181e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.582605224300719e-05</v>
+        <v>5.582605224300726e-05</v>
       </c>
     </row>
     <row r="9">
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.945840306916958e-05</v>
+        <v>1.945840306916959e-05</v>
       </c>
       <c r="C9" t="n">
         <v>2.427115211655042e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>3.144898455236229e-05</v>
+        <v>3.144898455236228e-05</v>
       </c>
       <c r="E9" t="n">
         <v>2.905218463603047e-05</v>
@@ -7938,22 +7938,22 @@
         <v>2.42711522238069e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>3.353254539604841e-05</v>
+        <v>3.353254539604839e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.925449561848246e-05</v>
+        <v>2.925449561848244e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>2.426891243454346e-05</v>
+        <v>2.426891243454347e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.657715696946784e-05</v>
+        <v>2.657715696946783e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.323628608152839e-05</v>
+        <v>2.323628608152835e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>5.087297464943059e-05</v>
+        <v>5.087297464943058e-05</v>
       </c>
     </row>
   </sheetData>
